--- a/docs/narrative/02_MATRIZ_DIALOGOS_Y_TEXTOS_GVO.xlsx
+++ b/docs/narrative/02_MATRIZ_DIALOGOS_Y_TEXTOS_GVO.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz" sheetId="1" r:id="R8cf6ffd179714070"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz" sheetId="1" r:id="R4601b69ae7054791"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -193,7 +193,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
-        <x:v>﻿ID</x:v>
+        <x:v>ID</x:v>
       </x:c>
       <x:c r="B1" t="str">
         <x:v>Pantalla / estación</x:v>
@@ -2223,22 +2223,22 @@
         <x:v>Entrada</x:v>
       </x:c>
       <x:c r="F50" t="str">
-        <x:v>Planta, Lía y seis capas apagadas.</x:v>
+        <x:v>Escena inicial con Lía y elementos principales visibles.</x:v>
       </x:c>
       <x:c r="G50" t="str">
-        <x:v>Transición desde Mundo I.</x:v>
+        <x:v>Ingreso a la pantalla.</x:v>
       </x:c>
       <x:c r="H50" t="str">
-        <x:v>Presentar que hay una señal invisible que debe ser mediada.</x:v>
+        <x:v>Presentar la diferencia entre planta viva, señal y música mediada.</x:v>
       </x:c>
       <x:c r="I50" t="str">
-        <x:v>Señal bioeléctrica</x:v>
+        <x:v>Señal bioeléctrica / mediación</x:v>
       </x:c>
       <x:c r="J50" t="str">
-        <x:v>Planta hace música</x:v>
+        <x:v>Planta que canta</x:v>
       </x:c>
       <x:c r="K50" t="str">
-        <x:v>90-170 caracteres</x:v>
+        <x:v>90-160 caracteres</x:v>
       </x:c>
       <x:c r="L50" t="str"/>
       <x:c r="M50" t="str"/>
@@ -2249,37 +2249,37 @@
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str">
-        <x:v>W2_PLANTA_LIA_01</x:v>
+        <x:v>W2_INTRO_AMB_01</x:v>
       </x:c>
       <x:c r="B51" t="str">
         <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C51" t="str">
-        <x:v>w2_planta</x:v>
+        <x:v>w2_intro</x:v>
       </x:c>
       <x:c r="D51" t="str">
-        <x:v>Lía</x:v>
+        <x:v>Ambiente</x:v>
       </x:c>
       <x:c r="E51" t="str">
-        <x:v>Diálogo por capa</x:v>
+        <x:v>Texto ambiental</x:v>
       </x:c>
       <x:c r="F51" t="str">
-        <x:v>Capa activa se ilumina; Lía acompaña.</x:v>
+        <x:v>Escena inicial con Lía y elementos principales visibles.</x:v>
       </x:c>
       <x:c r="G51" t="str">
-        <x:v>Visitante activó la capa correspondiente.</x:v>
+        <x:v>Ingreso a la pantalla.</x:v>
       </x:c>
       <x:c r="H51" t="str">
-        <x:v>Reconocer el origen vivo.</x:v>
+        <x:v>Situar el pulso invisible como algo que no se ve a simple vista.</x:v>
       </x:c>
       <x:c r="I51" t="str">
-        <x:v>Planta viva</x:v>
+        <x:v>Invisibilidad / pulso</x:v>
       </x:c>
       <x:c r="J51" t="str">
-        <x:v>Tecnicismo largo o magia</x:v>
+        <x:v>Magia literal</x:v>
       </x:c>
       <x:c r="K51" t="str">
-        <x:v>80-150 caracteres</x:v>
+        <x:v>50-120 caracteres</x:v>
       </x:c>
       <x:c r="L51" t="str"/>
       <x:c r="M51" t="str"/>
@@ -2290,37 +2290,37 @@
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="str">
-        <x:v>W2_SENAL_LIA_01</x:v>
+        <x:v>W2_PLANTA_HINT_01</x:v>
       </x:c>
       <x:c r="B52" t="str">
         <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C52" t="str">
-        <x:v>w2_senal</x:v>
+        <x:v>w2_planta_available</x:v>
       </x:c>
       <x:c r="D52" t="str">
         <x:v>Lía</x:v>
       </x:c>
       <x:c r="E52" t="str">
-        <x:v>Diálogo por capa</x:v>
+        <x:v>Instrucción contextual</x:v>
       </x:c>
       <x:c r="F52" t="str">
-        <x:v>Capa activa se ilumina; Lía acompaña.</x:v>
+        <x:v>Elemento PLANTA disponible o activo.</x:v>
       </x:c>
       <x:c r="G52" t="str">
-        <x:v>Visitante activó la capa correspondiente.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H52" t="str">
-        <x:v>Aclarar que la señal existe pero no es música.</x:v>
+        <x:v>Invitar a activar la capa PLANTA VIVA.</x:v>
       </x:c>
       <x:c r="I52" t="str">
-        <x:v>Señal bioeléctrica</x:v>
+        <x:v>Planta viva</x:v>
       </x:c>
       <x:c r="J52" t="str">
-        <x:v>Tecnicismo largo o magia</x:v>
+        <x:v>Orden agresiva</x:v>
       </x:c>
       <x:c r="K52" t="str">
-        <x:v>80-150 caracteres</x:v>
+        <x:v>40-90 caracteres</x:v>
       </x:c>
       <x:c r="L52" t="str"/>
       <x:c r="M52" t="str"/>
@@ -2331,37 +2331,37 @@
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="str">
-        <x:v>W2_CAPTURA_LIA_01</x:v>
+        <x:v>W2_PLANTA_AMB_01</x:v>
       </x:c>
       <x:c r="B53" t="str">
         <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C53" t="str">
-        <x:v>w2_captura</x:v>
+        <x:v>w2_planta_active</x:v>
       </x:c>
       <x:c r="D53" t="str">
-        <x:v>Lía</x:v>
+        <x:v>Ambiente</x:v>
       </x:c>
       <x:c r="E53" t="str">
-        <x:v>Diálogo por capa</x:v>
+        <x:v>Respuesta ambiental</x:v>
       </x:c>
       <x:c r="F53" t="str">
-        <x:v>Capa activa se ilumina; Lía acompaña.</x:v>
+        <x:v>Elemento PLANTA disponible o activo.</x:v>
       </x:c>
       <x:c r="G53" t="str">
-        <x:v>Visitante activó la capa correspondiente.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H53" t="str">
-        <x:v>Mostrar primer paso de mediación.</x:v>
+        <x:v>Reconocer la planta como origen vivo del proceso.</x:v>
       </x:c>
       <x:c r="I53" t="str">
-        <x:v>Captura</x:v>
+        <x:v>Vida / origen</x:v>
       </x:c>
       <x:c r="J53" t="str">
-        <x:v>Tecnicismo largo o magia</x:v>
+        <x:v>Adorno</x:v>
       </x:c>
       <x:c r="K53" t="str">
-        <x:v>80-150 caracteres</x:v>
+        <x:v>50-120 caracteres</x:v>
       </x:c>
       <x:c r="L53" t="str"/>
       <x:c r="M53" t="str"/>
@@ -2372,37 +2372,37 @@
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="str">
-        <x:v>W2_ACOND_LIA_01</x:v>
+        <x:v>W2_PLANTA_CONFIRM_01</x:v>
       </x:c>
       <x:c r="B54" t="str">
         <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C54" t="str">
-        <x:v>w2_acond</x:v>
+        <x:v>w2_planta_active</x:v>
       </x:c>
       <x:c r="D54" t="str">
         <x:v>Lía</x:v>
       </x:c>
       <x:c r="E54" t="str">
-        <x:v>Diálogo por capa</x:v>
+        <x:v>Confirmación breve</x:v>
       </x:c>
       <x:c r="F54" t="str">
-        <x:v>Capa activa se ilumina; Lía acompaña.</x:v>
+        <x:v>Elemento PLANTA disponible o activo.</x:v>
       </x:c>
       <x:c r="G54" t="str">
-        <x:v>Visitante activó la capa correspondiente.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H54" t="str">
-        <x:v>Explicar preparación de la señal.</x:v>
+        <x:v>Confirmar que el recorrido parte de una vida, no de una máquina.</x:v>
       </x:c>
       <x:c r="I54" t="str">
-        <x:v>Acondicionamiento</x:v>
+        <x:v>Origen vivo</x:v>
       </x:c>
       <x:c r="J54" t="str">
-        <x:v>Tecnicismo largo o magia</x:v>
+        <x:v>Máquina como origen</x:v>
       </x:c>
       <x:c r="K54" t="str">
-        <x:v>80-150 caracteres</x:v>
+        <x:v>40-100 caracteres</x:v>
       </x:c>
       <x:c r="L54" t="str"/>
       <x:c r="M54" t="str"/>
@@ -2413,37 +2413,37 @@
     </x:row>
     <x:row r="55">
       <x:c r="A55" t="str">
-        <x:v>W2_MAPEO_LIA_01</x:v>
+        <x:v>W2_SENAL_HINT_01</x:v>
       </x:c>
       <x:c r="B55" t="str">
         <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C55" t="str">
-        <x:v>w2_mapeo</x:v>
+        <x:v>w2_senal_available</x:v>
       </x:c>
       <x:c r="D55" t="str">
         <x:v>Lía</x:v>
       </x:c>
       <x:c r="E55" t="str">
-        <x:v>Diálogo por capa</x:v>
+        <x:v>Instrucción contextual</x:v>
       </x:c>
       <x:c r="F55" t="str">
-        <x:v>Capa activa se ilumina; Lía acompaña.</x:v>
+        <x:v>Elemento SENAL disponible o activo.</x:v>
       </x:c>
       <x:c r="G55" t="str">
-        <x:v>Visitante activó la capa correspondiente.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H55" t="str">
-        <x:v>Explicar interpretación/traducción de datos.</x:v>
+        <x:v>Invitar a activar la capa SEÑAL.</x:v>
       </x:c>
       <x:c r="I55" t="str">
-        <x:v>Mapeo</x:v>
+        <x:v>Señal bioeléctrica</x:v>
       </x:c>
       <x:c r="J55" t="str">
-        <x:v>Tecnicismo largo o magia</x:v>
+        <x:v>Música directa</x:v>
       </x:c>
       <x:c r="K55" t="str">
-        <x:v>80-150 caracteres</x:v>
+        <x:v>40-90 caracteres</x:v>
       </x:c>
       <x:c r="L55" t="str"/>
       <x:c r="M55" t="str"/>
@@ -2454,37 +2454,37 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" t="str">
-        <x:v>W2_RESULTADO_LIA_01</x:v>
+        <x:v>W2_SENAL_AMB_01</x:v>
       </x:c>
       <x:c r="B56" t="str">
         <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C56" t="str">
-        <x:v>w2_resultado</x:v>
+        <x:v>w2_senal_active</x:v>
       </x:c>
       <x:c r="D56" t="str">
-        <x:v>Lía</x:v>
+        <x:v>Ambiente</x:v>
       </x:c>
       <x:c r="E56" t="str">
-        <x:v>Diálogo por capa</x:v>
+        <x:v>Respuesta ambiental</x:v>
       </x:c>
       <x:c r="F56" t="str">
-        <x:v>Capa activa se ilumina; Lía acompaña.</x:v>
+        <x:v>Elemento SENAL disponible o activo.</x:v>
       </x:c>
       <x:c r="G56" t="str">
-        <x:v>Visitante activó la capa correspondiente.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H56" t="str">
-        <x:v>Cerrar como experiencia sonora mediada.</x:v>
+        <x:v>Mostrar que hay actividad no visible en la planta.</x:v>
       </x:c>
       <x:c r="I56" t="str">
-        <x:v>Resultado mediado</x:v>
+        <x:v>Bioelectricidad</x:v>
       </x:c>
       <x:c r="J56" t="str">
-        <x:v>Tecnicismo largo o magia</x:v>
+        <x:v>Canto literal</x:v>
       </x:c>
       <x:c r="K56" t="str">
-        <x:v>80-150 caracteres</x:v>
+        <x:v>50-130 caracteres</x:v>
       </x:c>
       <x:c r="L56" t="str"/>
       <x:c r="M56" t="str"/>
@@ -2495,37 +2495,37 @@
     </x:row>
     <x:row r="57">
       <x:c r="A57" t="str">
-        <x:v>W2_LOCKED_01</x:v>
+        <x:v>W2_SENAL_CONFIRM_01</x:v>
       </x:c>
       <x:c r="B57" t="str">
         <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C57" t="str">
-        <x:v>w2_layer_locked</x:v>
+        <x:v>w2_senal_active</x:v>
       </x:c>
       <x:c r="D57" t="str">
-        <x:v>Lía o sistema</x:v>
+        <x:v>Lía</x:v>
       </x:c>
       <x:c r="E57" t="str">
-        <x:v>Bloqueo suave</x:v>
+        <x:v>Confirmación breve</x:v>
       </x:c>
       <x:c r="F57" t="str">
-        <x:v>Usuario toca capa fuera de orden.</x:v>
+        <x:v>Elemento SENAL disponible o activo.</x:v>
       </x:c>
       <x:c r="G57" t="str">
-        <x:v>Toque fuera de secuencia.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H57" t="str">
-        <x:v>Recordar que la señal se comprende por etapas.</x:v>
+        <x:v>Aclarar que señal no equivale todavía a sonido.</x:v>
       </x:c>
       <x:c r="I57" t="str">
-        <x:v>Orden por capas</x:v>
+        <x:v>Señal no es música</x:v>
       </x:c>
       <x:c r="J57" t="str">
-        <x:v>Regaño técnico</x:v>
+        <x:v>Confundir señal y música</x:v>
       </x:c>
       <x:c r="K57" t="str">
-        <x:v>40-100 caracteres</x:v>
+        <x:v>50-110 caracteres</x:v>
       </x:c>
       <x:c r="L57" t="str"/>
       <x:c r="M57" t="str"/>
@@ -2536,37 +2536,37 @@
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="str">
-        <x:v>W2_COMPLETE_LIA_01</x:v>
+        <x:v>W2_CAPTURA_HINT_01</x:v>
       </x:c>
       <x:c r="B58" t="str">
         <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C58" t="str">
-        <x:v>w2_complete</x:v>
+        <x:v>w2_captura_available</x:v>
       </x:c>
       <x:c r="D58" t="str">
         <x:v>Lía</x:v>
       </x:c>
       <x:c r="E58" t="str">
-        <x:v>Cierre</x:v>
+        <x:v>Instrucción contextual</x:v>
       </x:c>
       <x:c r="F58" t="str">
-        <x:v>Seis capas completadas.</x:v>
+        <x:v>Elemento CAPTURA disponible o activo.</x:v>
       </x:c>
       <x:c r="G58" t="str">
-        <x:v>Usuario completó Resultado mediado.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H58" t="str">
-        <x:v>Cerrar diferencia entre señal y experiencia sonora.</x:v>
+        <x:v>Invitar a activar la capa CAPTURA.</x:v>
       </x:c>
       <x:c r="I58" t="str">
-        <x:v>Señal mediada</x:v>
+        <x:v>Captura</x:v>
       </x:c>
       <x:c r="J58" t="str">
-        <x:v>Decir que planta canta</x:v>
+        <x:v>Cadena completa</x:v>
       </x:c>
       <x:c r="K58" t="str">
-        <x:v>90-160 caracteres</x:v>
+        <x:v>40-90 caracteres</x:v>
       </x:c>
       <x:c r="L58" t="str"/>
       <x:c r="M58" t="str"/>
@@ -2577,37 +2577,37 @@
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="str">
-        <x:v>W2_CONTINUE_BTN_01</x:v>
+        <x:v>W2_CAPTURA_AMB_01</x:v>
       </x:c>
       <x:c r="B59" t="str">
         <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C59" t="str">
-        <x:v>w2_complete</x:v>
+        <x:v>w2_captura_active</x:v>
       </x:c>
       <x:c r="D59" t="str">
-        <x:v>Sistema / interfaz</x:v>
+        <x:v>Ambiente</x:v>
       </x:c>
       <x:c r="E59" t="str">
-        <x:v>Botón</x:v>
+        <x:v>Respuesta ambiental</x:v>
       </x:c>
       <x:c r="F59" t="str">
-        <x:v>Botón continuar habilitado.</x:v>
+        <x:v>Elemento CAPTURA disponible o activo.</x:v>
       </x:c>
       <x:c r="G59" t="str">
-        <x:v>Estación completada.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H59" t="str">
-        <x:v>Avanzar a Mundo III.</x:v>
+        <x:v>Mostrar que el sistema empieza a tomar la señal con cuidado.</x:v>
       </x:c>
       <x:c r="I59" t="str">
-        <x:v>Secuencia</x:v>
+        <x:v>Captura cuidadosa</x:v>
       </x:c>
       <x:c r="J59" t="str">
-        <x:v>Ambigüedad</x:v>
+        <x:v>Apropiación de la planta</x:v>
       </x:c>
       <x:c r="K59" t="str">
-        <x:v>1-4 palabras</x:v>
+        <x:v>50-130 caracteres</x:v>
       </x:c>
       <x:c r="L59" t="str"/>
       <x:c r="M59" t="str"/>
@@ -2618,37 +2618,37 @@
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="str">
-        <x:v>W3_INTRO_LIA_01</x:v>
+        <x:v>W2_CAPTURA_CONFIRM_01</x:v>
       </x:c>
       <x:c r="B60" t="str">
-        <x:v>Estación III — Cuaderno Pixel</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C60" t="str">
-        <x:v>w3_intro</x:v>
+        <x:v>w2_captura_active</x:v>
       </x:c>
       <x:c r="D60" t="str">
         <x:v>Lía</x:v>
       </x:c>
       <x:c r="E60" t="str">
-        <x:v>Entrada</x:v>
+        <x:v>Confirmación breve</x:v>
       </x:c>
       <x:c r="F60" t="str">
-        <x:v>Cuaderno pixel aparece con tres bloques.</x:v>
+        <x:v>Elemento CAPTURA disponible o activo.</x:v>
       </x:c>
       <x:c r="G60" t="str">
-        <x:v>Transición desde Mundo II.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H60" t="str">
-        <x:v>Presentar OKÚA como proceso de pruebas y ajustes.</x:v>
+        <x:v>Confirmar que captar no es inventar una voz.</x:v>
       </x:c>
       <x:c r="I60" t="str">
-        <x:v>Bitácora / prueba / ajuste</x:v>
+        <x:v>Captura / mediación</x:v>
       </x:c>
       <x:c r="J60" t="str">
-        <x:v>Sistema perfecto desde el inicio</x:v>
+        <x:v>Voz falsa de la planta</x:v>
       </x:c>
       <x:c r="K60" t="str">
-        <x:v>90-170 caracteres</x:v>
+        <x:v>50-110 caracteres</x:v>
       </x:c>
       <x:c r="L60" t="str"/>
       <x:c r="M60" t="str"/>
@@ -2659,37 +2659,37 @@
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="str">
-        <x:v>W3_PLANTA_LIA_01</x:v>
+        <x:v>W2_ACONDICIONAMIENTO_HINT_01</x:v>
       </x:c>
       <x:c r="B61" t="str">
-        <x:v>Estación III — Cuaderno Pixel</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C61" t="str">
-        <x:v>w3_planta</x:v>
+        <x:v>w2_acondicionamiento_available</x:v>
       </x:c>
       <x:c r="D61" t="str">
         <x:v>Lía</x:v>
       </x:c>
       <x:c r="E61" t="str">
-        <x:v>Diálogo por bloque</x:v>
+        <x:v>Instrucción contextual</x:v>
       </x:c>
       <x:c r="F61" t="str">
-        <x:v>Bloque del cuaderno activo con checkmark pendiente.</x:v>
+        <x:v>Elemento ACONDICIONAMIENTO disponible o activo.</x:v>
       </x:c>
       <x:c r="G61" t="str">
-        <x:v>Visitante activó el bloque correspondiente.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H61" t="str">
-        <x:v>Observación inicial del fenómeno.</x:v>
+        <x:v>Invitar a activar la capa ACONDICIONAMIENTO.</x:v>
       </x:c>
       <x:c r="I61" t="str">
-        <x:v>Planta</x:v>
+        <x:v>Acondicionamiento</x:v>
       </x:c>
       <x:c r="J61" t="str">
-        <x:v>Minijuego complejo o tecnicismo pesado</x:v>
+        <x:v>Tecnicismo pesado</x:v>
       </x:c>
       <x:c r="K61" t="str">
-        <x:v>80-150 caracteres</x:v>
+        <x:v>40-100 caracteres</x:v>
       </x:c>
       <x:c r="L61" t="str"/>
       <x:c r="M61" t="str"/>
@@ -2700,37 +2700,37 @@
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="str">
-        <x:v>W3_PROTOTIPO_LIA_01</x:v>
+        <x:v>W2_ACONDICIONAMIENTO_AMB_01</x:v>
       </x:c>
       <x:c r="B62" t="str">
-        <x:v>Estación III — Cuaderno Pixel</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C62" t="str">
-        <x:v>w3_prototipo</x:v>
+        <x:v>w2_acondicionamiento_active</x:v>
       </x:c>
       <x:c r="D62" t="str">
-        <x:v>Lía</x:v>
+        <x:v>Ambiente</x:v>
       </x:c>
       <x:c r="E62" t="str">
-        <x:v>Diálogo por bloque</x:v>
+        <x:v>Respuesta ambiental</x:v>
       </x:c>
       <x:c r="F62" t="str">
-        <x:v>Bloque del cuaderno activo con checkmark pendiente.</x:v>
+        <x:v>Elemento ACONDICIONAMIENTO disponible o activo.</x:v>
       </x:c>
       <x:c r="G62" t="str">
-        <x:v>Visitante activó el bloque correspondiente.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H62" t="str">
-        <x:v>Prueba material y aprendizaje.</x:v>
+        <x:v>Indicar que la señal debe prepararse antes de interpretarse.</x:v>
       </x:c>
       <x:c r="I62" t="str">
-        <x:v>Prototipo</x:v>
+        <x:v>Preparación de señal</x:v>
       </x:c>
       <x:c r="J62" t="str">
-        <x:v>Minijuego complejo o tecnicismo pesado</x:v>
+        <x:v>Magia</x:v>
       </x:c>
       <x:c r="K62" t="str">
-        <x:v>80-150 caracteres</x:v>
+        <x:v>50-130 caracteres</x:v>
       </x:c>
       <x:c r="L62" t="str"/>
       <x:c r="M62" t="str"/>
@@ -2741,37 +2741,37 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="str">
-        <x:v>W3_SENAL_LIA_01</x:v>
+        <x:v>W2_ACONDICIONAMIENTO_CONFIRM_01</x:v>
       </x:c>
       <x:c r="B63" t="str">
-        <x:v>Estación III — Cuaderno Pixel</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C63" t="str">
-        <x:v>w3_senal</x:v>
+        <x:v>w2_acondicionamiento_active</x:v>
       </x:c>
       <x:c r="D63" t="str">
         <x:v>Lía</x:v>
       </x:c>
       <x:c r="E63" t="str">
-        <x:v>Diálogo por bloque</x:v>
+        <x:v>Confirmación breve</x:v>
       </x:c>
       <x:c r="F63" t="str">
-        <x:v>Bloque del cuaderno activo con checkmark pendiente.</x:v>
+        <x:v>Elemento ACONDICIONAMIENTO disponible o activo.</x:v>
       </x:c>
       <x:c r="G63" t="str">
-        <x:v>Visitante activó el bloque correspondiente.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H63" t="str">
-        <x:v>Revisión de señales y límites.</x:v>
+        <x:v>Confirmar que preparar la señal evita una lectura directa falsa.</x:v>
       </x:c>
       <x:c r="I63" t="str">
-        <x:v>Señal</x:v>
+        <x:v>Señal preparada</x:v>
       </x:c>
       <x:c r="J63" t="str">
-        <x:v>Minijuego complejo o tecnicismo pesado</x:v>
+        <x:v>Música inmediata</x:v>
       </x:c>
       <x:c r="K63" t="str">
-        <x:v>80-150 caracteres</x:v>
+        <x:v>50-120 caracteres</x:v>
       </x:c>
       <x:c r="L63" t="str"/>
       <x:c r="M63" t="str"/>
@@ -2782,37 +2782,37 @@
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="str">
-        <x:v>W3_AJUSTADO_LIA_01</x:v>
+        <x:v>W2_MAPEO_HINT_01</x:v>
       </x:c>
       <x:c r="B64" t="str">
-        <x:v>Estación III — Cuaderno Pixel</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C64" t="str">
-        <x:v>w3_ajustado</x:v>
+        <x:v>w2_mapeo_available</x:v>
       </x:c>
       <x:c r="D64" t="str">
         <x:v>Lía</x:v>
       </x:c>
       <x:c r="E64" t="str">
-        <x:v>Cierre / sello</x:v>
+        <x:v>Instrucción contextual</x:v>
       </x:c>
       <x:c r="F64" t="str">
-        <x:v>Sello AJUSTADO aparece al completar bloques.</x:v>
+        <x:v>Elemento MAPEO disponible o activo.</x:v>
       </x:c>
       <x:c r="G64" t="str">
-        <x:v>Visitante completó tres bloques.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H64" t="str">
-        <x:v>Expresar que ajustar también es parte del sistema.</x:v>
+        <x:v>Invitar a activar la capa MAPEO.</x:v>
       </x:c>
       <x:c r="I64" t="str">
-        <x:v>Ajuste / mejora</x:v>
+        <x:v>Mapeo</x:v>
       </x:c>
       <x:c r="J64" t="str">
-        <x:v>Triunfalismo absoluto</x:v>
+        <x:v>Traducción mágica</x:v>
       </x:c>
       <x:c r="K64" t="str">
-        <x:v>70-140 caracteres</x:v>
+        <x:v>40-90 caracteres</x:v>
       </x:c>
       <x:c r="L64" t="str"/>
       <x:c r="M64" t="str"/>
@@ -2823,37 +2823,37 @@
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="str">
-        <x:v>W3_LOCKED_01</x:v>
+        <x:v>W2_MAPEO_AMB_01</x:v>
       </x:c>
       <x:c r="B65" t="str">
-        <x:v>Estación III — Cuaderno Pixel</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C65" t="str">
-        <x:v>w3_block_locked</x:v>
+        <x:v>w2_mapeo_active</x:v>
       </x:c>
       <x:c r="D65" t="str">
-        <x:v>Lía o sistema</x:v>
+        <x:v>Ambiente</x:v>
       </x:c>
       <x:c r="E65" t="str">
-        <x:v>Bloqueo suave</x:v>
+        <x:v>Respuesta ambiental</x:v>
       </x:c>
       <x:c r="F65" t="str">
-        <x:v>Bloque tocado fuera de orden.</x:v>
+        <x:v>Elemento MAPEO disponible o activo.</x:v>
       </x:c>
       <x:c r="G65" t="str">
-        <x:v>Toque fuera de secuencia.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H65" t="str">
-        <x:v>Guiar al bloque correcto.</x:v>
+        <x:v>Mostrar que los datos se relacionan con una forma sonora.</x:v>
       </x:c>
       <x:c r="I65" t="str">
-        <x:v>Secuencia de bitácora</x:v>
+        <x:v>Interpretación / mapeo</x:v>
       </x:c>
       <x:c r="J65" t="str">
-        <x:v>Error fuerte</x:v>
+        <x:v>Canto natural</x:v>
       </x:c>
       <x:c r="K65" t="str">
-        <x:v>40-100 caracteres</x:v>
+        <x:v>50-130 caracteres</x:v>
       </x:c>
       <x:c r="L65" t="str"/>
       <x:c r="M65" t="str"/>
@@ -2864,37 +2864,37 @@
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="str">
-        <x:v>W3_CONTINUE_BTN_01</x:v>
+        <x:v>W2_MAPEO_CONFIRM_01</x:v>
       </x:c>
       <x:c r="B66" t="str">
-        <x:v>Estación III — Cuaderno Pixel</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C66" t="str">
-        <x:v>w3_ajustado</x:v>
+        <x:v>w2_mapeo_active</x:v>
       </x:c>
       <x:c r="D66" t="str">
-        <x:v>Sistema / interfaz</x:v>
+        <x:v>Lía</x:v>
       </x:c>
       <x:c r="E66" t="str">
-        <x:v>Botón</x:v>
+        <x:v>Confirmación breve</x:v>
       </x:c>
       <x:c r="F66" t="str">
-        <x:v>Botón continuar habilitado tras sello.</x:v>
+        <x:v>Elemento MAPEO disponible o activo.</x:v>
       </x:c>
       <x:c r="G66" t="str">
-        <x:v>Estación completada.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H66" t="str">
-        <x:v>Avanzar a Mundo IV.</x:v>
+        <x:v>Confirmar que mapear es decidir cómo interpretar datos.</x:v>
       </x:c>
       <x:c r="I66" t="str">
-        <x:v>Secuencia</x:v>
+        <x:v>Interpretación</x:v>
       </x:c>
       <x:c r="J66" t="str">
-        <x:v>Ambigüedad</x:v>
+        <x:v>Equivalencia automática</x:v>
       </x:c>
       <x:c r="K66" t="str">
-        <x:v>1-4 palabras</x:v>
+        <x:v>50-120 caracteres</x:v>
       </x:c>
       <x:c r="L66" t="str"/>
       <x:c r="M66" t="str"/>
@@ -2905,37 +2905,37 @@
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="str">
-        <x:v>W4_INTRO_LIA_01</x:v>
+        <x:v>W2_RESULTADO_HINT_01</x:v>
       </x:c>
       <x:c r="B67" t="str">
-        <x:v>Estación IV — Mesa de Sistema</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C67" t="str">
-        <x:v>w4_intro</x:v>
+        <x:v>w2_resultado_available</x:v>
       </x:c>
       <x:c r="D67" t="str">
         <x:v>Lía</x:v>
       </x:c>
       <x:c r="E67" t="str">
-        <x:v>Entrada</x:v>
+        <x:v>Instrucción contextual</x:v>
       </x:c>
       <x:c r="F67" t="str">
-        <x:v>Mesa técnica con ocho nodos apagados.</x:v>
+        <x:v>Elemento RESULTADO disponible o activo.</x:v>
       </x:c>
       <x:c r="G67" t="str">
-        <x:v>Transición desde Mundo III.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H67" t="str">
-        <x:v>Presentar que ahora se verá la cadena técnica completa.</x:v>
+        <x:v>Invitar a activar RESULTADO MEDIADO.</x:v>
       </x:c>
       <x:c r="I67" t="str">
-        <x:v>Cadena técnica</x:v>
+        <x:v>Resultado mediado</x:v>
       </x:c>
       <x:c r="J67" t="str">
-        <x:v>Poetizar sin precisión</x:v>
+        <x:v>Resultado mágico</x:v>
       </x:c>
       <x:c r="K67" t="str">
-        <x:v>90-170 caracteres</x:v>
+        <x:v>40-100 caracteres</x:v>
       </x:c>
       <x:c r="L67" t="str"/>
       <x:c r="M67" t="str"/>
@@ -2946,37 +2946,37 @@
     </x:row>
     <x:row r="68">
       <x:c r="A68" t="str">
-        <x:v>W4_PLANTA_CARD_01</x:v>
+        <x:v>W2_RESULTADO_AMB_01</x:v>
       </x:c>
       <x:c r="B68" t="str">
-        <x:v>Estación IV — Mesa de Sistema</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C68" t="str">
-        <x:v>w4_planta</x:v>
+        <x:v>w2_resultado_active</x:v>
       </x:c>
       <x:c r="D68" t="str">
-        <x:v>Lía / sistema</x:v>
+        <x:v>Ambiente</x:v>
       </x:c>
       <x:c r="E68" t="str">
-        <x:v>Tarjeta técnica breve</x:v>
+        <x:v>Respuesta ambiental</x:v>
       </x:c>
       <x:c r="F68" t="str">
-        <x:v>Nodo activo sobre mesa técnica.</x:v>
+        <x:v>Elemento RESULTADO disponible o activo.</x:v>
       </x:c>
       <x:c r="G68" t="str">
-        <x:v>Visitante activó el nodo correspondiente.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H68" t="str">
-        <x:v>Origen vivo de la cadena.</x:v>
+        <x:v>Cerrar el recorrido de capas como experiencia sonora mediada.</x:v>
       </x:c>
       <x:c r="I68" t="str">
-        <x:v>Planta</x:v>
+        <x:v>Sonido mediado</x:v>
       </x:c>
       <x:c r="J68" t="str">
-        <x:v>Omitir o renombrar nodo clave</x:v>
+        <x:v>Planta cantante</x:v>
       </x:c>
       <x:c r="K68" t="str">
-        <x:v>70-140 caracteres</x:v>
+        <x:v>60-140 caracteres</x:v>
       </x:c>
       <x:c r="L68" t="str"/>
       <x:c r="M68" t="str"/>
@@ -2987,37 +2987,37 @@
     </x:row>
     <x:row r="69">
       <x:c r="A69" t="str">
-        <x:v>W4_BIONOSIFICADOR_CARD_01</x:v>
+        <x:v>W2_RESULTADO_CONFIRM_01</x:v>
       </x:c>
       <x:c r="B69" t="str">
-        <x:v>Estación IV — Mesa de Sistema</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C69" t="str">
-        <x:v>w4_bionosificador</x:v>
+        <x:v>w2_resultado_active</x:v>
       </x:c>
       <x:c r="D69" t="str">
-        <x:v>Lía / sistema</x:v>
+        <x:v>Lía</x:v>
       </x:c>
       <x:c r="E69" t="str">
-        <x:v>Tarjeta técnica breve</x:v>
+        <x:v>Confirmación breve</x:v>
       </x:c>
       <x:c r="F69" t="str">
-        <x:v>Nodo activo sobre mesa técnica.</x:v>
+        <x:v>Elemento RESULTADO disponible o activo.</x:v>
       </x:c>
       <x:c r="G69" t="str">
-        <x:v>Visitante activó el nodo correspondiente.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H69" t="str">
-        <x:v>Primer nodo de mediación/captura.</x:v>
+        <x:v>Confirmar que el resultado no elimina la mediación.</x:v>
       </x:c>
       <x:c r="I69" t="str">
-        <x:v>Bionosificador</x:v>
+        <x:v>Mediación</x:v>
       </x:c>
       <x:c r="J69" t="str">
-        <x:v>Omitir o renombrar nodo clave</x:v>
+        <x:v>Sonido directo</x:v>
       </x:c>
       <x:c r="K69" t="str">
-        <x:v>70-140 caracteres</x:v>
+        <x:v>50-120 caracteres</x:v>
       </x:c>
       <x:c r="L69" t="str"/>
       <x:c r="M69" t="str"/>
@@ -3028,37 +3028,37 @@
     </x:row>
     <x:row r="70">
       <x:c r="A70" t="str">
-        <x:v>W4_ESP32_CARD_01</x:v>
+        <x:v>W2_LAYER_LOCKED_01</x:v>
       </x:c>
       <x:c r="B70" t="str">
-        <x:v>Estación IV — Mesa de Sistema</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C70" t="str">
-        <x:v>w4_esp32</x:v>
+        <x:v>w2_layer_locked</x:v>
       </x:c>
       <x:c r="D70" t="str">
-        <x:v>Lía / sistema</x:v>
+        <x:v>Lía o sistema</x:v>
       </x:c>
       <x:c r="E70" t="str">
-        <x:v>Tarjeta técnica breve</x:v>
+        <x:v>Bloqueo suave</x:v>
       </x:c>
       <x:c r="F70" t="str">
-        <x:v>Nodo activo sobre mesa técnica.</x:v>
+        <x:v>Elemento fuera de orden no avanza.</x:v>
       </x:c>
       <x:c r="G70" t="str">
-        <x:v>Visitante activó el nodo correspondiente.</x:v>
+        <x:v>Visitante tocó un elemento bloqueado.</x:v>
       </x:c>
       <x:c r="H70" t="str">
-        <x:v>Procesamiento/lectura de control.</x:v>
+        <x:v>Orientar a la capa correcta.</x:v>
       </x:c>
       <x:c r="I70" t="str">
-        <x:v>ESP32</x:v>
+        <x:v>Secuencia por capas</x:v>
       </x:c>
       <x:c r="J70" t="str">
-        <x:v>Omitir o renombrar nodo clave</x:v>
+        <x:v>Regaño técnico</x:v>
       </x:c>
       <x:c r="K70" t="str">
-        <x:v>70-140 caracteres</x:v>
+        <x:v>35-90 caracteres</x:v>
       </x:c>
       <x:c r="L70" t="str"/>
       <x:c r="M70" t="str"/>
@@ -3069,37 +3069,37 @@
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="str">
-        <x:v>W4_MIDI_CARD_01</x:v>
+        <x:v>W2_LAYER_REPEAT_01</x:v>
       </x:c>
       <x:c r="B71" t="str">
-        <x:v>Estación IV — Mesa de Sistema</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C71" t="str">
-        <x:v>w4_midi</x:v>
+        <x:v>w2_layer_locked</x:v>
       </x:c>
       <x:c r="D71" t="str">
-        <x:v>Lía / sistema</x:v>
+        <x:v>Lía o sistema</x:v>
       </x:c>
       <x:c r="E71" t="str">
-        <x:v>Tarjeta técnica breve</x:v>
+        <x:v>Relectura / repetición</x:v>
       </x:c>
       <x:c r="F71" t="str">
-        <x:v>Nodo activo sobre mesa técnica.</x:v>
+        <x:v>Elemento ya revisado recibe nuevo toque.</x:v>
       </x:c>
       <x:c r="G71" t="str">
-        <x:v>Visitante activó el nodo correspondiente.</x:v>
+        <x:v>Visitante repite un elemento completado.</x:v>
       </x:c>
       <x:c r="H71" t="str">
-        <x:v>Lenguaje de control musical/datos.</x:v>
+        <x:v>Indicar que esa capa ya fue leída.</x:v>
       </x:c>
       <x:c r="I71" t="str">
-        <x:v>MIDI</x:v>
+        <x:v>Revisión cuidadosa</x:v>
       </x:c>
       <x:c r="J71" t="str">
-        <x:v>Omitir o renombrar nodo clave</x:v>
+        <x:v>Error técnico</x:v>
       </x:c>
       <x:c r="K71" t="str">
-        <x:v>70-140 caracteres</x:v>
+        <x:v>35-90 caracteres</x:v>
       </x:c>
       <x:c r="L71" t="str"/>
       <x:c r="M71" t="str"/>
@@ -3110,37 +3110,37 @@
     </x:row>
     <x:row r="72">
       <x:c r="A72" t="str">
-        <x:v>W4_WIFI_UDP_CARD_01</x:v>
+        <x:v>W2_COMPLETE_LIA_01</x:v>
       </x:c>
       <x:c r="B72" t="str">
-        <x:v>Estación IV — Mesa de Sistema</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C72" t="str">
-        <x:v>w4_wifi_udp</x:v>
+        <x:v>w2_complete</x:v>
       </x:c>
       <x:c r="D72" t="str">
-        <x:v>Lía / sistema</x:v>
+        <x:v>Lía</x:v>
       </x:c>
       <x:c r="E72" t="str">
-        <x:v>Tarjeta técnica breve</x:v>
+        <x:v>Cierre</x:v>
       </x:c>
       <x:c r="F72" t="str">
-        <x:v>Nodo activo sobre mesa técnica.</x:v>
+        <x:v>Pantalla completa con todos los pasos activados.</x:v>
       </x:c>
       <x:c r="G72" t="str">
-        <x:v>Visitante activó el nodo correspondiente.</x:v>
+        <x:v>Visitante completó la secuencia principal.</x:v>
       </x:c>
       <x:c r="H72" t="str">
-        <x:v>Transmisión en red local.</x:v>
+        <x:v>Preparar paso hacia el cuaderno de pruebas.</x:v>
       </x:c>
       <x:c r="I72" t="str">
-        <x:v>Wi‑Fi/UDP</x:v>
+        <x:v>Señal mediada</x:v>
       </x:c>
       <x:c r="J72" t="str">
-        <x:v>Omitir o renombrar nodo clave</x:v>
+        <x:v>Planta que canta</x:v>
       </x:c>
       <x:c r="K72" t="str">
-        <x:v>70-140 caracteres</x:v>
+        <x:v>80-150 caracteres</x:v>
       </x:c>
       <x:c r="L72" t="str"/>
       <x:c r="M72" t="str"/>
@@ -3151,37 +3151,37 @@
     </x:row>
     <x:row r="73">
       <x:c r="A73" t="str">
-        <x:v>W4_ROUTER_CARD_01</x:v>
+        <x:v>W2_COMPLETE_AMB_01</x:v>
       </x:c>
       <x:c r="B73" t="str">
-        <x:v>Estación IV — Mesa de Sistema</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C73" t="str">
-        <x:v>w4_router</x:v>
+        <x:v>w2_complete</x:v>
       </x:c>
       <x:c r="D73" t="str">
-        <x:v>Lía / sistema</x:v>
+        <x:v>Ambiente</x:v>
       </x:c>
       <x:c r="E73" t="str">
-        <x:v>Tarjeta técnica breve</x:v>
+        <x:v>Cierre ambiental</x:v>
       </x:c>
       <x:c r="F73" t="str">
-        <x:v>Nodo activo sobre mesa técnica.</x:v>
+        <x:v>Pantalla completa con todos los pasos activados.</x:v>
       </x:c>
       <x:c r="G73" t="str">
-        <x:v>Visitante activó el nodo correspondiente.</x:v>
+        <x:v>Visitante completó la secuencia principal.</x:v>
       </x:c>
       <x:c r="H73" t="str">
-        <x:v>Organización de comunicación local.</x:v>
+        <x:v>Cerrar el pulso invisible como capa comprendida.</x:v>
       </x:c>
       <x:c r="I73" t="str">
-        <x:v>Router</x:v>
+        <x:v>Pulso / mediación</x:v>
       </x:c>
       <x:c r="J73" t="str">
-        <x:v>Omitir o renombrar nodo clave</x:v>
+        <x:v>Triunfalismo técnico</x:v>
       </x:c>
       <x:c r="K73" t="str">
-        <x:v>70-140 caracteres</x:v>
+        <x:v>50-120 caracteres</x:v>
       </x:c>
       <x:c r="L73" t="str"/>
       <x:c r="M73" t="str"/>
@@ -3192,37 +3192,37 @@
     </x:row>
     <x:row r="74">
       <x:c r="A74" t="str">
-        <x:v>W4_SISTEMA_CENTRAL_CARD_01</x:v>
+        <x:v>W2_CONTINUE_BTN_01</x:v>
       </x:c>
       <x:c r="B74" t="str">
-        <x:v>Estación IV — Mesa de Sistema</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C74" t="str">
-        <x:v>w4_sistema_central</x:v>
+        <x:v>w2_complete</x:v>
       </x:c>
       <x:c r="D74" t="str">
-        <x:v>Lía / sistema</x:v>
+        <x:v>Sistema / interfaz</x:v>
       </x:c>
       <x:c r="E74" t="str">
-        <x:v>Tarjeta técnica breve</x:v>
+        <x:v>Botón</x:v>
       </x:c>
       <x:c r="F74" t="str">
-        <x:v>Nodo activo sobre mesa técnica.</x:v>
+        <x:v>Botón de avance habilitado.</x:v>
       </x:c>
       <x:c r="G74" t="str">
-        <x:v>Visitante activó el nodo correspondiente.</x:v>
+        <x:v>Pantalla completada.</x:v>
       </x:c>
       <x:c r="H74" t="str">
-        <x:v>Coordinación del montaje.</x:v>
+        <x:v>Avanzar a transición hacia Mundo III.</x:v>
       </x:c>
       <x:c r="I74" t="str">
-        <x:v>Sistema central</x:v>
+        <x:v>Avance secuencial</x:v>
       </x:c>
       <x:c r="J74" t="str">
-        <x:v>Omitir o renombrar nodo clave</x:v>
+        <x:v>Ambigüedad</x:v>
       </x:c>
       <x:c r="K74" t="str">
-        <x:v>70-140 caracteres</x:v>
+        <x:v>1-4 palabras</x:v>
       </x:c>
       <x:c r="L74" t="str"/>
       <x:c r="M74" t="str"/>
@@ -3233,37 +3233,37 @@
     </x:row>
     <x:row r="75">
       <x:c r="A75" t="str">
-        <x:v>W4_SONIDO_CARD_01</x:v>
+        <x:v>W2_ACCESSIBLE_SCENE_01</x:v>
       </x:c>
       <x:c r="B75" t="str">
-        <x:v>Estación IV — Mesa de Sistema</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C75" t="str">
-        <x:v>w4_sonido</x:v>
+        <x:v>w2_intro</x:v>
       </x:c>
       <x:c r="D75" t="str">
-        <x:v>Lía / sistema</x:v>
+        <x:v>Sistema / accesibilidad</x:v>
       </x:c>
       <x:c r="E75" t="str">
-        <x:v>Tarjeta técnica breve</x:v>
+        <x:v>Descripción accesible</x:v>
       </x:c>
       <x:c r="F75" t="str">
-        <x:v>Nodo activo sobre mesa técnica.</x:v>
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
       </x:c>
       <x:c r="G75" t="str">
-        <x:v>Visitante activó el nodo correspondiente.</x:v>
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
       </x:c>
       <x:c r="H75" t="str">
-        <x:v>Resultado sonoro organizado y mediado.</x:v>
+        <x:v>Describir planta, Lía y seis capas inferiores.</x:v>
       </x:c>
       <x:c r="I75" t="str">
-        <x:v>Sonido</x:v>
+        <x:v>Planta, Lía, capas</x:v>
       </x:c>
       <x:c r="J75" t="str">
-        <x:v>Omitir o renombrar nodo clave</x:v>
+        <x:v>Texto excesivo</x:v>
       </x:c>
       <x:c r="K75" t="str">
-        <x:v>70-140 caracteres</x:v>
+        <x:v>90-170 caracteres</x:v>
       </x:c>
       <x:c r="L75" t="str"/>
       <x:c r="M75" t="str"/>
@@ -3274,37 +3274,37 @@
     </x:row>
     <x:row r="76">
       <x:c r="A76" t="str">
-        <x:v>W4_LOCKED_01</x:v>
+        <x:v>W2_ACCESSIBLE_PLANTA_01</x:v>
       </x:c>
       <x:c r="B76" t="str">
-        <x:v>Estación IV — Mesa de Sistema</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C76" t="str">
-        <x:v>w4_node_locked</x:v>
+        <x:v>w2_planta_active</x:v>
       </x:c>
       <x:c r="D76" t="str">
-        <x:v>Sistema / Lía</x:v>
+        <x:v>Sistema / accesibilidad</x:v>
       </x:c>
       <x:c r="E76" t="str">
-        <x:v>Bloqueo suave</x:v>
+        <x:v>Descripción accesible</x:v>
       </x:c>
       <x:c r="F76" t="str">
-        <x:v>Nodo fuera de orden tocado.</x:v>
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
       </x:c>
       <x:c r="G76" t="str">
-        <x:v>Toque fuera de secuencia.</x:v>
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
       </x:c>
       <x:c r="H76" t="str">
-        <x:v>Mantener orden de la cadena.</x:v>
+        <x:v>Describir activación de PLANTA VIVA.</x:v>
       </x:c>
       <x:c r="I76" t="str">
-        <x:v>Cadena técnica ordenada</x:v>
+        <x:v>Planta viva</x:v>
       </x:c>
       <x:c r="J76" t="str">
-        <x:v>Permitir salto conceptual</x:v>
+        <x:v>Adorno</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>40-100 caracteres</x:v>
+        <x:v>70-140 caracteres</x:v>
       </x:c>
       <x:c r="L76" t="str"/>
       <x:c r="M76" t="str"/>
@@ -3315,37 +3315,37 @@
     </x:row>
     <x:row r="77">
       <x:c r="A77" t="str">
-        <x:v>W4_COMPLETE_LIA_01</x:v>
+        <x:v>W2_ACCESSIBLE_SENAL_01</x:v>
       </x:c>
       <x:c r="B77" t="str">
-        <x:v>Estación IV — Mesa de Sistema</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C77" t="str">
-        <x:v>w4_complete</x:v>
+        <x:v>w2_senal_active</x:v>
       </x:c>
       <x:c r="D77" t="str">
-        <x:v>Lía</x:v>
+        <x:v>Sistema / accesibilidad</x:v>
       </x:c>
       <x:c r="E77" t="str">
-        <x:v>Cierre</x:v>
+        <x:v>Descripción accesible</x:v>
       </x:c>
       <x:c r="F77" t="str">
-        <x:v>Los ocho nodos quedan activos.</x:v>
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
       </x:c>
       <x:c r="G77" t="str">
-        <x:v>Usuario completó Sonido.</x:v>
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
       </x:c>
       <x:c r="H77" t="str">
-        <x:v>Cerrar cadena técnica y preparar síntesis espacial.</x:v>
+        <x:v>Describir activación de SEÑAL.</x:v>
       </x:c>
       <x:c r="I77" t="str">
-        <x:v>Mediación técnica completa</x:v>
+        <x:v>Señal bioeléctrica</x:v>
       </x:c>
       <x:c r="J77" t="str">
-        <x:v>Reexplicar todo</x:v>
+        <x:v>Música directa</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>90-160 caracteres</x:v>
+        <x:v>70-140 caracteres</x:v>
       </x:c>
       <x:c r="L77" t="str"/>
       <x:c r="M77" t="str"/>
@@ -3356,37 +3356,37 @@
     </x:row>
     <x:row r="78">
       <x:c r="A78" t="str">
-        <x:v>W4_CONTINUE_BTN_01</x:v>
+        <x:v>W2_ACCESSIBLE_CAPTURA_01</x:v>
       </x:c>
       <x:c r="B78" t="str">
-        <x:v>Estación IV — Mesa de Sistema</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C78" t="str">
-        <x:v>w4_complete</x:v>
+        <x:v>w2_captura_active</x:v>
       </x:c>
       <x:c r="D78" t="str">
-        <x:v>Sistema / interfaz</x:v>
+        <x:v>Sistema / accesibilidad</x:v>
       </x:c>
       <x:c r="E78" t="str">
-        <x:v>Botón</x:v>
+        <x:v>Descripción accesible</x:v>
       </x:c>
       <x:c r="F78" t="str">
-        <x:v>Botón continuar habilitado.</x:v>
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
       </x:c>
       <x:c r="G78" t="str">
-        <x:v>Estación completada.</x:v>
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
       </x:c>
       <x:c r="H78" t="str">
-        <x:v>Avanzar a Mundo V.</x:v>
+        <x:v>Describir activación de CAPTURA.</x:v>
       </x:c>
       <x:c r="I78" t="str">
-        <x:v>Secuencia</x:v>
+        <x:v>Captura</x:v>
       </x:c>
       <x:c r="J78" t="str">
-        <x:v>Ambigüedad</x:v>
+        <x:v>Voz de la planta</x:v>
       </x:c>
       <x:c r="K78" t="str">
-        <x:v>1-4 palabras</x:v>
+        <x:v>70-140 caracteres</x:v>
       </x:c>
       <x:c r="L78" t="str"/>
       <x:c r="M78" t="str"/>
@@ -3397,37 +3397,37 @@
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="str">
-        <x:v>W5_INTRO_LIA_01</x:v>
+        <x:v>W2_ACCESSIBLE_ACONDICIONAMIENTO_01</x:v>
       </x:c>
       <x:c r="B79" t="str">
-        <x:v>Estación V — Mapa del Presente</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C79" t="str">
-        <x:v>w5_intro</x:v>
+        <x:v>w2_acondicionamiento_active</x:v>
       </x:c>
       <x:c r="D79" t="str">
-        <x:v>Lía</x:v>
+        <x:v>Sistema / accesibilidad</x:v>
       </x:c>
       <x:c r="E79" t="str">
-        <x:v>Entrada</x:v>
+        <x:v>Descripción accesible</x:v>
       </x:c>
       <x:c r="F79" t="str">
-        <x:v>Mapa del montaje actual con áreas apagadas.</x:v>
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
       </x:c>
       <x:c r="G79" t="str">
-        <x:v>Transición desde Mundo IV.</x:v>
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
       </x:c>
       <x:c r="H79" t="str">
-        <x:v>Presentar OKÚA como montaje vivo situado.</x:v>
+        <x:v>Describir activación de ACONDICIONAMIENTO.</x:v>
       </x:c>
       <x:c r="I79" t="str">
-        <x:v>Presente / espacio real</x:v>
+        <x:v>Señal preparada</x:v>
       </x:c>
       <x:c r="J79" t="str">
-        <x:v>Repetir cadena técnica</x:v>
+        <x:v>Magia</x:v>
       </x:c>
       <x:c r="K79" t="str">
-        <x:v>90-170 caracteres</x:v>
+        <x:v>70-150 caracteres</x:v>
       </x:c>
       <x:c r="L79" t="str"/>
       <x:c r="M79" t="str"/>
@@ -3438,34 +3438,34 @@
     </x:row>
     <x:row r="80">
       <x:c r="A80" t="str">
-        <x:v>W5_PLANTAS_LIA_01</x:v>
+        <x:v>W2_ACCESSIBLE_MAPEO_01</x:v>
       </x:c>
       <x:c r="B80" t="str">
-        <x:v>Estación V — Mapa del Presente</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C80" t="str">
-        <x:v>w5_plantas</x:v>
+        <x:v>w2_mapeo_active</x:v>
       </x:c>
       <x:c r="D80" t="str">
-        <x:v>Lía / ambiente</x:v>
+        <x:v>Sistema / accesibilidad</x:v>
       </x:c>
       <x:c r="E80" t="str">
-        <x:v>Diálogo por área</x:v>
+        <x:v>Descripción accesible</x:v>
       </x:c>
       <x:c r="F80" t="str">
-        <x:v>Área del mapa se ilumina.</x:v>
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
       </x:c>
       <x:c r="G80" t="str">
-        <x:v>Visitante activó el área correspondiente.</x:v>
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
       </x:c>
       <x:c r="H80" t="str">
-        <x:v>Reconocer origen vivo del montaje.</x:v>
+        <x:v>Describir activación de MAPEO.</x:v>
       </x:c>
       <x:c r="I80" t="str">
-        <x:v>Plantas</x:v>
+        <x:v>Mapeo</x:v>
       </x:c>
       <x:c r="J80" t="str">
-        <x:v>Repetir estación IV o añadir teoría nueva</x:v>
+        <x:v>Traducción literal</x:v>
       </x:c>
       <x:c r="K80" t="str">
         <x:v>70-140 caracteres</x:v>
@@ -3479,37 +3479,37 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81" t="str">
-        <x:v>W5_SISTEMA_LIA_01</x:v>
+        <x:v>W2_ACCESSIBLE_RESULTADO_01</x:v>
       </x:c>
       <x:c r="B81" t="str">
-        <x:v>Estación V — Mapa del Presente</x:v>
+        <x:v>Estación II — Pulso invisible</x:v>
       </x:c>
       <x:c r="C81" t="str">
-        <x:v>w5_sistema</x:v>
+        <x:v>w2_resultado_active</x:v>
       </x:c>
       <x:c r="D81" t="str">
-        <x:v>Lía / ambiente</x:v>
+        <x:v>Sistema / accesibilidad</x:v>
       </x:c>
       <x:c r="E81" t="str">
-        <x:v>Diálogo por área</x:v>
+        <x:v>Descripción accesible</x:v>
       </x:c>
       <x:c r="F81" t="str">
-        <x:v>Área del mapa se ilumina.</x:v>
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
       </x:c>
       <x:c r="G81" t="str">
-        <x:v>Visitante activó el área correspondiente.</x:v>
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
       </x:c>
       <x:c r="H81" t="str">
-        <x:v>Mostrar mediación operando en el presente.</x:v>
+        <x:v>Describir activación de RESULTADO MEDIADO.</x:v>
       </x:c>
       <x:c r="I81" t="str">
-        <x:v>Sistema</x:v>
+        <x:v>Resultado mediado</x:v>
       </x:c>
       <x:c r="J81" t="str">
-        <x:v>Repetir estación IV o añadir teoría nueva</x:v>
+        <x:v>Planta que canta</x:v>
       </x:c>
       <x:c r="K81" t="str">
-        <x:v>70-140 caracteres</x:v>
+        <x:v>70-150 caracteres</x:v>
       </x:c>
       <x:c r="L81" t="str"/>
       <x:c r="M81" t="str"/>
@@ -3520,37 +3520,37 @@
     </x:row>
     <x:row r="82">
       <x:c r="A82" t="str">
-        <x:v>W5_ESPACIO_LIA_01</x:v>
+        <x:v>W3_INTRO_LIA_01</x:v>
       </x:c>
       <x:c r="B82" t="str">
-        <x:v>Estación V — Mapa del Presente</x:v>
+        <x:v>Estación III — Cuaderno Pixel</x:v>
       </x:c>
       <x:c r="C82" t="str">
-        <x:v>w5_espacio</x:v>
+        <x:v>w3_intro</x:v>
       </x:c>
       <x:c r="D82" t="str">
-        <x:v>Lía / ambiente</x:v>
+        <x:v>Lía</x:v>
       </x:c>
       <x:c r="E82" t="str">
-        <x:v>Diálogo por área</x:v>
+        <x:v>Entrada</x:v>
       </x:c>
       <x:c r="F82" t="str">
-        <x:v>Área del mapa se ilumina.</x:v>
+        <x:v>Escena inicial con Lía y elementos principales visibles.</x:v>
       </x:c>
       <x:c r="G82" t="str">
-        <x:v>Visitante activó el área correspondiente.</x:v>
+        <x:v>Ingreso a la pantalla.</x:v>
       </x:c>
       <x:c r="H82" t="str">
-        <x:v>Aterrizar la experiencia en lugar real.</x:v>
+        <x:v>Presentar el cuaderno como memoria de pruebas y ajustes.</x:v>
       </x:c>
       <x:c r="I82" t="str">
-        <x:v>Espacio</x:v>
+        <x:v>Bitácora / pruebas</x:v>
       </x:c>
       <x:c r="J82" t="str">
-        <x:v>Repetir estación IV o añadir teoría nueva</x:v>
+        <x:v>Sistema perfecto</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>70-140 caracteres</x:v>
+        <x:v>90-160 caracteres</x:v>
       </x:c>
       <x:c r="L82" t="str"/>
       <x:c r="M82" t="str"/>
@@ -3561,37 +3561,37 @@
     </x:row>
     <x:row r="83">
       <x:c r="A83" t="str">
-        <x:v>W5_VISITANTE_LIA_01</x:v>
+        <x:v>W3_INTRO_AMB_01</x:v>
       </x:c>
       <x:c r="B83" t="str">
-        <x:v>Estación V — Mapa del Presente</x:v>
+        <x:v>Estación III — Cuaderno Pixel</x:v>
       </x:c>
       <x:c r="C83" t="str">
-        <x:v>w5_visitante</x:v>
+        <x:v>w3_intro</x:v>
       </x:c>
       <x:c r="D83" t="str">
-        <x:v>Lía / ambiente</x:v>
+        <x:v>Ambiente</x:v>
       </x:c>
       <x:c r="E83" t="str">
-        <x:v>Diálogo por área</x:v>
+        <x:v>Texto ambiental</x:v>
       </x:c>
       <x:c r="F83" t="str">
-        <x:v>Área del mapa se ilumina.</x:v>
+        <x:v>Escena inicial con Lía y elementos principales visibles.</x:v>
       </x:c>
       <x:c r="G83" t="str">
-        <x:v>Visitante activó el área correspondiente.</x:v>
+        <x:v>Ingreso a la pantalla.</x:v>
       </x:c>
       <x:c r="H83" t="str">
-        <x:v>Incluir participación del recorrido.</x:v>
+        <x:v>Situar la pantalla como registro, no como laboratorio saturado.</x:v>
       </x:c>
       <x:c r="I83" t="str">
-        <x:v>Visitante</x:v>
+        <x:v>Memoria / registro</x:v>
       </x:c>
       <x:c r="J83" t="str">
-        <x:v>Repetir estación IV o añadir teoría nueva</x:v>
+        <x:v>Saturación técnica</x:v>
       </x:c>
       <x:c r="K83" t="str">
-        <x:v>70-140 caracteres</x:v>
+        <x:v>50-120 caracteres</x:v>
       </x:c>
       <x:c r="L83" t="str"/>
       <x:c r="M83" t="str"/>
@@ -3602,37 +3602,37 @@
     </x:row>
     <x:row r="84">
       <x:c r="A84" t="str">
-        <x:v>W5_LOCKED_01</x:v>
+        <x:v>W3_PLANTA_HINT_01</x:v>
       </x:c>
       <x:c r="B84" t="str">
-        <x:v>Estación V — Mapa del Presente</x:v>
+        <x:v>Estación III — Cuaderno Pixel</x:v>
       </x:c>
       <x:c r="C84" t="str">
-        <x:v>w5_area_locked</x:v>
+        <x:v>w3_planta_available</x:v>
       </x:c>
       <x:c r="D84" t="str">
-        <x:v>Lía o sistema</x:v>
+        <x:v>Lía</x:v>
       </x:c>
       <x:c r="E84" t="str">
-        <x:v>Bloqueo suave</x:v>
+        <x:v>Instrucción contextual</x:v>
       </x:c>
       <x:c r="F84" t="str">
-        <x:v>Área fuera de orden tocada.</x:v>
+        <x:v>Elemento PLANTA disponible o activo.</x:v>
       </x:c>
       <x:c r="G84" t="str">
-        <x:v>Toque fuera de secuencia.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H84" t="str">
-        <x:v>Guiar a la siguiente área.</x:v>
+        <x:v>Invitar a abrir el bloque PLANTA.</x:v>
       </x:c>
       <x:c r="I84" t="str">
-        <x:v>Síntesis ordenada</x:v>
+        <x:v>Observación inicial</x:v>
       </x:c>
       <x:c r="J84" t="str">
-        <x:v>Regaño</x:v>
+        <x:v>Minijuego</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>40-100 caracteres</x:v>
+        <x:v>40-90 caracteres</x:v>
       </x:c>
       <x:c r="L84" t="str"/>
       <x:c r="M84" t="str"/>
@@ -3643,37 +3643,37 @@
     </x:row>
     <x:row r="85">
       <x:c r="A85" t="str">
-        <x:v>W5_COMPLETE_LIA_01</x:v>
+        <x:v>W3_PLANTA_NOTE_01</x:v>
       </x:c>
       <x:c r="B85" t="str">
-        <x:v>Estación V — Mapa del Presente</x:v>
+        <x:v>Estación III — Cuaderno Pixel</x:v>
       </x:c>
       <x:c r="C85" t="str">
-        <x:v>w5_complete</x:v>
+        <x:v>w3_planta_active</x:v>
       </x:c>
       <x:c r="D85" t="str">
-        <x:v>Lía</x:v>
+        <x:v>Cuaderno / ambiente</x:v>
       </x:c>
       <x:c r="E85" t="str">
-        <x:v>Cierre previo</x:v>
+        <x:v>Nota de bitácora</x:v>
       </x:c>
       <x:c r="F85" t="str">
-        <x:v>Mapa completado; botón de cierre activo.</x:v>
+        <x:v>Elemento PLANTA disponible o activo.</x:v>
       </x:c>
       <x:c r="G85" t="str">
-        <x:v>Usuario completó Visitante.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H85" t="str">
-        <x:v>Preparar paso al mirador final.</x:v>
+        <x:v>Mostrar que el proceso comenzó observando una planta viva.</x:v>
       </x:c>
       <x:c r="I85" t="str">
-        <x:v>Cierre del recorrido</x:v>
+        <x:v>Planta / observación</x:v>
       </x:c>
       <x:c r="J85" t="str">
-        <x:v>Introducir estación nueva</x:v>
+        <x:v>Adorno</x:v>
       </x:c>
       <x:c r="K85" t="str">
-        <x:v>90-160 caracteres</x:v>
+        <x:v>60-130 caracteres</x:v>
       </x:c>
       <x:c r="L85" t="str"/>
       <x:c r="M85" t="str"/>
@@ -3684,37 +3684,37 @@
     </x:row>
     <x:row r="86">
       <x:c r="A86" t="str">
-        <x:v>W5_FINAL_BTN_01</x:v>
+        <x:v>W3_PLANTA_CONFIRM_01</x:v>
       </x:c>
       <x:c r="B86" t="str">
-        <x:v>Estación V — Mapa del Presente</x:v>
+        <x:v>Estación III — Cuaderno Pixel</x:v>
       </x:c>
       <x:c r="C86" t="str">
-        <x:v>w5_complete</x:v>
+        <x:v>w3_planta_active</x:v>
       </x:c>
       <x:c r="D86" t="str">
-        <x:v>Sistema / interfaz</x:v>
+        <x:v>Lía</x:v>
       </x:c>
       <x:c r="E86" t="str">
-        <x:v>Botón</x:v>
+        <x:v>Confirmación breve</x:v>
       </x:c>
       <x:c r="F86" t="str">
-        <x:v>Botón Ir al cierre habilitado.</x:v>
+        <x:v>Elemento PLANTA disponible o activo.</x:v>
       </x:c>
       <x:c r="G86" t="str">
-        <x:v>Estación completada.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H86" t="str">
-        <x:v>Abrir transición final.</x:v>
+        <x:v>Confirmar que observar fue el primer dato del desarrollo.</x:v>
       </x:c>
       <x:c r="I86" t="str">
-        <x:v>Cierre</x:v>
+        <x:v>Observación</x:v>
       </x:c>
       <x:c r="J86" t="str">
-        <x:v>Ambigüedad</x:v>
+        <x:v>Conclusión automática</x:v>
       </x:c>
       <x:c r="K86" t="str">
-        <x:v>1-4 palabras</x:v>
+        <x:v>50-110 caracteres</x:v>
       </x:c>
       <x:c r="L86" t="str"/>
       <x:c r="M86" t="str"/>
@@ -3725,37 +3725,37 @@
     </x:row>
     <x:row r="87">
       <x:c r="A87" t="str">
-        <x:v>FINAL_LIA_MESSAGE_01</x:v>
+        <x:v>W3_PROTOTIPO_HINT_01</x:v>
       </x:c>
       <x:c r="B87" t="str">
-        <x:v>Pantalla final — Mirador</x:v>
+        <x:v>Estación III — Cuaderno Pixel</x:v>
       </x:c>
       <x:c r="C87" t="str">
-        <x:v>final_intro</x:v>
+        <x:v>w3_prototipo_available</x:v>
       </x:c>
       <x:c r="D87" t="str">
         <x:v>Lía</x:v>
       </x:c>
       <x:c r="E87" t="str">
-        <x:v>Mensaje final</x:v>
+        <x:v>Instrucción contextual</x:v>
       </x:c>
       <x:c r="F87" t="str">
-        <x:v>Mirador final aparece con accesos a cinco mundos.</x:v>
+        <x:v>Elemento PROTOTIPO disponible o activo.</x:v>
       </x:c>
       <x:c r="G87" t="str">
-        <x:v>Transición final completada.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H87" t="str">
-        <x:v>Confirmar recorrido completo y abrir revisión libre.</x:v>
+        <x:v>Invitar a abrir el bloque PROTOTIPO.</x:v>
       </x:c>
       <x:c r="I87" t="str">
-        <x:v>Cierre / revisión libre</x:v>
+        <x:v>Prototipo</x:v>
       </x:c>
       <x:c r="J87" t="str">
-        <x:v>Nueva teoría</x:v>
+        <x:v>Perfección inicial</x:v>
       </x:c>
       <x:c r="K87" t="str">
-        <x:v>90-170 caracteres</x:v>
+        <x:v>40-90 caracteres</x:v>
       </x:c>
       <x:c r="L87" t="str"/>
       <x:c r="M87" t="str"/>
@@ -3766,37 +3766,37 @@
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="str">
-        <x:v>FINAL_ACCESS_I_LABEL_01</x:v>
+        <x:v>W3_PROTOTIPO_NOTE_01</x:v>
       </x:c>
       <x:c r="B88" t="str">
-        <x:v>Pantalla final — Mirador</x:v>
+        <x:v>Estación III — Cuaderno Pixel</x:v>
       </x:c>
       <x:c r="C88" t="str">
-        <x:v>final_review</x:v>
+        <x:v>w3_prototipo_active</x:v>
       </x:c>
       <x:c r="D88" t="str">
-        <x:v>Sistema / interfaz</x:v>
+        <x:v>Cuaderno / ambiente</x:v>
       </x:c>
       <x:c r="E88" t="str">
-        <x:v>Label de acceso</x:v>
+        <x:v>Nota de bitácora</x:v>
       </x:c>
       <x:c r="F88" t="str">
-        <x:v>Acceso flotante a Mundo I.</x:v>
+        <x:v>Elemento PROTOTIPO disponible o activo.</x:v>
       </x:c>
       <x:c r="G88" t="str">
-        <x:v>Visitante revisa opciones.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H88" t="str">
-        <x:v>Nombrar acceso en revisión libre.</x:v>
+        <x:v>Mostrar que el prototipo permitió probar límites.</x:v>
       </x:c>
       <x:c r="I88" t="str">
-        <x:v>Raíz</x:v>
+        <x:v>Prueba material</x:v>
       </x:c>
       <x:c r="J88" t="str">
-        <x:v>Texto excesivo</x:v>
+        <x:v>Magia técnica</x:v>
       </x:c>
       <x:c r="K88" t="str">
-        <x:v>2-6 palabras</x:v>
+        <x:v>60-130 caracteres</x:v>
       </x:c>
       <x:c r="L88" t="str"/>
       <x:c r="M88" t="str"/>
@@ -3807,37 +3807,37 @@
     </x:row>
     <x:row r="89">
       <x:c r="A89" t="str">
-        <x:v>FINAL_ACCESS_II_LABEL_01</x:v>
+        <x:v>W3_PROTOTIPO_CONFIRM_01</x:v>
       </x:c>
       <x:c r="B89" t="str">
-        <x:v>Pantalla final — Mirador</x:v>
+        <x:v>Estación III — Cuaderno Pixel</x:v>
       </x:c>
       <x:c r="C89" t="str">
-        <x:v>final_review</x:v>
+        <x:v>w3_prototipo_active</x:v>
       </x:c>
       <x:c r="D89" t="str">
-        <x:v>Sistema / interfaz</x:v>
+        <x:v>Lía</x:v>
       </x:c>
       <x:c r="E89" t="str">
-        <x:v>Label de acceso</x:v>
+        <x:v>Confirmación breve</x:v>
       </x:c>
       <x:c r="F89" t="str">
-        <x:v>Acceso flotante a Mundo II.</x:v>
+        <x:v>Elemento PROTOTIPO disponible o activo.</x:v>
       </x:c>
       <x:c r="G89" t="str">
-        <x:v>Visitante revisa opciones.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H89" t="str">
-        <x:v>Nombrar acceso en revisión libre.</x:v>
+        <x:v>Confirmar que probar también es aprender del error.</x:v>
       </x:c>
       <x:c r="I89" t="str">
-        <x:v>Pulso invisible</x:v>
+        <x:v>Prueba / aprendizaje</x:v>
       </x:c>
       <x:c r="J89" t="str">
-        <x:v>Texto excesivo</x:v>
+        <x:v>Fallo como fracaso total</x:v>
       </x:c>
       <x:c r="K89" t="str">
-        <x:v>2-6 palabras</x:v>
+        <x:v>50-110 caracteres</x:v>
       </x:c>
       <x:c r="L89" t="str"/>
       <x:c r="M89" t="str"/>
@@ -3848,37 +3848,37 @@
     </x:row>
     <x:row r="90">
       <x:c r="A90" t="str">
-        <x:v>FINAL_ACCESS_III_LABEL_01</x:v>
+        <x:v>W3_SENAL_HINT_01</x:v>
       </x:c>
       <x:c r="B90" t="str">
-        <x:v>Pantalla final — Mirador</x:v>
+        <x:v>Estación III — Cuaderno Pixel</x:v>
       </x:c>
       <x:c r="C90" t="str">
-        <x:v>final_review</x:v>
+        <x:v>w3_senal_available</x:v>
       </x:c>
       <x:c r="D90" t="str">
-        <x:v>Sistema / interfaz</x:v>
+        <x:v>Lía</x:v>
       </x:c>
       <x:c r="E90" t="str">
-        <x:v>Label de acceso</x:v>
+        <x:v>Instrucción contextual</x:v>
       </x:c>
       <x:c r="F90" t="str">
-        <x:v>Acceso flotante a Mundo III.</x:v>
+        <x:v>Elemento SENAL disponible o activo.</x:v>
       </x:c>
       <x:c r="G90" t="str">
-        <x:v>Visitante revisa opciones.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H90" t="str">
-        <x:v>Nombrar acceso en revisión libre.</x:v>
+        <x:v>Invitar a abrir el bloque SEÑAL.</x:v>
       </x:c>
       <x:c r="I90" t="str">
-        <x:v>Cuaderno de pruebas</x:v>
+        <x:v>Señal revisada</x:v>
       </x:c>
       <x:c r="J90" t="str">
-        <x:v>Texto excesivo</x:v>
+        <x:v>Música directa</x:v>
       </x:c>
       <x:c r="K90" t="str">
-        <x:v>2-6 palabras</x:v>
+        <x:v>40-90 caracteres</x:v>
       </x:c>
       <x:c r="L90" t="str"/>
       <x:c r="M90" t="str"/>
@@ -3889,37 +3889,37 @@
     </x:row>
     <x:row r="91">
       <x:c r="A91" t="str">
-        <x:v>FINAL_ACCESS_IV_LABEL_01</x:v>
+        <x:v>W3_SENAL_NOTE_01</x:v>
       </x:c>
       <x:c r="B91" t="str">
-        <x:v>Pantalla final — Mirador</x:v>
+        <x:v>Estación III — Cuaderno Pixel</x:v>
       </x:c>
       <x:c r="C91" t="str">
-        <x:v>final_review</x:v>
+        <x:v>w3_senal_active</x:v>
       </x:c>
       <x:c r="D91" t="str">
-        <x:v>Sistema / interfaz</x:v>
+        <x:v>Cuaderno / ambiente</x:v>
       </x:c>
       <x:c r="E91" t="str">
-        <x:v>Label de acceso</x:v>
+        <x:v>Nota de bitácora</x:v>
       </x:c>
       <x:c r="F91" t="str">
-        <x:v>Acceso flotante a Mundo IV.</x:v>
+        <x:v>Elemento SENAL disponible o activo.</x:v>
       </x:c>
       <x:c r="G91" t="str">
-        <x:v>Visitante revisa opciones.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H91" t="str">
-        <x:v>Nombrar acceso en revisión libre.</x:v>
+        <x:v>Mostrar que la señal debió revisarse y entenderse.</x:v>
       </x:c>
       <x:c r="I91" t="str">
-        <x:v>Mesa de sistema</x:v>
+        <x:v>Revisión de señal</x:v>
       </x:c>
       <x:c r="J91" t="str">
-        <x:v>Texto excesivo</x:v>
+        <x:v>Señal lista desde el inicio</x:v>
       </x:c>
       <x:c r="K91" t="str">
-        <x:v>2-6 palabras</x:v>
+        <x:v>60-130 caracteres</x:v>
       </x:c>
       <x:c r="L91" t="str"/>
       <x:c r="M91" t="str"/>
@@ -3930,37 +3930,37 @@
     </x:row>
     <x:row r="92">
       <x:c r="A92" t="str">
-        <x:v>FINAL_ACCESS_V_LABEL_01</x:v>
+        <x:v>W3_SENAL_CONFIRM_01</x:v>
       </x:c>
       <x:c r="B92" t="str">
-        <x:v>Pantalla final — Mirador</x:v>
+        <x:v>Estación III — Cuaderno Pixel</x:v>
       </x:c>
       <x:c r="C92" t="str">
-        <x:v>final_review</x:v>
+        <x:v>w3_senal_active</x:v>
       </x:c>
       <x:c r="D92" t="str">
-        <x:v>Sistema / interfaz</x:v>
+        <x:v>Lía</x:v>
       </x:c>
       <x:c r="E92" t="str">
-        <x:v>Label de acceso</x:v>
+        <x:v>Confirmación breve</x:v>
       </x:c>
       <x:c r="F92" t="str">
-        <x:v>Acceso flotante a Mundo V.</x:v>
+        <x:v>Elemento SENAL disponible o activo.</x:v>
       </x:c>
       <x:c r="G92" t="str">
-        <x:v>Visitante revisa opciones.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H92" t="str">
-        <x:v>Nombrar acceso en revisión libre.</x:v>
+        <x:v>Confirmar que la señal también mostró límites.</x:v>
       </x:c>
       <x:c r="I92" t="str">
-        <x:v>Mapa del presente</x:v>
+        <x:v>Límites / revisión</x:v>
       </x:c>
       <x:c r="J92" t="str">
-        <x:v>Texto excesivo</x:v>
+        <x:v>Triunfalismo técnico</x:v>
       </x:c>
       <x:c r="K92" t="str">
-        <x:v>2-6 palabras</x:v>
+        <x:v>50-110 caracteres</x:v>
       </x:c>
       <x:c r="L92" t="str"/>
       <x:c r="M92" t="str"/>
@@ -3971,37 +3971,37 @@
     </x:row>
     <x:row r="93">
       <x:c r="A93" t="str">
-        <x:v>FINAL_HELP_01</x:v>
+        <x:v>W3_AJUSTADO_HINT_01</x:v>
       </x:c>
       <x:c r="B93" t="str">
-        <x:v>Pantalla final — Mirador</x:v>
+        <x:v>Estación III — Cuaderno Pixel</x:v>
       </x:c>
       <x:c r="C93" t="str">
-        <x:v>final_review</x:v>
+        <x:v>w3_ajustado_available</x:v>
       </x:c>
       <x:c r="D93" t="str">
         <x:v>Lía</x:v>
       </x:c>
       <x:c r="E93" t="str">
-        <x:v>Ayuda breve</x:v>
+        <x:v>Instrucción contextual</x:v>
       </x:c>
       <x:c r="F93" t="str">
-        <x:v>Accesos libres visibles.</x:v>
+        <x:v>Elemento AJUSTADO disponible o activo.</x:v>
       </x:c>
       <x:c r="G93" t="str">
-        <x:v>Visitante necesita orientación o permanece en pantalla.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H93" t="str">
-        <x:v>Explicar que puede volver a cualquier mundo.</x:v>
+        <x:v>Invitar a leer o activar el sello AJUSTADO.</x:v>
       </x:c>
       <x:c r="I93" t="str">
-        <x:v>Revisión libre</x:v>
+        <x:v>Ajuste</x:v>
       </x:c>
       <x:c r="J93" t="str">
-        <x:v>Bloqueo innecesario</x:v>
+        <x:v>Final mágico</x:v>
       </x:c>
       <x:c r="K93" t="str">
-        <x:v>60-130 caracteres</x:v>
+        <x:v>40-100 caracteres</x:v>
       </x:c>
       <x:c r="L93" t="str"/>
       <x:c r="M93" t="str"/>
@@ -4012,37 +4012,37 @@
     </x:row>
     <x:row r="94">
       <x:c r="A94" t="str">
-        <x:v>FINAL_BACK_HOME_BTN_01</x:v>
+        <x:v>W3_AJUSTADO_AMB_01</x:v>
       </x:c>
       <x:c r="B94" t="str">
-        <x:v>Pantalla final — Mirador</x:v>
+        <x:v>Estación III — Cuaderno Pixel</x:v>
       </x:c>
       <x:c r="C94" t="str">
-        <x:v>final_return</x:v>
+        <x:v>w3_ajustado_active</x:v>
       </x:c>
       <x:c r="D94" t="str">
-        <x:v>Sistema / interfaz</x:v>
+        <x:v>Cuaderno / ambiente</x:v>
       </x:c>
       <x:c r="E94" t="str">
-        <x:v>Botón</x:v>
+        <x:v>Sello / respuesta</x:v>
       </x:c>
       <x:c r="F94" t="str">
-        <x:v>Botón Volver al inicio visible.</x:v>
+        <x:v>Elemento AJUSTADO disponible o activo.</x:v>
       </x:c>
       <x:c r="G94" t="str">
-        <x:v>Visitante termina recorrido.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H94" t="str">
-        <x:v>Volver a portada o inicio según diseño.</x:v>
+        <x:v>Expresar que ajustar forma parte de construir el sistema.</x:v>
       </x:c>
       <x:c r="I94" t="str">
-        <x:v>Salida clara</x:v>
+        <x:v>Ajuste / mejora</x:v>
       </x:c>
       <x:c r="J94" t="str">
-        <x:v>Confundir con reinicio</x:v>
+        <x:v>Perfección absoluta</x:v>
       </x:c>
       <x:c r="K94" t="str">
-        <x:v>1-4 palabras</x:v>
+        <x:v>60-130 caracteres</x:v>
       </x:c>
       <x:c r="L94" t="str"/>
       <x:c r="M94" t="str"/>
@@ -4053,37 +4053,37 @@
     </x:row>
     <x:row r="95">
       <x:c r="A95" t="str">
-        <x:v>FINAL_RESTART_BTN_01</x:v>
+        <x:v>W3_AJUSTADO_CONFIRM_01</x:v>
       </x:c>
       <x:c r="B95" t="str">
-        <x:v>Pantalla final — Mirador</x:v>
+        <x:v>Estación III — Cuaderno Pixel</x:v>
       </x:c>
       <x:c r="C95" t="str">
-        <x:v>final_restart</x:v>
+        <x:v>w3_ajustado_active</x:v>
       </x:c>
       <x:c r="D95" t="str">
-        <x:v>Sistema / interfaz</x:v>
+        <x:v>Lía</x:v>
       </x:c>
       <x:c r="E95" t="str">
-        <x:v>Botón</x:v>
+        <x:v>Confirmación breve</x:v>
       </x:c>
       <x:c r="F95" t="str">
-        <x:v>Botón Reiniciar recorrido visible.</x:v>
+        <x:v>Elemento AJUSTADO disponible o activo.</x:v>
       </x:c>
       <x:c r="G95" t="str">
-        <x:v>Visitante puede borrar/proponer reinicio.</x:v>
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
       </x:c>
       <x:c r="H95" t="str">
-        <x:v>Iniciar reinicio completo.</x:v>
+        <x:v>Cerrar la idea de iteración: probar, corregir y mejorar.</x:v>
       </x:c>
       <x:c r="I95" t="str">
-        <x:v>Reinicio</x:v>
+        <x:v>Iteración</x:v>
       </x:c>
       <x:c r="J95" t="str">
-        <x:v>Ambigüedad</x:v>
+        <x:v>Todo funcionó primero</x:v>
       </x:c>
       <x:c r="K95" t="str">
-        <x:v>1-4 palabras</x:v>
+        <x:v>60-130 caracteres</x:v>
       </x:c>
       <x:c r="L95" t="str"/>
       <x:c r="M95" t="str"/>
@@ -4094,37 +4094,37 @@
     </x:row>
     <x:row r="96">
       <x:c r="A96" t="str">
-        <x:v>FINAL_RESTART_CONFIRM_01</x:v>
+        <x:v>W3_BLOCK_LOCKED_01</x:v>
       </x:c>
       <x:c r="B96" t="str">
-        <x:v>Pantalla final — Mirador</x:v>
+        <x:v>Estación III — Cuaderno Pixel</x:v>
       </x:c>
       <x:c r="C96" t="str">
-        <x:v>final_restart_confirm</x:v>
+        <x:v>w3_block_locked</x:v>
       </x:c>
       <x:c r="D96" t="str">
-        <x:v>Sistema / interfaz</x:v>
+        <x:v>Lía o sistema</x:v>
       </x:c>
       <x:c r="E96" t="str">
-        <x:v>Confirmación</x:v>
+        <x:v>Bloqueo suave</x:v>
       </x:c>
       <x:c r="F96" t="str">
-        <x:v>Posible confirmación antes de reiniciar.</x:v>
+        <x:v>Elemento fuera de orden no avanza.</x:v>
       </x:c>
       <x:c r="G96" t="str">
-        <x:v>Visitante toca Reiniciar.</x:v>
+        <x:v>Visitante tocó un elemento bloqueado.</x:v>
       </x:c>
       <x:c r="H96" t="str">
-        <x:v>Evitar reinicio accidental.</x:v>
+        <x:v>Guiar al bloque correcto.</x:v>
       </x:c>
       <x:c r="I96" t="str">
-        <x:v>Confirmación clara</x:v>
+        <x:v>Secuencia de bitácora</x:v>
       </x:c>
       <x:c r="J96" t="str">
-        <x:v>Poetizar una acción crítica</x:v>
+        <x:v>Error fuerte</x:v>
       </x:c>
       <x:c r="K96" t="str">
-        <x:v>60-130 caracteres</x:v>
+        <x:v>35-90 caracteres</x:v>
       </x:c>
       <x:c r="L96" t="str"/>
       <x:c r="M96" t="str"/>
@@ -4135,37 +4135,37 @@
     </x:row>
     <x:row r="97">
       <x:c r="A97" t="str">
-        <x:v>FINAL_CREDITS_01</x:v>
+        <x:v>W3_BLOCK_REPEAT_01</x:v>
       </x:c>
       <x:c r="B97" t="str">
-        <x:v>Pantalla final — Mirador</x:v>
+        <x:v>Estación III — Cuaderno Pixel</x:v>
       </x:c>
       <x:c r="C97" t="str">
-        <x:v>final_credits</x:v>
+        <x:v>w3_block_locked</x:v>
       </x:c>
       <x:c r="D97" t="str">
-        <x:v>Sistema / interfaz</x:v>
+        <x:v>Lía o sistema</x:v>
       </x:c>
       <x:c r="E97" t="str">
-        <x:v>Créditos</x:v>
+        <x:v>Relectura / repetición</x:v>
       </x:c>
       <x:c r="F97" t="str">
-        <x:v>Panel de créditos esencial.</x:v>
+        <x:v>Elemento ya revisado recibe nuevo toque.</x:v>
       </x:c>
       <x:c r="G97" t="str">
-        <x:v>Pantalla final visible.</x:v>
+        <x:v>Visitante repite un elemento completado.</x:v>
       </x:c>
       <x:c r="H97" t="str">
-        <x:v>Mostrar autoría mínima y clara.</x:v>
+        <x:v>Indicar que ese bloque ya fue leído.</x:v>
       </x:c>
       <x:c r="I97" t="str">
-        <x:v>Créditos esenciales</x:v>
+        <x:v>Revisión cuidadosa</x:v>
       </x:c>
       <x:c r="J97" t="str">
-        <x:v>Lista larga saturada</x:v>
+        <x:v>Regaño</x:v>
       </x:c>
       <x:c r="K97" t="str">
-        <x:v>Variable</x:v>
+        <x:v>35-90 caracteres</x:v>
       </x:c>
       <x:c r="L97" t="str"/>
       <x:c r="M97" t="str"/>
@@ -4174,6 +4174,4147 @@
         <x:v>Pendiente escritor</x:v>
       </x:c>
     </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str">
+        <x:v>W3_COMPLETE_LIA_01</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>Estación III — Cuaderno Pixel</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>w3_complete</x:v>
+      </x:c>
+      <x:c r="D98" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E98" t="str">
+        <x:v>Cierre</x:v>
+      </x:c>
+      <x:c r="F98" t="str">
+        <x:v>Pantalla completa con todos los pasos activados.</x:v>
+      </x:c>
+      <x:c r="G98" t="str">
+        <x:v>Visitante completó la secuencia principal.</x:v>
+      </x:c>
+      <x:c r="H98" t="str">
+        <x:v>Preparar paso hacia la cadena técnica completa.</x:v>
+      </x:c>
+      <x:c r="I98" t="str">
+        <x:v>Prueba / ajuste</x:v>
+      </x:c>
+      <x:c r="J98" t="str">
+        <x:v>Explicar ocho nodos aquí</x:v>
+      </x:c>
+      <x:c r="K98" t="str">
+        <x:v>80-150 caracteres</x:v>
+      </x:c>
+      <x:c r="L98" t="str"/>
+      <x:c r="M98" t="str"/>
+      <x:c r="N98" t="str"/>
+      <x:c r="O98" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>W3_CONTINUE_BTN_01</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>Estación III — Cuaderno Pixel</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>w3_complete</x:v>
+      </x:c>
+      <x:c r="D99" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E99" t="str">
+        <x:v>Botón</x:v>
+      </x:c>
+      <x:c r="F99" t="str">
+        <x:v>Botón de avance habilitado.</x:v>
+      </x:c>
+      <x:c r="G99" t="str">
+        <x:v>Pantalla completada.</x:v>
+      </x:c>
+      <x:c r="H99" t="str">
+        <x:v>Avanzar a transición hacia Mundo IV.</x:v>
+      </x:c>
+      <x:c r="I99" t="str">
+        <x:v>Avance secuencial</x:v>
+      </x:c>
+      <x:c r="J99" t="str">
+        <x:v>Ambigüedad</x:v>
+      </x:c>
+      <x:c r="K99" t="str">
+        <x:v>1-4 palabras</x:v>
+      </x:c>
+      <x:c r="L99" t="str"/>
+      <x:c r="M99" t="str"/>
+      <x:c r="N99" t="str"/>
+      <x:c r="O99" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str">
+        <x:v>W3_ACCESSIBLE_SCENE_01</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>Estación III — Cuaderno Pixel</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>w3_intro</x:v>
+      </x:c>
+      <x:c r="D100" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E100" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F100" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G100" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H100" t="str">
+        <x:v>Describir cuaderno, Lía, tres bloques y sello.</x:v>
+      </x:c>
+      <x:c r="I100" t="str">
+        <x:v>Cuaderno / bloques</x:v>
+      </x:c>
+      <x:c r="J100" t="str">
+        <x:v>Texto excesivo</x:v>
+      </x:c>
+      <x:c r="K100" t="str">
+        <x:v>90-170 caracteres</x:v>
+      </x:c>
+      <x:c r="L100" t="str"/>
+      <x:c r="M100" t="str"/>
+      <x:c r="N100" t="str"/>
+      <x:c r="O100" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str">
+        <x:v>W3_ACCESSIBLE_PLANTA_01</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>Estación III — Cuaderno Pixel</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>w3_planta_active</x:v>
+      </x:c>
+      <x:c r="D101" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E101" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F101" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G101" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H101" t="str">
+        <x:v>Describir activación de PLANTA.</x:v>
+      </x:c>
+      <x:c r="I101" t="str">
+        <x:v>Planta</x:v>
+      </x:c>
+      <x:c r="J101" t="str">
+        <x:v>Decoración</x:v>
+      </x:c>
+      <x:c r="K101" t="str">
+        <x:v>70-140 caracteres</x:v>
+      </x:c>
+      <x:c r="L101" t="str"/>
+      <x:c r="M101" t="str"/>
+      <x:c r="N101" t="str"/>
+      <x:c r="O101" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="str">
+        <x:v>W3_ACCESSIBLE_PROTOTIPO_01</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>Estación III — Cuaderno Pixel</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>w3_prototipo_active</x:v>
+      </x:c>
+      <x:c r="D102" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E102" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F102" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G102" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H102" t="str">
+        <x:v>Describir activación de PROTOTIPO.</x:v>
+      </x:c>
+      <x:c r="I102" t="str">
+        <x:v>Prototipo</x:v>
+      </x:c>
+      <x:c r="J102" t="str">
+        <x:v>Magia técnica</x:v>
+      </x:c>
+      <x:c r="K102" t="str">
+        <x:v>70-140 caracteres</x:v>
+      </x:c>
+      <x:c r="L102" t="str"/>
+      <x:c r="M102" t="str"/>
+      <x:c r="N102" t="str"/>
+      <x:c r="O102" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>W3_ACCESSIBLE_SENAL_01</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>Estación III — Cuaderno Pixel</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>w3_senal_active</x:v>
+      </x:c>
+      <x:c r="D103" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E103" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F103" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G103" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H103" t="str">
+        <x:v>Describir activación de SEÑAL.</x:v>
+      </x:c>
+      <x:c r="I103" t="str">
+        <x:v>Señal</x:v>
+      </x:c>
+      <x:c r="J103" t="str">
+        <x:v>Música directa</x:v>
+      </x:c>
+      <x:c r="K103" t="str">
+        <x:v>70-140 caracteres</x:v>
+      </x:c>
+      <x:c r="L103" t="str"/>
+      <x:c r="M103" t="str"/>
+      <x:c r="N103" t="str"/>
+      <x:c r="O103" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>W3_ACCESSIBLE_AJUSTADO_01</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>Estación III — Cuaderno Pixel</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>w3_ajustado_active</x:v>
+      </x:c>
+      <x:c r="D104" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E104" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F104" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G104" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H104" t="str">
+        <x:v>Describir aparición o activación del sello AJUSTADO.</x:v>
+      </x:c>
+      <x:c r="I104" t="str">
+        <x:v>Ajuste</x:v>
+      </x:c>
+      <x:c r="J104" t="str">
+        <x:v>Perfección absoluta</x:v>
+      </x:c>
+      <x:c r="K104" t="str">
+        <x:v>70-150 caracteres</x:v>
+      </x:c>
+      <x:c r="L104" t="str"/>
+      <x:c r="M104" t="str"/>
+      <x:c r="N104" t="str"/>
+      <x:c r="O104" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>W4_INTRO_LIA_01</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>w4_intro</x:v>
+      </x:c>
+      <x:c r="D105" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E105" t="str">
+        <x:v>Entrada</x:v>
+      </x:c>
+      <x:c r="F105" t="str">
+        <x:v>Escena inicial con Lía y elementos principales visibles.</x:v>
+      </x:c>
+      <x:c r="G105" t="str">
+        <x:v>Ingreso a la pantalla.</x:v>
+      </x:c>
+      <x:c r="H105" t="str">
+        <x:v>Presentar que ahora se verá la cadena técnica completa.</x:v>
+      </x:c>
+      <x:c r="I105" t="str">
+        <x:v>Cadena técnica</x:v>
+      </x:c>
+      <x:c r="J105" t="str">
+        <x:v>Poetizar sin precisión</x:v>
+      </x:c>
+      <x:c r="K105" t="str">
+        <x:v>90-160 caracteres</x:v>
+      </x:c>
+      <x:c r="L105" t="str"/>
+      <x:c r="M105" t="str"/>
+      <x:c r="N105" t="str"/>
+      <x:c r="O105" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>W4_INTRO_SYS_01</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>w4_intro</x:v>
+      </x:c>
+      <x:c r="D106" t="str">
+        <x:v>Sistema / ambiente</x:v>
+      </x:c>
+      <x:c r="E106" t="str">
+        <x:v>Texto de orientación</x:v>
+      </x:c>
+      <x:c r="F106" t="str">
+        <x:v>Escena inicial con Lía y elementos principales visibles.</x:v>
+      </x:c>
+      <x:c r="G106" t="str">
+        <x:v>Ingreso a la pantalla.</x:v>
+      </x:c>
+      <x:c r="H106" t="str">
+        <x:v>Situar la mesa como sistema conectado y ordenado.</x:v>
+      </x:c>
+      <x:c r="I106" t="str">
+        <x:v>Sistema conectado</x:v>
+      </x:c>
+      <x:c r="J106" t="str">
+        <x:v>Saturación técnica</x:v>
+      </x:c>
+      <x:c r="K106" t="str">
+        <x:v>50-120 caracteres</x:v>
+      </x:c>
+      <x:c r="L106" t="str"/>
+      <x:c r="M106" t="str"/>
+      <x:c r="N106" t="str"/>
+      <x:c r="O106" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="str">
+        <x:v>W4_PLANTA_HINT_01</x:v>
+      </x:c>
+      <x:c r="B107" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C107" t="str">
+        <x:v>w4_planta_available</x:v>
+      </x:c>
+      <x:c r="D107" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E107" t="str">
+        <x:v>Instrucción contextual</x:v>
+      </x:c>
+      <x:c r="F107" t="str">
+        <x:v>Elemento PLANTA disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G107" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H107" t="str">
+        <x:v>Invitar a activar el nodo PLANTA.</x:v>
+      </x:c>
+      <x:c r="I107" t="str">
+        <x:v>Planta como origen</x:v>
+      </x:c>
+      <x:c r="J107" t="str">
+        <x:v>Empezar en la máquina</x:v>
+      </x:c>
+      <x:c r="K107" t="str">
+        <x:v>40-90 caracteres</x:v>
+      </x:c>
+      <x:c r="L107" t="str"/>
+      <x:c r="M107" t="str"/>
+      <x:c r="N107" t="str"/>
+      <x:c r="O107" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="str">
+        <x:v>W4_PLANTA_CARD_01</x:v>
+      </x:c>
+      <x:c r="B108" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C108" t="str">
+        <x:v>w4_planta_active</x:v>
+      </x:c>
+      <x:c r="D108" t="str">
+        <x:v>Lía / sistema</x:v>
+      </x:c>
+      <x:c r="E108" t="str">
+        <x:v>Tarjeta técnica breve</x:v>
+      </x:c>
+      <x:c r="F108" t="str">
+        <x:v>Elemento PLANTA disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G108" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H108" t="str">
+        <x:v>Explicar la planta como origen vivo de la cadena.</x:v>
+      </x:c>
+      <x:c r="I108" t="str">
+        <x:v>Planta</x:v>
+      </x:c>
+      <x:c r="J108" t="str">
+        <x:v>Adorno</x:v>
+      </x:c>
+      <x:c r="K108" t="str">
+        <x:v>70-140 caracteres</x:v>
+      </x:c>
+      <x:c r="L108" t="str"/>
+      <x:c r="M108" t="str"/>
+      <x:c r="N108" t="str"/>
+      <x:c r="O108" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" t="str">
+        <x:v>W4_PLANTA_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B109" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C109" t="str">
+        <x:v>w4_planta_active</x:v>
+      </x:c>
+      <x:c r="D109" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E109" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F109" t="str">
+        <x:v>Elemento PLANTA disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G109" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H109" t="str">
+        <x:v>Confirmar que todo parte de la planta, no del sonido.</x:v>
+      </x:c>
+      <x:c r="I109" t="str">
+        <x:v>Origen vivo</x:v>
+      </x:c>
+      <x:c r="J109" t="str">
+        <x:v>Sonido directo</x:v>
+      </x:c>
+      <x:c r="K109" t="str">
+        <x:v>40-100 caracteres</x:v>
+      </x:c>
+      <x:c r="L109" t="str"/>
+      <x:c r="M109" t="str"/>
+      <x:c r="N109" t="str"/>
+      <x:c r="O109" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" t="str">
+        <x:v>W4_BIONOSIFICADOR_HINT_01</x:v>
+      </x:c>
+      <x:c r="B110" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C110" t="str">
+        <x:v>w4_bionosificador_available</x:v>
+      </x:c>
+      <x:c r="D110" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E110" t="str">
+        <x:v>Instrucción contextual</x:v>
+      </x:c>
+      <x:c r="F110" t="str">
+        <x:v>Elemento BIONOSIFICADOR disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G110" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H110" t="str">
+        <x:v>Invitar a activar BIONOSIFICADOR.</x:v>
+      </x:c>
+      <x:c r="I110" t="str">
+        <x:v>Bionosificador</x:v>
+      </x:c>
+      <x:c r="J110" t="str">
+        <x:v>Sensor genérico</x:v>
+      </x:c>
+      <x:c r="K110" t="str">
+        <x:v>40-100 caracteres</x:v>
+      </x:c>
+      <x:c r="L110" t="str"/>
+      <x:c r="M110" t="str"/>
+      <x:c r="N110" t="str"/>
+      <x:c r="O110" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" t="str">
+        <x:v>W4_BIONOSIFICADOR_CARD_01</x:v>
+      </x:c>
+      <x:c r="B111" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C111" t="str">
+        <x:v>w4_bionosificador_active</x:v>
+      </x:c>
+      <x:c r="D111" t="str">
+        <x:v>Lía / sistema</x:v>
+      </x:c>
+      <x:c r="E111" t="str">
+        <x:v>Tarjeta técnica breve</x:v>
+      </x:c>
+      <x:c r="F111" t="str">
+        <x:v>Elemento BIONOSIFICADOR disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G111" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H111" t="str">
+        <x:v>Explicar captura/acondicionamiento inicial de la señal.</x:v>
+      </x:c>
+      <x:c r="I111" t="str">
+        <x:v>Bionosificador</x:v>
+      </x:c>
+      <x:c r="J111" t="str">
+        <x:v>Renombrarlo u omitirlo</x:v>
+      </x:c>
+      <x:c r="K111" t="str">
+        <x:v>70-150 caracteres</x:v>
+      </x:c>
+      <x:c r="L111" t="str"/>
+      <x:c r="M111" t="str"/>
+      <x:c r="N111" t="str"/>
+      <x:c r="O111" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" t="str">
+        <x:v>W4_BIONOSIFICADOR_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B112" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C112" t="str">
+        <x:v>w4_bionosificador_active</x:v>
+      </x:c>
+      <x:c r="D112" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E112" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F112" t="str">
+        <x:v>Elemento BIONOSIFICADOR disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G112" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H112" t="str">
+        <x:v>Confirmar que este nodo inicia la mediación técnica.</x:v>
+      </x:c>
+      <x:c r="I112" t="str">
+        <x:v>Mediación técnica</x:v>
+      </x:c>
+      <x:c r="J112" t="str">
+        <x:v>Magia</x:v>
+      </x:c>
+      <x:c r="K112" t="str">
+        <x:v>50-110 caracteres</x:v>
+      </x:c>
+      <x:c r="L112" t="str"/>
+      <x:c r="M112" t="str"/>
+      <x:c r="N112" t="str"/>
+      <x:c r="O112" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="str">
+        <x:v>W4_ESP32_HINT_01</x:v>
+      </x:c>
+      <x:c r="B113" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C113" t="str">
+        <x:v>w4_esp32_available</x:v>
+      </x:c>
+      <x:c r="D113" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E113" t="str">
+        <x:v>Instrucción contextual</x:v>
+      </x:c>
+      <x:c r="F113" t="str">
+        <x:v>Elemento ESP32 disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G113" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H113" t="str">
+        <x:v>Invitar a activar ESP32.</x:v>
+      </x:c>
+      <x:c r="I113" t="str">
+        <x:v>ESP32</x:v>
+      </x:c>
+      <x:c r="J113" t="str">
+        <x:v>Ocultar nodo clave</x:v>
+      </x:c>
+      <x:c r="K113" t="str">
+        <x:v>40-90 caracteres</x:v>
+      </x:c>
+      <x:c r="L113" t="str"/>
+      <x:c r="M113" t="str"/>
+      <x:c r="N113" t="str"/>
+      <x:c r="O113" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="str">
+        <x:v>W4_ESP32_CARD_01</x:v>
+      </x:c>
+      <x:c r="B114" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C114" t="str">
+        <x:v>w4_esp32_active</x:v>
+      </x:c>
+      <x:c r="D114" t="str">
+        <x:v>Lía / sistema</x:v>
+      </x:c>
+      <x:c r="E114" t="str">
+        <x:v>Tarjeta técnica breve</x:v>
+      </x:c>
+      <x:c r="F114" t="str">
+        <x:v>Elemento ESP32 disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G114" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H114" t="str">
+        <x:v>Explicar el ESP32 como nodo de lectura/control.</x:v>
+      </x:c>
+      <x:c r="I114" t="str">
+        <x:v>ESP32</x:v>
+      </x:c>
+      <x:c r="J114" t="str">
+        <x:v>Confundir con sonido final</x:v>
+      </x:c>
+      <x:c r="K114" t="str">
+        <x:v>70-140 caracteres</x:v>
+      </x:c>
+      <x:c r="L114" t="str"/>
+      <x:c r="M114" t="str"/>
+      <x:c r="N114" t="str"/>
+      <x:c r="O114" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="str">
+        <x:v>W4_ESP32_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C115" t="str">
+        <x:v>w4_esp32_active</x:v>
+      </x:c>
+      <x:c r="D115" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E115" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F115" t="str">
+        <x:v>Elemento ESP32 disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G115" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H115" t="str">
+        <x:v>Confirmar que el dato necesita organización.</x:v>
+      </x:c>
+      <x:c r="I115" t="str">
+        <x:v>Lectura/control</x:v>
+      </x:c>
+      <x:c r="J115" t="str">
+        <x:v>Automatismo mágico</x:v>
+      </x:c>
+      <x:c r="K115" t="str">
+        <x:v>40-100 caracteres</x:v>
+      </x:c>
+      <x:c r="L115" t="str"/>
+      <x:c r="M115" t="str"/>
+      <x:c r="N115" t="str"/>
+      <x:c r="O115" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="str">
+        <x:v>W4_MIDI_HINT_01</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>w4_midi_available</x:v>
+      </x:c>
+      <x:c r="D116" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E116" t="str">
+        <x:v>Instrucción contextual</x:v>
+      </x:c>
+      <x:c r="F116" t="str">
+        <x:v>Elemento MIDI disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G116" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H116" t="str">
+        <x:v>Invitar a activar MIDI.</x:v>
+      </x:c>
+      <x:c r="I116" t="str">
+        <x:v>MIDI</x:v>
+      </x:c>
+      <x:c r="J116" t="str">
+        <x:v>Audio directo</x:v>
+      </x:c>
+      <x:c r="K116" t="str">
+        <x:v>40-90 caracteres</x:v>
+      </x:c>
+      <x:c r="L116" t="str"/>
+      <x:c r="M116" t="str"/>
+      <x:c r="N116" t="str"/>
+      <x:c r="O116" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="str">
+        <x:v>W4_MIDI_CARD_01</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C117" t="str">
+        <x:v>w4_midi_active</x:v>
+      </x:c>
+      <x:c r="D117" t="str">
+        <x:v>Lía / sistema</x:v>
+      </x:c>
+      <x:c r="E117" t="str">
+        <x:v>Tarjeta técnica breve</x:v>
+      </x:c>
+      <x:c r="F117" t="str">
+        <x:v>Elemento MIDI disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G117" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H117" t="str">
+        <x:v>Explicar MIDI como lenguaje de control/eventos musicales.</x:v>
+      </x:c>
+      <x:c r="I117" t="str">
+        <x:v>MIDI</x:v>
+      </x:c>
+      <x:c r="J117" t="str">
+        <x:v>Confundir con sonido físico</x:v>
+      </x:c>
+      <x:c r="K117" t="str">
+        <x:v>70-150 caracteres</x:v>
+      </x:c>
+      <x:c r="L117" t="str"/>
+      <x:c r="M117" t="str"/>
+      <x:c r="N117" t="str"/>
+      <x:c r="O117" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="str">
+        <x:v>W4_MIDI_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>w4_midi_active</x:v>
+      </x:c>
+      <x:c r="D118" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E118" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F118" t="str">
+        <x:v>Elemento MIDI disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G118" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H118" t="str">
+        <x:v>Confirmar que MIDI organiza eventos, no es la planta cantando.</x:v>
+      </x:c>
+      <x:c r="I118" t="str">
+        <x:v>Control musical</x:v>
+      </x:c>
+      <x:c r="J118" t="str">
+        <x:v>Planta cantante</x:v>
+      </x:c>
+      <x:c r="K118" t="str">
+        <x:v>50-120 caracteres</x:v>
+      </x:c>
+      <x:c r="L118" t="str"/>
+      <x:c r="M118" t="str"/>
+      <x:c r="N118" t="str"/>
+      <x:c r="O118" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="str">
+        <x:v>W4_WIFI_UDP_HINT_01</x:v>
+      </x:c>
+      <x:c r="B119" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C119" t="str">
+        <x:v>w4_wifi_udp_available</x:v>
+      </x:c>
+      <x:c r="D119" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E119" t="str">
+        <x:v>Instrucción contextual</x:v>
+      </x:c>
+      <x:c r="F119" t="str">
+        <x:v>Elemento WIFI disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G119" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H119" t="str">
+        <x:v>Invitar a activar Wi‑Fi/UDP.</x:v>
+      </x:c>
+      <x:c r="I119" t="str">
+        <x:v>Wi‑Fi/UDP</x:v>
+      </x:c>
+      <x:c r="J119" t="str">
+        <x:v>Internet externo</x:v>
+      </x:c>
+      <x:c r="K119" t="str">
+        <x:v>40-100 caracteres</x:v>
+      </x:c>
+      <x:c r="L119" t="str"/>
+      <x:c r="M119" t="str"/>
+      <x:c r="N119" t="str"/>
+      <x:c r="O119" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str">
+        <x:v>W4_WIFI_UDP_CARD_01</x:v>
+      </x:c>
+      <x:c r="B120" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C120" t="str">
+        <x:v>w4_wifi_udp_active</x:v>
+      </x:c>
+      <x:c r="D120" t="str">
+        <x:v>Lía / sistema</x:v>
+      </x:c>
+      <x:c r="E120" t="str">
+        <x:v>Tarjeta técnica breve</x:v>
+      </x:c>
+      <x:c r="F120" t="str">
+        <x:v>Elemento WIFI disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G120" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H120" t="str">
+        <x:v>Explicar transmisión local de datos por red.</x:v>
+      </x:c>
+      <x:c r="I120" t="str">
+        <x:v>Red local / UDP</x:v>
+      </x:c>
+      <x:c r="J120" t="str">
+        <x:v>Prometer Internet</x:v>
+      </x:c>
+      <x:c r="K120" t="str">
+        <x:v>70-150 caracteres</x:v>
+      </x:c>
+      <x:c r="L120" t="str"/>
+      <x:c r="M120" t="str"/>
+      <x:c r="N120" t="str"/>
+      <x:c r="O120" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>W4_WIFI_UDP_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>w4_wifi_udp_active</x:v>
+      </x:c>
+      <x:c r="D121" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E121" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F121" t="str">
+        <x:v>Elemento WIFI disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G121" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H121" t="str">
+        <x:v>Confirmar que los datos viajan dentro del montaje.</x:v>
+      </x:c>
+      <x:c r="I121" t="str">
+        <x:v>Comunicación local</x:v>
+      </x:c>
+      <x:c r="J121" t="str">
+        <x:v>Nube/API externa</x:v>
+      </x:c>
+      <x:c r="K121" t="str">
+        <x:v>50-110 caracteres</x:v>
+      </x:c>
+      <x:c r="L121" t="str"/>
+      <x:c r="M121" t="str"/>
+      <x:c r="N121" t="str"/>
+      <x:c r="O121" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="str">
+        <x:v>W4_ROUTER_HINT_01</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>w4_router_available</x:v>
+      </x:c>
+      <x:c r="D122" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E122" t="str">
+        <x:v>Instrucción contextual</x:v>
+      </x:c>
+      <x:c r="F122" t="str">
+        <x:v>Elemento ROUTER disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G122" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H122" t="str">
+        <x:v>Invitar a activar ROUTER.</x:v>
+      </x:c>
+      <x:c r="I122" t="str">
+        <x:v>Router</x:v>
+      </x:c>
+      <x:c r="J122" t="str">
+        <x:v>Internet como requisito</x:v>
+      </x:c>
+      <x:c r="K122" t="str">
+        <x:v>40-90 caracteres</x:v>
+      </x:c>
+      <x:c r="L122" t="str"/>
+      <x:c r="M122" t="str"/>
+      <x:c r="N122" t="str"/>
+      <x:c r="O122" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="str">
+        <x:v>W4_ROUTER_CARD_01</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>w4_router_active</x:v>
+      </x:c>
+      <x:c r="D123" t="str">
+        <x:v>Lía / sistema</x:v>
+      </x:c>
+      <x:c r="E123" t="str">
+        <x:v>Tarjeta técnica breve</x:v>
+      </x:c>
+      <x:c r="F123" t="str">
+        <x:v>Elemento ROUTER disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G123" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H123" t="str">
+        <x:v>Explicar el router como organizador de comunicación local.</x:v>
+      </x:c>
+      <x:c r="I123" t="str">
+        <x:v>Router</x:v>
+      </x:c>
+      <x:c r="J123" t="str">
+        <x:v>Acceso externo</x:v>
+      </x:c>
+      <x:c r="K123" t="str">
+        <x:v>70-150 caracteres</x:v>
+      </x:c>
+      <x:c r="L123" t="str"/>
+      <x:c r="M123" t="str"/>
+      <x:c r="N123" t="str"/>
+      <x:c r="O123" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="str">
+        <x:v>W4_ROUTER_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>w4_router_active</x:v>
+      </x:c>
+      <x:c r="D124" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E124" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F124" t="str">
+        <x:v>Elemento ROUTER disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G124" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H124" t="str">
+        <x:v>Confirmar que la red mantiene ordenado el intercambio.</x:v>
+      </x:c>
+      <x:c r="I124" t="str">
+        <x:v>Red ordenada</x:v>
+      </x:c>
+      <x:c r="J124" t="str">
+        <x:v>Red mágica</x:v>
+      </x:c>
+      <x:c r="K124" t="str">
+        <x:v>50-110 caracteres</x:v>
+      </x:c>
+      <x:c r="L124" t="str"/>
+      <x:c r="M124" t="str"/>
+      <x:c r="N124" t="str"/>
+      <x:c r="O124" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="str">
+        <x:v>W4_SISTEMA_CENTRAL_HINT_01</x:v>
+      </x:c>
+      <x:c r="B125" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C125" t="str">
+        <x:v>w4_sistema_central_available</x:v>
+      </x:c>
+      <x:c r="D125" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E125" t="str">
+        <x:v>Instrucción contextual</x:v>
+      </x:c>
+      <x:c r="F125" t="str">
+        <x:v>Elemento SISTEMA disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G125" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H125" t="str">
+        <x:v>Invitar a activar SISTEMA CENTRAL.</x:v>
+      </x:c>
+      <x:c r="I125" t="str">
+        <x:v>Sistema central</x:v>
+      </x:c>
+      <x:c r="J125" t="str">
+        <x:v>Omitir coordinación</x:v>
+      </x:c>
+      <x:c r="K125" t="str">
+        <x:v>40-100 caracteres</x:v>
+      </x:c>
+      <x:c r="L125" t="str"/>
+      <x:c r="M125" t="str"/>
+      <x:c r="N125" t="str"/>
+      <x:c r="O125" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="str">
+        <x:v>W4_SISTEMA_CENTRAL_CARD_01</x:v>
+      </x:c>
+      <x:c r="B126" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>w4_sistema_central_active</x:v>
+      </x:c>
+      <x:c r="D126" t="str">
+        <x:v>Lía / sistema</x:v>
+      </x:c>
+      <x:c r="E126" t="str">
+        <x:v>Tarjeta técnica breve</x:v>
+      </x:c>
+      <x:c r="F126" t="str">
+        <x:v>Elemento SISTEMA disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G126" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H126" t="str">
+        <x:v>Explicar recepción, coordinación y organización del montaje.</x:v>
+      </x:c>
+      <x:c r="I126" t="str">
+        <x:v>Sistema central</x:v>
+      </x:c>
+      <x:c r="J126" t="str">
+        <x:v>Caja negra mágica</x:v>
+      </x:c>
+      <x:c r="K126" t="str">
+        <x:v>70-150 caracteres</x:v>
+      </x:c>
+      <x:c r="L126" t="str"/>
+      <x:c r="M126" t="str"/>
+      <x:c r="N126" t="str"/>
+      <x:c r="O126" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="str">
+        <x:v>W4_SISTEMA_CENTRAL_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B127" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>w4_sistema_central_active</x:v>
+      </x:c>
+      <x:c r="D127" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E127" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F127" t="str">
+        <x:v>Elemento SISTEMA disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G127" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H127" t="str">
+        <x:v>Confirmar que el sistema reúne lo que la red transporta.</x:v>
+      </x:c>
+      <x:c r="I127" t="str">
+        <x:v>Coordinación</x:v>
+      </x:c>
+      <x:c r="J127" t="str">
+        <x:v>Salto directo al sonido</x:v>
+      </x:c>
+      <x:c r="K127" t="str">
+        <x:v>50-120 caracteres</x:v>
+      </x:c>
+      <x:c r="L127" t="str"/>
+      <x:c r="M127" t="str"/>
+      <x:c r="N127" t="str"/>
+      <x:c r="O127" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="str">
+        <x:v>W4_SONIDO_HINT_01</x:v>
+      </x:c>
+      <x:c r="B128" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>w4_sonido_available</x:v>
+      </x:c>
+      <x:c r="D128" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E128" t="str">
+        <x:v>Instrucción contextual</x:v>
+      </x:c>
+      <x:c r="F128" t="str">
+        <x:v>Elemento SONIDO disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G128" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H128" t="str">
+        <x:v>Invitar a activar SONIDO.</x:v>
+      </x:c>
+      <x:c r="I128" t="str">
+        <x:v>Sonido mediado</x:v>
+      </x:c>
+      <x:c r="J128" t="str">
+        <x:v>Planta emite sonido</x:v>
+      </x:c>
+      <x:c r="K128" t="str">
+        <x:v>40-90 caracteres</x:v>
+      </x:c>
+      <x:c r="L128" t="str"/>
+      <x:c r="M128" t="str"/>
+      <x:c r="N128" t="str"/>
+      <x:c r="O128" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="str">
+        <x:v>W4_SONIDO_CARD_01</x:v>
+      </x:c>
+      <x:c r="B129" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>w4_sonido_active</x:v>
+      </x:c>
+      <x:c r="D129" t="str">
+        <x:v>Lía / sistema</x:v>
+      </x:c>
+      <x:c r="E129" t="str">
+        <x:v>Tarjeta técnica breve</x:v>
+      </x:c>
+      <x:c r="F129" t="str">
+        <x:v>Elemento SONIDO disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G129" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H129" t="str">
+        <x:v>Explicar el sonido como resultado organizado y mediado.</x:v>
+      </x:c>
+      <x:c r="I129" t="str">
+        <x:v>Resultado sonoro mediado</x:v>
+      </x:c>
+      <x:c r="J129" t="str">
+        <x:v>Música directa de planta</x:v>
+      </x:c>
+      <x:c r="K129" t="str">
+        <x:v>70-150 caracteres</x:v>
+      </x:c>
+      <x:c r="L129" t="str"/>
+      <x:c r="M129" t="str"/>
+      <x:c r="N129" t="str"/>
+      <x:c r="O129" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="str">
+        <x:v>W4_SONIDO_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B130" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>w4_sonido_active</x:v>
+      </x:c>
+      <x:c r="D130" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E130" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F130" t="str">
+        <x:v>Elemento SONIDO disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G130" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H130" t="str">
+        <x:v>Confirmar que el resultado depende de toda la cadena.</x:v>
+      </x:c>
+      <x:c r="I130" t="str">
+        <x:v>Cadena completa</x:v>
+      </x:c>
+      <x:c r="J130" t="str">
+        <x:v>Salto mágico</x:v>
+      </x:c>
+      <x:c r="K130" t="str">
+        <x:v>50-120 caracteres</x:v>
+      </x:c>
+      <x:c r="L130" t="str"/>
+      <x:c r="M130" t="str"/>
+      <x:c r="N130" t="str"/>
+      <x:c r="O130" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="str">
+        <x:v>W4_NODE_LOCKED_01</x:v>
+      </x:c>
+      <x:c r="B131" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>w4_node_locked</x:v>
+      </x:c>
+      <x:c r="D131" t="str">
+        <x:v>Sistema / Lía</x:v>
+      </x:c>
+      <x:c r="E131" t="str">
+        <x:v>Bloqueo suave</x:v>
+      </x:c>
+      <x:c r="F131" t="str">
+        <x:v>Elemento fuera de orden no avanza.</x:v>
+      </x:c>
+      <x:c r="G131" t="str">
+        <x:v>Visitante tocó un elemento bloqueado.</x:v>
+      </x:c>
+      <x:c r="H131" t="str">
+        <x:v>Mantener el orden de la cadena.</x:v>
+      </x:c>
+      <x:c r="I131" t="str">
+        <x:v>Cadena técnica ordenada</x:v>
+      </x:c>
+      <x:c r="J131" t="str">
+        <x:v>Regaño</x:v>
+      </x:c>
+      <x:c r="K131" t="str">
+        <x:v>35-90 caracteres</x:v>
+      </x:c>
+      <x:c r="L131" t="str"/>
+      <x:c r="M131" t="str"/>
+      <x:c r="N131" t="str"/>
+      <x:c r="O131" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="str">
+        <x:v>W4_NODE_REPEAT_01</x:v>
+      </x:c>
+      <x:c r="B132" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C132" t="str">
+        <x:v>w4_node_locked</x:v>
+      </x:c>
+      <x:c r="D132" t="str">
+        <x:v>Sistema / Lía</x:v>
+      </x:c>
+      <x:c r="E132" t="str">
+        <x:v>Relectura / repetición</x:v>
+      </x:c>
+      <x:c r="F132" t="str">
+        <x:v>Elemento ya revisado recibe nuevo toque.</x:v>
+      </x:c>
+      <x:c r="G132" t="str">
+        <x:v>Visitante repite un elemento completado.</x:v>
+      </x:c>
+      <x:c r="H132" t="str">
+        <x:v>Indicar que ese nodo ya fue revisado.</x:v>
+      </x:c>
+      <x:c r="I132" t="str">
+        <x:v>Revisión de cadena</x:v>
+      </x:c>
+      <x:c r="J132" t="str">
+        <x:v>Error técnico</x:v>
+      </x:c>
+      <x:c r="K132" t="str">
+        <x:v>35-90 caracteres</x:v>
+      </x:c>
+      <x:c r="L132" t="str"/>
+      <x:c r="M132" t="str"/>
+      <x:c r="N132" t="str"/>
+      <x:c r="O132" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="str">
+        <x:v>W4_COMPLETE_LIA_01</x:v>
+      </x:c>
+      <x:c r="B133" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>w4_complete</x:v>
+      </x:c>
+      <x:c r="D133" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E133" t="str">
+        <x:v>Cierre</x:v>
+      </x:c>
+      <x:c r="F133" t="str">
+        <x:v>Pantalla completa con todos los pasos activados.</x:v>
+      </x:c>
+      <x:c r="G133" t="str">
+        <x:v>Visitante completó la secuencia principal.</x:v>
+      </x:c>
+      <x:c r="H133" t="str">
+        <x:v>Cerrar cadena técnica y preparar síntesis espacial.</x:v>
+      </x:c>
+      <x:c r="I133" t="str">
+        <x:v>Mediación técnica completa</x:v>
+      </x:c>
+      <x:c r="J133" t="str">
+        <x:v>Reexplicar todo</x:v>
+      </x:c>
+      <x:c r="K133" t="str">
+        <x:v>90-160 caracteres</x:v>
+      </x:c>
+      <x:c r="L133" t="str"/>
+      <x:c r="M133" t="str"/>
+      <x:c r="N133" t="str"/>
+      <x:c r="O133" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="str">
+        <x:v>W4_COMPLETE_SYS_01</x:v>
+      </x:c>
+      <x:c r="B134" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>w4_complete</x:v>
+      </x:c>
+      <x:c r="D134" t="str">
+        <x:v>Sistema / ambiente</x:v>
+      </x:c>
+      <x:c r="E134" t="str">
+        <x:v>Cierre ambiental</x:v>
+      </x:c>
+      <x:c r="F134" t="str">
+        <x:v>Pantalla completa con todos los pasos activados.</x:v>
+      </x:c>
+      <x:c r="G134" t="str">
+        <x:v>Visitante completó la secuencia principal.</x:v>
+      </x:c>
+      <x:c r="H134" t="str">
+        <x:v>Confirmar que los ocho nodos forman una sola operación.</x:v>
+      </x:c>
+      <x:c r="I134" t="str">
+        <x:v>Sistema completo</x:v>
+      </x:c>
+      <x:c r="J134" t="str">
+        <x:v>Triunfalismo técnico</x:v>
+      </x:c>
+      <x:c r="K134" t="str">
+        <x:v>60-130 caracteres</x:v>
+      </x:c>
+      <x:c r="L134" t="str"/>
+      <x:c r="M134" t="str"/>
+      <x:c r="N134" t="str"/>
+      <x:c r="O134" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="str">
+        <x:v>W4_CONTINUE_BTN_01</x:v>
+      </x:c>
+      <x:c r="B135" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>w4_complete</x:v>
+      </x:c>
+      <x:c r="D135" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E135" t="str">
+        <x:v>Botón</x:v>
+      </x:c>
+      <x:c r="F135" t="str">
+        <x:v>Botón de avance habilitado.</x:v>
+      </x:c>
+      <x:c r="G135" t="str">
+        <x:v>Pantalla completada.</x:v>
+      </x:c>
+      <x:c r="H135" t="str">
+        <x:v>Avanzar a transición hacia Mundo V.</x:v>
+      </x:c>
+      <x:c r="I135" t="str">
+        <x:v>Avance secuencial</x:v>
+      </x:c>
+      <x:c r="J135" t="str">
+        <x:v>Ambigüedad</x:v>
+      </x:c>
+      <x:c r="K135" t="str">
+        <x:v>1-4 palabras</x:v>
+      </x:c>
+      <x:c r="L135" t="str"/>
+      <x:c r="M135" t="str"/>
+      <x:c r="N135" t="str"/>
+      <x:c r="O135" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="str">
+        <x:v>W4_ACCESSIBLE_SCENE_01</x:v>
+      </x:c>
+      <x:c r="B136" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>w4_intro</x:v>
+      </x:c>
+      <x:c r="D136" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E136" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F136" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G136" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H136" t="str">
+        <x:v>Describir mesa, Lía, línea de flujo y ocho nodos.</x:v>
+      </x:c>
+      <x:c r="I136" t="str">
+        <x:v>Mesa / cadena</x:v>
+      </x:c>
+      <x:c r="J136" t="str">
+        <x:v>Texto excesivo</x:v>
+      </x:c>
+      <x:c r="K136" t="str">
+        <x:v>90-180 caracteres</x:v>
+      </x:c>
+      <x:c r="L136" t="str"/>
+      <x:c r="M136" t="str"/>
+      <x:c r="N136" t="str"/>
+      <x:c r="O136" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="str">
+        <x:v>W4_ACCESSIBLE_PLANTA_01</x:v>
+      </x:c>
+      <x:c r="B137" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>w4_planta_active</x:v>
+      </x:c>
+      <x:c r="D137" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E137" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F137" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G137" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H137" t="str">
+        <x:v>Describir activación de PLANTA.</x:v>
+      </x:c>
+      <x:c r="I137" t="str">
+        <x:v>Planta</x:v>
+      </x:c>
+      <x:c r="J137" t="str">
+        <x:v>Adorno</x:v>
+      </x:c>
+      <x:c r="K137" t="str">
+        <x:v>70-140 caracteres</x:v>
+      </x:c>
+      <x:c r="L137" t="str"/>
+      <x:c r="M137" t="str"/>
+      <x:c r="N137" t="str"/>
+      <x:c r="O137" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="str">
+        <x:v>W4_ACCESSIBLE_BIONOSIFICADOR_01</x:v>
+      </x:c>
+      <x:c r="B138" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>w4_bionosificador_active</x:v>
+      </x:c>
+      <x:c r="D138" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E138" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F138" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G138" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H138" t="str">
+        <x:v>Describir activación de BIONOSIFICADOR.</x:v>
+      </x:c>
+      <x:c r="I138" t="str">
+        <x:v>Bionosificador</x:v>
+      </x:c>
+      <x:c r="J138" t="str">
+        <x:v>Sensor genérico</x:v>
+      </x:c>
+      <x:c r="K138" t="str">
+        <x:v>70-150 caracteres</x:v>
+      </x:c>
+      <x:c r="L138" t="str"/>
+      <x:c r="M138" t="str"/>
+      <x:c r="N138" t="str"/>
+      <x:c r="O138" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="str">
+        <x:v>W4_ACCESSIBLE_ESP32_01</x:v>
+      </x:c>
+      <x:c r="B139" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>w4_esp32_active</x:v>
+      </x:c>
+      <x:c r="D139" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E139" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F139" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G139" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H139" t="str">
+        <x:v>Describir activación de ESP32.</x:v>
+      </x:c>
+      <x:c r="I139" t="str">
+        <x:v>ESP32</x:v>
+      </x:c>
+      <x:c r="J139" t="str">
+        <x:v>Sonido final</x:v>
+      </x:c>
+      <x:c r="K139" t="str">
+        <x:v>70-140 caracteres</x:v>
+      </x:c>
+      <x:c r="L139" t="str"/>
+      <x:c r="M139" t="str"/>
+      <x:c r="N139" t="str"/>
+      <x:c r="O139" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str">
+        <x:v>W4_ACCESSIBLE_MIDI_01</x:v>
+      </x:c>
+      <x:c r="B140" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>w4_midi_active</x:v>
+      </x:c>
+      <x:c r="D140" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E140" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F140" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G140" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H140" t="str">
+        <x:v>Describir activación de MIDI.</x:v>
+      </x:c>
+      <x:c r="I140" t="str">
+        <x:v>MIDI</x:v>
+      </x:c>
+      <x:c r="J140" t="str">
+        <x:v>Audio directo</x:v>
+      </x:c>
+      <x:c r="K140" t="str">
+        <x:v>70-140 caracteres</x:v>
+      </x:c>
+      <x:c r="L140" t="str"/>
+      <x:c r="M140" t="str"/>
+      <x:c r="N140" t="str"/>
+      <x:c r="O140" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>W4_ACCESSIBLE_WIFI_UDP_01</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>w4_wifi_udp_active</x:v>
+      </x:c>
+      <x:c r="D141" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E141" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F141" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G141" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H141" t="str">
+        <x:v>Describir activación de Wi‑Fi/UDP.</x:v>
+      </x:c>
+      <x:c r="I141" t="str">
+        <x:v>Wi‑Fi/UDP</x:v>
+      </x:c>
+      <x:c r="J141" t="str">
+        <x:v>Internet externo</x:v>
+      </x:c>
+      <x:c r="K141" t="str">
+        <x:v>70-150 caracteres</x:v>
+      </x:c>
+      <x:c r="L141" t="str"/>
+      <x:c r="M141" t="str"/>
+      <x:c r="N141" t="str"/>
+      <x:c r="O141" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>W4_ACCESSIBLE_ROUTER_01</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>w4_router_active</x:v>
+      </x:c>
+      <x:c r="D142" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E142" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F142" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G142" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H142" t="str">
+        <x:v>Describir activación de ROUTER.</x:v>
+      </x:c>
+      <x:c r="I142" t="str">
+        <x:v>Router</x:v>
+      </x:c>
+      <x:c r="J142" t="str">
+        <x:v>Nube/API externa</x:v>
+      </x:c>
+      <x:c r="K142" t="str">
+        <x:v>70-140 caracteres</x:v>
+      </x:c>
+      <x:c r="L142" t="str"/>
+      <x:c r="M142" t="str"/>
+      <x:c r="N142" t="str"/>
+      <x:c r="O142" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>W4_ACCESSIBLE_SISTEMA_CENTRAL_01</x:v>
+      </x:c>
+      <x:c r="B143" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>w4_sistema_central_active</x:v>
+      </x:c>
+      <x:c r="D143" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E143" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F143" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G143" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H143" t="str">
+        <x:v>Describir activación de SISTEMA CENTRAL.</x:v>
+      </x:c>
+      <x:c r="I143" t="str">
+        <x:v>Sistema central</x:v>
+      </x:c>
+      <x:c r="J143" t="str">
+        <x:v>Caja negra mágica</x:v>
+      </x:c>
+      <x:c r="K143" t="str">
+        <x:v>70-160 caracteres</x:v>
+      </x:c>
+      <x:c r="L143" t="str"/>
+      <x:c r="M143" t="str"/>
+      <x:c r="N143" t="str"/>
+      <x:c r="O143" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>W4_ACCESSIBLE_SONIDO_01</x:v>
+      </x:c>
+      <x:c r="B144" t="str">
+        <x:v>Estación IV — Mesa de Sistema</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>w4_sonido_active</x:v>
+      </x:c>
+      <x:c r="D144" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E144" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F144" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G144" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H144" t="str">
+        <x:v>Describir activación de SONIDO.</x:v>
+      </x:c>
+      <x:c r="I144" t="str">
+        <x:v>Sonido mediado</x:v>
+      </x:c>
+      <x:c r="J144" t="str">
+        <x:v>Planta que canta</x:v>
+      </x:c>
+      <x:c r="K144" t="str">
+        <x:v>70-150 caracteres</x:v>
+      </x:c>
+      <x:c r="L144" t="str"/>
+      <x:c r="M144" t="str"/>
+      <x:c r="N144" t="str"/>
+      <x:c r="O144" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>W5_INTRO_LIA_01</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>w5_intro</x:v>
+      </x:c>
+      <x:c r="D145" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E145" t="str">
+        <x:v>Entrada</x:v>
+      </x:c>
+      <x:c r="F145" t="str">
+        <x:v>Escena inicial con Lía y elementos principales visibles.</x:v>
+      </x:c>
+      <x:c r="G145" t="str">
+        <x:v>Ingreso a la pantalla.</x:v>
+      </x:c>
+      <x:c r="H145" t="str">
+        <x:v>Presentar OKÚA como montaje vivo situado.</x:v>
+      </x:c>
+      <x:c r="I145" t="str">
+        <x:v>Presente / espacio real</x:v>
+      </x:c>
+      <x:c r="J145" t="str">
+        <x:v>Repetir cadena técnica</x:v>
+      </x:c>
+      <x:c r="K145" t="str">
+        <x:v>90-160 caracteres</x:v>
+      </x:c>
+      <x:c r="L145" t="str"/>
+      <x:c r="M145" t="str"/>
+      <x:c r="N145" t="str"/>
+      <x:c r="O145" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="str">
+        <x:v>W5_INTRO_AMB_01</x:v>
+      </x:c>
+      <x:c r="B146" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C146" t="str">
+        <x:v>w5_intro</x:v>
+      </x:c>
+      <x:c r="D146" t="str">
+        <x:v>Ambiente</x:v>
+      </x:c>
+      <x:c r="E146" t="str">
+        <x:v>Texto ambiental</x:v>
+      </x:c>
+      <x:c r="F146" t="str">
+        <x:v>Escena inicial con Lía y elementos principales visibles.</x:v>
+      </x:c>
+      <x:c r="G146" t="str">
+        <x:v>Ingreso a la pantalla.</x:v>
+      </x:c>
+      <x:c r="H146" t="str">
+        <x:v>Situar mapa, espacio y recorrido como conjunto.</x:v>
+      </x:c>
+      <x:c r="I146" t="str">
+        <x:v>Experiencia situada</x:v>
+      </x:c>
+      <x:c r="J146" t="str">
+        <x:v>Nueva teoría</x:v>
+      </x:c>
+      <x:c r="K146" t="str">
+        <x:v>50-120 caracteres</x:v>
+      </x:c>
+      <x:c r="L146" t="str"/>
+      <x:c r="M146" t="str"/>
+      <x:c r="N146" t="str"/>
+      <x:c r="O146" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="str">
+        <x:v>W5_PLANTAS_HINT_01</x:v>
+      </x:c>
+      <x:c r="B147" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>w5_plantas_available</x:v>
+      </x:c>
+      <x:c r="D147" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E147" t="str">
+        <x:v>Instrucción contextual</x:v>
+      </x:c>
+      <x:c r="F147" t="str">
+        <x:v>Elemento PLANTAS disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G147" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H147" t="str">
+        <x:v>Invitar a activar PLANTAS.</x:v>
+      </x:c>
+      <x:c r="I147" t="str">
+        <x:v>Plantas</x:v>
+      </x:c>
+      <x:c r="J147" t="str">
+        <x:v>Repetir Mundo I completo</x:v>
+      </x:c>
+      <x:c r="K147" t="str">
+        <x:v>40-90 caracteres</x:v>
+      </x:c>
+      <x:c r="L147" t="str"/>
+      <x:c r="M147" t="str"/>
+      <x:c r="N147" t="str"/>
+      <x:c r="O147" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="str">
+        <x:v>W5_PLANTAS_AMB_01</x:v>
+      </x:c>
+      <x:c r="B148" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C148" t="str">
+        <x:v>w5_plantas_active</x:v>
+      </x:c>
+      <x:c r="D148" t="str">
+        <x:v>Lía / ambiente</x:v>
+      </x:c>
+      <x:c r="E148" t="str">
+        <x:v>Diálogo por área</x:v>
+      </x:c>
+      <x:c r="F148" t="str">
+        <x:v>Elemento PLANTAS disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G148" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H148" t="str">
+        <x:v>Reconocer el origen vivo del montaje actual.</x:v>
+      </x:c>
+      <x:c r="I148" t="str">
+        <x:v>Plantas / vida</x:v>
+      </x:c>
+      <x:c r="J148" t="str">
+        <x:v>Adorno</x:v>
+      </x:c>
+      <x:c r="K148" t="str">
+        <x:v>70-140 caracteres</x:v>
+      </x:c>
+      <x:c r="L148" t="str"/>
+      <x:c r="M148" t="str"/>
+      <x:c r="N148" t="str"/>
+      <x:c r="O148" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="str">
+        <x:v>W5_PLANTAS_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B149" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C149" t="str">
+        <x:v>w5_plantas_active</x:v>
+      </x:c>
+      <x:c r="D149" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E149" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F149" t="str">
+        <x:v>Elemento PLANTAS disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G149" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H149" t="str">
+        <x:v>Confirmar que el presente del montaje parte de vidas vegetales.</x:v>
+      </x:c>
+      <x:c r="I149" t="str">
+        <x:v>Origen vivo</x:v>
+      </x:c>
+      <x:c r="J149" t="str">
+        <x:v>Planta como objeto</x:v>
+      </x:c>
+      <x:c r="K149" t="str">
+        <x:v>50-120 caracteres</x:v>
+      </x:c>
+      <x:c r="L149" t="str"/>
+      <x:c r="M149" t="str"/>
+      <x:c r="N149" t="str"/>
+      <x:c r="O149" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="str">
+        <x:v>W5_SISTEMA_HINT_01</x:v>
+      </x:c>
+      <x:c r="B150" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C150" t="str">
+        <x:v>w5_sistema_available</x:v>
+      </x:c>
+      <x:c r="D150" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E150" t="str">
+        <x:v>Instrucción contextual</x:v>
+      </x:c>
+      <x:c r="F150" t="str">
+        <x:v>Elemento SISTEMA disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G150" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H150" t="str">
+        <x:v>Invitar a activar SISTEMA.</x:v>
+      </x:c>
+      <x:c r="I150" t="str">
+        <x:v>Sistema</x:v>
+      </x:c>
+      <x:c r="J150" t="str">
+        <x:v>Reexplicar ocho nodos</x:v>
+      </x:c>
+      <x:c r="K150" t="str">
+        <x:v>40-90 caracteres</x:v>
+      </x:c>
+      <x:c r="L150" t="str"/>
+      <x:c r="M150" t="str"/>
+      <x:c r="N150" t="str"/>
+      <x:c r="O150" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" t="str">
+        <x:v>W5_SISTEMA_AMB_01</x:v>
+      </x:c>
+      <x:c r="B151" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C151" t="str">
+        <x:v>w5_sistema_active</x:v>
+      </x:c>
+      <x:c r="D151" t="str">
+        <x:v>Lía / ambiente</x:v>
+      </x:c>
+      <x:c r="E151" t="str">
+        <x:v>Diálogo por área</x:v>
+      </x:c>
+      <x:c r="F151" t="str">
+        <x:v>Elemento SISTEMA disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G151" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H151" t="str">
+        <x:v>Mostrar la mediación operando en el presente.</x:v>
+      </x:c>
+      <x:c r="I151" t="str">
+        <x:v>Sistema / mediación</x:v>
+      </x:c>
+      <x:c r="J151" t="str">
+        <x:v>Repetir Estación IV</x:v>
+      </x:c>
+      <x:c r="K151" t="str">
+        <x:v>70-140 caracteres</x:v>
+      </x:c>
+      <x:c r="L151" t="str"/>
+      <x:c r="M151" t="str"/>
+      <x:c r="N151" t="str"/>
+      <x:c r="O151" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" t="str">
+        <x:v>W5_SISTEMA_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B152" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C152" t="str">
+        <x:v>w5_sistema_active</x:v>
+      </x:c>
+      <x:c r="D152" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E152" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F152" t="str">
+        <x:v>Elemento SISTEMA disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G152" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H152" t="str">
+        <x:v>Confirmar que el sistema sostiene la experiencia sin reemplazarla.</x:v>
+      </x:c>
+      <x:c r="I152" t="str">
+        <x:v>Mediación actual</x:v>
+      </x:c>
+      <x:c r="J152" t="str">
+        <x:v>Máquina como centro único</x:v>
+      </x:c>
+      <x:c r="K152" t="str">
+        <x:v>50-120 caracteres</x:v>
+      </x:c>
+      <x:c r="L152" t="str"/>
+      <x:c r="M152" t="str"/>
+      <x:c r="N152" t="str"/>
+      <x:c r="O152" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="str">
+        <x:v>W5_ESPACIO_HINT_01</x:v>
+      </x:c>
+      <x:c r="B153" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C153" t="str">
+        <x:v>w5_espacio_available</x:v>
+      </x:c>
+      <x:c r="D153" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E153" t="str">
+        <x:v>Instrucción contextual</x:v>
+      </x:c>
+      <x:c r="F153" t="str">
+        <x:v>Elemento ESPACIO disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G153" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H153" t="str">
+        <x:v>Invitar a activar ESPACIO.</x:v>
+      </x:c>
+      <x:c r="I153" t="str">
+        <x:v>Espacio</x:v>
+      </x:c>
+      <x:c r="J153" t="str">
+        <x:v>Abstracción total</x:v>
+      </x:c>
+      <x:c r="K153" t="str">
+        <x:v>40-90 caracteres</x:v>
+      </x:c>
+      <x:c r="L153" t="str"/>
+      <x:c r="M153" t="str"/>
+      <x:c r="N153" t="str"/>
+      <x:c r="O153" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="str">
+        <x:v>W5_ESPACIO_AMB_01</x:v>
+      </x:c>
+      <x:c r="B154" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C154" t="str">
+        <x:v>w5_espacio_active</x:v>
+      </x:c>
+      <x:c r="D154" t="str">
+        <x:v>Lía / ambiente</x:v>
+      </x:c>
+      <x:c r="E154" t="str">
+        <x:v>Diálogo por área</x:v>
+      </x:c>
+      <x:c r="F154" t="str">
+        <x:v>Elemento ESPACIO disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G154" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H154" t="str">
+        <x:v>Aterrizar la experiencia en un lugar real.</x:v>
+      </x:c>
+      <x:c r="I154" t="str">
+        <x:v>Lugar / montaje</x:v>
+      </x:c>
+      <x:c r="J154" t="str">
+        <x:v>App aislada del jardín</x:v>
+      </x:c>
+      <x:c r="K154" t="str">
+        <x:v>70-140 caracteres</x:v>
+      </x:c>
+      <x:c r="L154" t="str"/>
+      <x:c r="M154" t="str"/>
+      <x:c r="N154" t="str"/>
+      <x:c r="O154" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="str">
+        <x:v>W5_ESPACIO_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B155" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>w5_espacio_active</x:v>
+      </x:c>
+      <x:c r="D155" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E155" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F155" t="str">
+        <x:v>Elemento ESPACIO disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G155" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H155" t="str">
+        <x:v>Confirmar que el espacio también organiza la experiencia.</x:v>
+      </x:c>
+      <x:c r="I155" t="str">
+        <x:v>Experiencia situada</x:v>
+      </x:c>
+      <x:c r="J155" t="str">
+        <x:v>Decorado</x:v>
+      </x:c>
+      <x:c r="K155" t="str">
+        <x:v>50-120 caracteres</x:v>
+      </x:c>
+      <x:c r="L155" t="str"/>
+      <x:c r="M155" t="str"/>
+      <x:c r="N155" t="str"/>
+      <x:c r="O155" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="str">
+        <x:v>W5_VISITANTE_HINT_01</x:v>
+      </x:c>
+      <x:c r="B156" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>w5_visitante_available</x:v>
+      </x:c>
+      <x:c r="D156" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E156" t="str">
+        <x:v>Instrucción contextual</x:v>
+      </x:c>
+      <x:c r="F156" t="str">
+        <x:v>Elemento VISITANTE disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G156" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H156" t="str">
+        <x:v>Invitar a activar VISITANTE.</x:v>
+      </x:c>
+      <x:c r="I156" t="str">
+        <x:v>Visitante</x:v>
+      </x:c>
+      <x:c r="J156" t="str">
+        <x:v>Usuario pasivo</x:v>
+      </x:c>
+      <x:c r="K156" t="str">
+        <x:v>40-90 caracteres</x:v>
+      </x:c>
+      <x:c r="L156" t="str"/>
+      <x:c r="M156" t="str"/>
+      <x:c r="N156" t="str"/>
+      <x:c r="O156" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" t="str">
+        <x:v>W5_VISITANTE_AMB_01</x:v>
+      </x:c>
+      <x:c r="B157" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C157" t="str">
+        <x:v>w5_visitante_active</x:v>
+      </x:c>
+      <x:c r="D157" t="str">
+        <x:v>Lía / ambiente</x:v>
+      </x:c>
+      <x:c r="E157" t="str">
+        <x:v>Diálogo por área</x:v>
+      </x:c>
+      <x:c r="F157" t="str">
+        <x:v>Elemento VISITANTE disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G157" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H157" t="str">
+        <x:v>Incluir la participación del visitante en la lectura del montaje.</x:v>
+      </x:c>
+      <x:c r="I157" t="str">
+        <x:v>Participación</x:v>
+      </x:c>
+      <x:c r="J157" t="str">
+        <x:v>Público como espectador pasivo</x:v>
+      </x:c>
+      <x:c r="K157" t="str">
+        <x:v>70-150 caracteres</x:v>
+      </x:c>
+      <x:c r="L157" t="str"/>
+      <x:c r="M157" t="str"/>
+      <x:c r="N157" t="str"/>
+      <x:c r="O157" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" t="str">
+        <x:v>W5_VISITANTE_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B158" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C158" t="str">
+        <x:v>w5_visitante_active</x:v>
+      </x:c>
+      <x:c r="D158" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E158" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F158" t="str">
+        <x:v>Elemento VISITANTE disponible o activo.</x:v>
+      </x:c>
+      <x:c r="G158" t="str">
+        <x:v>Visitante sigue la secuencia indicada.</x:v>
+      </x:c>
+      <x:c r="H158" t="str">
+        <x:v>Confirmar que el recorrido se completa con quien lo atraviesa.</x:v>
+      </x:c>
+      <x:c r="I158" t="str">
+        <x:v>Visitante / experiencia</x:v>
+      </x:c>
+      <x:c r="J158" t="str">
+        <x:v>Antropocentrismo excesivo</x:v>
+      </x:c>
+      <x:c r="K158" t="str">
+        <x:v>50-130 caracteres</x:v>
+      </x:c>
+      <x:c r="L158" t="str"/>
+      <x:c r="M158" t="str"/>
+      <x:c r="N158" t="str"/>
+      <x:c r="O158" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" t="str">
+        <x:v>W5_AREA_LOCKED_01</x:v>
+      </x:c>
+      <x:c r="B159" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C159" t="str">
+        <x:v>w5_area_locked</x:v>
+      </x:c>
+      <x:c r="D159" t="str">
+        <x:v>Lía o sistema</x:v>
+      </x:c>
+      <x:c r="E159" t="str">
+        <x:v>Bloqueo suave</x:v>
+      </x:c>
+      <x:c r="F159" t="str">
+        <x:v>Elemento fuera de orden no avanza.</x:v>
+      </x:c>
+      <x:c r="G159" t="str">
+        <x:v>Visitante tocó un elemento bloqueado.</x:v>
+      </x:c>
+      <x:c r="H159" t="str">
+        <x:v>Guiar a la siguiente área.</x:v>
+      </x:c>
+      <x:c r="I159" t="str">
+        <x:v>Síntesis ordenada</x:v>
+      </x:c>
+      <x:c r="J159" t="str">
+        <x:v>Regaño</x:v>
+      </x:c>
+      <x:c r="K159" t="str">
+        <x:v>35-90 caracteres</x:v>
+      </x:c>
+      <x:c r="L159" t="str"/>
+      <x:c r="M159" t="str"/>
+      <x:c r="N159" t="str"/>
+      <x:c r="O159" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" t="str">
+        <x:v>W5_AREA_REPEAT_01</x:v>
+      </x:c>
+      <x:c r="B160" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C160" t="str">
+        <x:v>w5_area_locked</x:v>
+      </x:c>
+      <x:c r="D160" t="str">
+        <x:v>Lía o sistema</x:v>
+      </x:c>
+      <x:c r="E160" t="str">
+        <x:v>Relectura / repetición</x:v>
+      </x:c>
+      <x:c r="F160" t="str">
+        <x:v>Elemento ya revisado recibe nuevo toque.</x:v>
+      </x:c>
+      <x:c r="G160" t="str">
+        <x:v>Visitante repite un elemento completado.</x:v>
+      </x:c>
+      <x:c r="H160" t="str">
+        <x:v>Indicar que esa área ya fue revisada.</x:v>
+      </x:c>
+      <x:c r="I160" t="str">
+        <x:v>Revisión cuidadosa</x:v>
+      </x:c>
+      <x:c r="J160" t="str">
+        <x:v>Error técnico</x:v>
+      </x:c>
+      <x:c r="K160" t="str">
+        <x:v>35-90 caracteres</x:v>
+      </x:c>
+      <x:c r="L160" t="str"/>
+      <x:c r="M160" t="str"/>
+      <x:c r="N160" t="str"/>
+      <x:c r="O160" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" t="str">
+        <x:v>W5_COMPLETE_LIA_01</x:v>
+      </x:c>
+      <x:c r="B161" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C161" t="str">
+        <x:v>w5_complete</x:v>
+      </x:c>
+      <x:c r="D161" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E161" t="str">
+        <x:v>Cierre previo</x:v>
+      </x:c>
+      <x:c r="F161" t="str">
+        <x:v>Pantalla completa con todos los pasos activados.</x:v>
+      </x:c>
+      <x:c r="G161" t="str">
+        <x:v>Visitante completó la secuencia principal.</x:v>
+      </x:c>
+      <x:c r="H161" t="str">
+        <x:v>Preparar paso al mirador final.</x:v>
+      </x:c>
+      <x:c r="I161" t="str">
+        <x:v>Cierre del recorrido</x:v>
+      </x:c>
+      <x:c r="J161" t="str">
+        <x:v>Introducir estación nueva</x:v>
+      </x:c>
+      <x:c r="K161" t="str">
+        <x:v>80-150 caracteres</x:v>
+      </x:c>
+      <x:c r="L161" t="str"/>
+      <x:c r="M161" t="str"/>
+      <x:c r="N161" t="str"/>
+      <x:c r="O161" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" t="str">
+        <x:v>W5_COMPLETE_AMB_01</x:v>
+      </x:c>
+      <x:c r="B162" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>w5_complete</x:v>
+      </x:c>
+      <x:c r="D162" t="str">
+        <x:v>Ambiente</x:v>
+      </x:c>
+      <x:c r="E162" t="str">
+        <x:v>Cierre ambiental</x:v>
+      </x:c>
+      <x:c r="F162" t="str">
+        <x:v>Pantalla completa con todos los pasos activados.</x:v>
+      </x:c>
+      <x:c r="G162" t="str">
+        <x:v>Visitante completó la secuencia principal.</x:v>
+      </x:c>
+      <x:c r="H162" t="str">
+        <x:v>Cerrar el mapa como síntesis del presente.</x:v>
+      </x:c>
+      <x:c r="I162" t="str">
+        <x:v>Presente / síntesis</x:v>
+      </x:c>
+      <x:c r="J162" t="str">
+        <x:v>Repetir teoría</x:v>
+      </x:c>
+      <x:c r="K162" t="str">
+        <x:v>50-120 caracteres</x:v>
+      </x:c>
+      <x:c r="L162" t="str"/>
+      <x:c r="M162" t="str"/>
+      <x:c r="N162" t="str"/>
+      <x:c r="O162" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" t="str">
+        <x:v>W5_FINAL_BTN_01</x:v>
+      </x:c>
+      <x:c r="B163" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C163" t="str">
+        <x:v>w5_complete</x:v>
+      </x:c>
+      <x:c r="D163" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E163" t="str">
+        <x:v>Botón</x:v>
+      </x:c>
+      <x:c r="F163" t="str">
+        <x:v>Botón de avance habilitado.</x:v>
+      </x:c>
+      <x:c r="G163" t="str">
+        <x:v>Pantalla completada.</x:v>
+      </x:c>
+      <x:c r="H163" t="str">
+        <x:v>Abrir transición hacia pantalla final.</x:v>
+      </x:c>
+      <x:c r="I163" t="str">
+        <x:v>Cierre</x:v>
+      </x:c>
+      <x:c r="J163" t="str">
+        <x:v>Ambigüedad</x:v>
+      </x:c>
+      <x:c r="K163" t="str">
+        <x:v>1-4 palabras</x:v>
+      </x:c>
+      <x:c r="L163" t="str"/>
+      <x:c r="M163" t="str"/>
+      <x:c r="N163" t="str"/>
+      <x:c r="O163" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" t="str">
+        <x:v>W5_ACCESSIBLE_SCENE_01</x:v>
+      </x:c>
+      <x:c r="B164" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C164" t="str">
+        <x:v>w5_intro</x:v>
+      </x:c>
+      <x:c r="D164" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E164" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F164" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G164" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H164" t="str">
+        <x:v>Describir mapa, Lía y cuatro áreas.</x:v>
+      </x:c>
+      <x:c r="I164" t="str">
+        <x:v>Mapa / áreas</x:v>
+      </x:c>
+      <x:c r="J164" t="str">
+        <x:v>Texto excesivo</x:v>
+      </x:c>
+      <x:c r="K164" t="str">
+        <x:v>90-170 caracteres</x:v>
+      </x:c>
+      <x:c r="L164" t="str"/>
+      <x:c r="M164" t="str"/>
+      <x:c r="N164" t="str"/>
+      <x:c r="O164" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" t="str">
+        <x:v>W5_ACCESSIBLE_PLANTAS_01</x:v>
+      </x:c>
+      <x:c r="B165" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C165" t="str">
+        <x:v>w5_plantas_active</x:v>
+      </x:c>
+      <x:c r="D165" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E165" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F165" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G165" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H165" t="str">
+        <x:v>Describir activación de PLANTAS.</x:v>
+      </x:c>
+      <x:c r="I165" t="str">
+        <x:v>Plantas</x:v>
+      </x:c>
+      <x:c r="J165" t="str">
+        <x:v>Adorno</x:v>
+      </x:c>
+      <x:c r="K165" t="str">
+        <x:v>70-140 caracteres</x:v>
+      </x:c>
+      <x:c r="L165" t="str"/>
+      <x:c r="M165" t="str"/>
+      <x:c r="N165" t="str"/>
+      <x:c r="O165" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" t="str">
+        <x:v>W5_ACCESSIBLE_SISTEMA_01</x:v>
+      </x:c>
+      <x:c r="B166" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C166" t="str">
+        <x:v>w5_sistema_active</x:v>
+      </x:c>
+      <x:c r="D166" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E166" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F166" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G166" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H166" t="str">
+        <x:v>Describir activación de SISTEMA.</x:v>
+      </x:c>
+      <x:c r="I166" t="str">
+        <x:v>Sistema</x:v>
+      </x:c>
+      <x:c r="J166" t="str">
+        <x:v>Ocho nodos completos</x:v>
+      </x:c>
+      <x:c r="K166" t="str">
+        <x:v>70-140 caracteres</x:v>
+      </x:c>
+      <x:c r="L166" t="str"/>
+      <x:c r="M166" t="str"/>
+      <x:c r="N166" t="str"/>
+      <x:c r="O166" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" t="str">
+        <x:v>W5_ACCESSIBLE_ESPACIO_01</x:v>
+      </x:c>
+      <x:c r="B167" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C167" t="str">
+        <x:v>w5_espacio_active</x:v>
+      </x:c>
+      <x:c r="D167" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E167" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F167" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G167" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H167" t="str">
+        <x:v>Describir activación de ESPACIO.</x:v>
+      </x:c>
+      <x:c r="I167" t="str">
+        <x:v>Espacio</x:v>
+      </x:c>
+      <x:c r="J167" t="str">
+        <x:v>Decorado</x:v>
+      </x:c>
+      <x:c r="K167" t="str">
+        <x:v>70-140 caracteres</x:v>
+      </x:c>
+      <x:c r="L167" t="str"/>
+      <x:c r="M167" t="str"/>
+      <x:c r="N167" t="str"/>
+      <x:c r="O167" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" t="str">
+        <x:v>W5_ACCESSIBLE_VISITANTE_01</x:v>
+      </x:c>
+      <x:c r="B168" t="str">
+        <x:v>Estación V — Mapa del Presente</x:v>
+      </x:c>
+      <x:c r="C168" t="str">
+        <x:v>w5_visitante_active</x:v>
+      </x:c>
+      <x:c r="D168" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E168" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F168" t="str">
+        <x:v>Estado visual activo requiere descripción accesible.</x:v>
+      </x:c>
+      <x:c r="G168" t="str">
+        <x:v>Fallback o lector de pantalla requiere descripción.</x:v>
+      </x:c>
+      <x:c r="H168" t="str">
+        <x:v>Describir activación de VISITANTE.</x:v>
+      </x:c>
+      <x:c r="I168" t="str">
+        <x:v>Visitante</x:v>
+      </x:c>
+      <x:c r="J168" t="str">
+        <x:v>Pasividad</x:v>
+      </x:c>
+      <x:c r="K168" t="str">
+        <x:v>70-150 caracteres</x:v>
+      </x:c>
+      <x:c r="L168" t="str"/>
+      <x:c r="M168" t="str"/>
+      <x:c r="N168" t="str"/>
+      <x:c r="O168" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" t="str">
+        <x:v>FINAL_TITLE_01</x:v>
+      </x:c>
+      <x:c r="B169" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C169" t="str">
+        <x:v>final_intro</x:v>
+      </x:c>
+      <x:c r="D169" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E169" t="str">
+        <x:v>Título</x:v>
+      </x:c>
+      <x:c r="F169" t="str">
+        <x:v>Mirador final con Lía, accesos y acciones visibles.</x:v>
+      </x:c>
+      <x:c r="G169" t="str">
+        <x:v>Visitante llegó al cierre.</x:v>
+      </x:c>
+      <x:c r="H169" t="str">
+        <x:v>Nombrar el cierre del recorrido.</x:v>
+      </x:c>
+      <x:c r="I169" t="str">
+        <x:v>Mirador final</x:v>
+      </x:c>
+      <x:c r="J169" t="str">
+        <x:v>Nueva estación</x:v>
+      </x:c>
+      <x:c r="K169" t="str">
+        <x:v>2-7 palabras</x:v>
+      </x:c>
+      <x:c r="L169" t="str"/>
+      <x:c r="M169" t="str"/>
+      <x:c r="N169" t="str"/>
+      <x:c r="O169" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" t="str">
+        <x:v>FINAL_SUBTITLE_01</x:v>
+      </x:c>
+      <x:c r="B170" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C170" t="str">
+        <x:v>final_intro</x:v>
+      </x:c>
+      <x:c r="D170" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E170" t="str">
+        <x:v>Subtítulo</x:v>
+      </x:c>
+      <x:c r="F170" t="str">
+        <x:v>Mirador final con Lía, accesos y acciones visibles.</x:v>
+      </x:c>
+      <x:c r="G170" t="str">
+        <x:v>Visitante llegó al cierre.</x:v>
+      </x:c>
+      <x:c r="H170" t="str">
+        <x:v>Confirmar recorrido completo.</x:v>
+      </x:c>
+      <x:c r="I170" t="str">
+        <x:v>Recorrido completo</x:v>
+      </x:c>
+      <x:c r="J170" t="str">
+        <x:v>Teoría nueva</x:v>
+      </x:c>
+      <x:c r="K170" t="str">
+        <x:v>2-8 palabras</x:v>
+      </x:c>
+      <x:c r="L170" t="str"/>
+      <x:c r="M170" t="str"/>
+      <x:c r="N170" t="str"/>
+      <x:c r="O170" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" t="str">
+        <x:v>FINAL_LIA_MESSAGE_01</x:v>
+      </x:c>
+      <x:c r="B171" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C171" t="str">
+        <x:v>final_intro</x:v>
+      </x:c>
+      <x:c r="D171" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E171" t="str">
+        <x:v>Mensaje final</x:v>
+      </x:c>
+      <x:c r="F171" t="str">
+        <x:v>Mirador final con Lía, accesos y acciones visibles.</x:v>
+      </x:c>
+      <x:c r="G171" t="str">
+        <x:v>Visitante llegó al cierre.</x:v>
+      </x:c>
+      <x:c r="H171" t="str">
+        <x:v>Confirmar recorrido completo y abrir revisión libre.</x:v>
+      </x:c>
+      <x:c r="I171" t="str">
+        <x:v>Cierre / revisión libre</x:v>
+      </x:c>
+      <x:c r="J171" t="str">
+        <x:v>Nueva teoría</x:v>
+      </x:c>
+      <x:c r="K171" t="str">
+        <x:v>90-170 caracteres</x:v>
+      </x:c>
+      <x:c r="L171" t="str"/>
+      <x:c r="M171" t="str"/>
+      <x:c r="N171" t="str"/>
+      <x:c r="O171" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" t="str">
+        <x:v>FINAL_AMB_01</x:v>
+      </x:c>
+      <x:c r="B172" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C172" t="str">
+        <x:v>final_intro</x:v>
+      </x:c>
+      <x:c r="D172" t="str">
+        <x:v>Ambiente</x:v>
+      </x:c>
+      <x:c r="E172" t="str">
+        <x:v>Cierre ambiental</x:v>
+      </x:c>
+      <x:c r="F172" t="str">
+        <x:v>Mirador final con Lía, accesos y acciones visibles.</x:v>
+      </x:c>
+      <x:c r="G172" t="str">
+        <x:v>Visitante llegó al cierre.</x:v>
+      </x:c>
+      <x:c r="H172" t="str">
+        <x:v>Dar sensación de contemplación y conjunto.</x:v>
+      </x:c>
+      <x:c r="I172" t="str">
+        <x:v>Cierre sereno</x:v>
+      </x:c>
+      <x:c r="J172" t="str">
+        <x:v>Urgencia</x:v>
+      </x:c>
+      <x:c r="K172" t="str">
+        <x:v>50-130 caracteres</x:v>
+      </x:c>
+      <x:c r="L172" t="str"/>
+      <x:c r="M172" t="str"/>
+      <x:c r="N172" t="str"/>
+      <x:c r="O172" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" t="str">
+        <x:v>FINAL_ACCESS_I_LABEL_01</x:v>
+      </x:c>
+      <x:c r="B173" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C173" t="str">
+        <x:v>final_review</x:v>
+      </x:c>
+      <x:c r="D173" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E173" t="str">
+        <x:v>Label de acceso</x:v>
+      </x:c>
+      <x:c r="F173" t="str">
+        <x:v>Accesos a mundos completados visibles.</x:v>
+      </x:c>
+      <x:c r="G173" t="str">
+        <x:v>Recorrido completado; revisión libre disponible.</x:v>
+      </x:c>
+      <x:c r="H173" t="str">
+        <x:v>Nombrar acceso a Mundo I en revisión libre.</x:v>
+      </x:c>
+      <x:c r="I173" t="str">
+        <x:v>Raíz</x:v>
+      </x:c>
+      <x:c r="J173" t="str">
+        <x:v>Texto excesivo</x:v>
+      </x:c>
+      <x:c r="K173" t="str">
+        <x:v>2-6 palabras</x:v>
+      </x:c>
+      <x:c r="L173" t="str"/>
+      <x:c r="M173" t="str"/>
+      <x:c r="N173" t="str"/>
+      <x:c r="O173" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" t="str">
+        <x:v>FINAL_ACCESS_I_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B174" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C174" t="str">
+        <x:v>final_access_i_selected</x:v>
+      </x:c>
+      <x:c r="D174" t="str">
+        <x:v>Sistema / Lía</x:v>
+      </x:c>
+      <x:c r="E174" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F174" t="str">
+        <x:v>Acceso de revisión seleccionado.</x:v>
+      </x:c>
+      <x:c r="G174" t="str">
+        <x:v>Visitante tocó un acceso de mundo.</x:v>
+      </x:c>
+      <x:c r="H174" t="str">
+        <x:v>Confirmar regreso a Mundo I en modo revisión.</x:v>
+      </x:c>
+      <x:c r="I174" t="str">
+        <x:v>Revisión de Raíz</x:v>
+      </x:c>
+      <x:c r="J174" t="str">
+        <x:v>Bloqueo</x:v>
+      </x:c>
+      <x:c r="K174" t="str">
+        <x:v>40-100 caracteres</x:v>
+      </x:c>
+      <x:c r="L174" t="str"/>
+      <x:c r="M174" t="str"/>
+      <x:c r="N174" t="str"/>
+      <x:c r="O174" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" t="str">
+        <x:v>FINAL_ACCESS_II_LABEL_01</x:v>
+      </x:c>
+      <x:c r="B175" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C175" t="str">
+        <x:v>final_review</x:v>
+      </x:c>
+      <x:c r="D175" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E175" t="str">
+        <x:v>Label de acceso</x:v>
+      </x:c>
+      <x:c r="F175" t="str">
+        <x:v>Accesos a mundos completados visibles.</x:v>
+      </x:c>
+      <x:c r="G175" t="str">
+        <x:v>Recorrido completado; revisión libre disponible.</x:v>
+      </x:c>
+      <x:c r="H175" t="str">
+        <x:v>Nombrar acceso a Mundo II en revisión libre.</x:v>
+      </x:c>
+      <x:c r="I175" t="str">
+        <x:v>Pulso invisible</x:v>
+      </x:c>
+      <x:c r="J175" t="str">
+        <x:v>Texto excesivo</x:v>
+      </x:c>
+      <x:c r="K175" t="str">
+        <x:v>2-6 palabras</x:v>
+      </x:c>
+      <x:c r="L175" t="str"/>
+      <x:c r="M175" t="str"/>
+      <x:c r="N175" t="str"/>
+      <x:c r="O175" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" t="str">
+        <x:v>FINAL_ACCESS_II_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B176" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C176" t="str">
+        <x:v>final_access_ii_selected</x:v>
+      </x:c>
+      <x:c r="D176" t="str">
+        <x:v>Sistema / Lía</x:v>
+      </x:c>
+      <x:c r="E176" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F176" t="str">
+        <x:v>Acceso de revisión seleccionado.</x:v>
+      </x:c>
+      <x:c r="G176" t="str">
+        <x:v>Visitante tocó un acceso de mundo.</x:v>
+      </x:c>
+      <x:c r="H176" t="str">
+        <x:v>Confirmar regreso a Mundo II en modo revisión.</x:v>
+      </x:c>
+      <x:c r="I176" t="str">
+        <x:v>Revisión de Pulso invisible</x:v>
+      </x:c>
+      <x:c r="J176" t="str">
+        <x:v>Bloqueo</x:v>
+      </x:c>
+      <x:c r="K176" t="str">
+        <x:v>40-100 caracteres</x:v>
+      </x:c>
+      <x:c r="L176" t="str"/>
+      <x:c r="M176" t="str"/>
+      <x:c r="N176" t="str"/>
+      <x:c r="O176" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" t="str">
+        <x:v>FINAL_ACCESS_III_LABEL_01</x:v>
+      </x:c>
+      <x:c r="B177" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C177" t="str">
+        <x:v>final_review</x:v>
+      </x:c>
+      <x:c r="D177" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E177" t="str">
+        <x:v>Label de acceso</x:v>
+      </x:c>
+      <x:c r="F177" t="str">
+        <x:v>Accesos a mundos completados visibles.</x:v>
+      </x:c>
+      <x:c r="G177" t="str">
+        <x:v>Recorrido completado; revisión libre disponible.</x:v>
+      </x:c>
+      <x:c r="H177" t="str">
+        <x:v>Nombrar acceso a Mundo III en revisión libre.</x:v>
+      </x:c>
+      <x:c r="I177" t="str">
+        <x:v>Cuaderno de pruebas</x:v>
+      </x:c>
+      <x:c r="J177" t="str">
+        <x:v>Texto excesivo</x:v>
+      </x:c>
+      <x:c r="K177" t="str">
+        <x:v>2-6 palabras</x:v>
+      </x:c>
+      <x:c r="L177" t="str"/>
+      <x:c r="M177" t="str"/>
+      <x:c r="N177" t="str"/>
+      <x:c r="O177" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" t="str">
+        <x:v>FINAL_ACCESS_III_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B178" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C178" t="str">
+        <x:v>final_access_iii_selected</x:v>
+      </x:c>
+      <x:c r="D178" t="str">
+        <x:v>Sistema / Lía</x:v>
+      </x:c>
+      <x:c r="E178" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F178" t="str">
+        <x:v>Acceso de revisión seleccionado.</x:v>
+      </x:c>
+      <x:c r="G178" t="str">
+        <x:v>Visitante tocó un acceso de mundo.</x:v>
+      </x:c>
+      <x:c r="H178" t="str">
+        <x:v>Confirmar regreso a Mundo III en modo revisión.</x:v>
+      </x:c>
+      <x:c r="I178" t="str">
+        <x:v>Revisión de Cuaderno</x:v>
+      </x:c>
+      <x:c r="J178" t="str">
+        <x:v>Bloqueo</x:v>
+      </x:c>
+      <x:c r="K178" t="str">
+        <x:v>40-100 caracteres</x:v>
+      </x:c>
+      <x:c r="L178" t="str"/>
+      <x:c r="M178" t="str"/>
+      <x:c r="N178" t="str"/>
+      <x:c r="O178" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" t="str">
+        <x:v>FINAL_ACCESS_IV_LABEL_01</x:v>
+      </x:c>
+      <x:c r="B179" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C179" t="str">
+        <x:v>final_review</x:v>
+      </x:c>
+      <x:c r="D179" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E179" t="str">
+        <x:v>Label de acceso</x:v>
+      </x:c>
+      <x:c r="F179" t="str">
+        <x:v>Accesos a mundos completados visibles.</x:v>
+      </x:c>
+      <x:c r="G179" t="str">
+        <x:v>Recorrido completado; revisión libre disponible.</x:v>
+      </x:c>
+      <x:c r="H179" t="str">
+        <x:v>Nombrar acceso a Mundo IV en revisión libre.</x:v>
+      </x:c>
+      <x:c r="I179" t="str">
+        <x:v>Mesa de sistema</x:v>
+      </x:c>
+      <x:c r="J179" t="str">
+        <x:v>Texto excesivo</x:v>
+      </x:c>
+      <x:c r="K179" t="str">
+        <x:v>2-6 palabras</x:v>
+      </x:c>
+      <x:c r="L179" t="str"/>
+      <x:c r="M179" t="str"/>
+      <x:c r="N179" t="str"/>
+      <x:c r="O179" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" t="str">
+        <x:v>FINAL_ACCESS_IV_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B180" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C180" t="str">
+        <x:v>final_access_iv_selected</x:v>
+      </x:c>
+      <x:c r="D180" t="str">
+        <x:v>Sistema / Lía</x:v>
+      </x:c>
+      <x:c r="E180" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F180" t="str">
+        <x:v>Acceso de revisión seleccionado.</x:v>
+      </x:c>
+      <x:c r="G180" t="str">
+        <x:v>Visitante tocó un acceso de mundo.</x:v>
+      </x:c>
+      <x:c r="H180" t="str">
+        <x:v>Confirmar regreso a Mundo IV en modo revisión.</x:v>
+      </x:c>
+      <x:c r="I180" t="str">
+        <x:v>Revisión de Mesa</x:v>
+      </x:c>
+      <x:c r="J180" t="str">
+        <x:v>Bloqueo</x:v>
+      </x:c>
+      <x:c r="K180" t="str">
+        <x:v>40-100 caracteres</x:v>
+      </x:c>
+      <x:c r="L180" t="str"/>
+      <x:c r="M180" t="str"/>
+      <x:c r="N180" t="str"/>
+      <x:c r="O180" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" t="str">
+        <x:v>FINAL_ACCESS_V_LABEL_01</x:v>
+      </x:c>
+      <x:c r="B181" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C181" t="str">
+        <x:v>final_review</x:v>
+      </x:c>
+      <x:c r="D181" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E181" t="str">
+        <x:v>Label de acceso</x:v>
+      </x:c>
+      <x:c r="F181" t="str">
+        <x:v>Accesos a mundos completados visibles.</x:v>
+      </x:c>
+      <x:c r="G181" t="str">
+        <x:v>Recorrido completado; revisión libre disponible.</x:v>
+      </x:c>
+      <x:c r="H181" t="str">
+        <x:v>Nombrar acceso a Mundo V en revisión libre.</x:v>
+      </x:c>
+      <x:c r="I181" t="str">
+        <x:v>Mapa del presente</x:v>
+      </x:c>
+      <x:c r="J181" t="str">
+        <x:v>Texto excesivo</x:v>
+      </x:c>
+      <x:c r="K181" t="str">
+        <x:v>2-6 palabras</x:v>
+      </x:c>
+      <x:c r="L181" t="str"/>
+      <x:c r="M181" t="str"/>
+      <x:c r="N181" t="str"/>
+      <x:c r="O181" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" t="str">
+        <x:v>FINAL_ACCESS_V_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B182" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C182" t="str">
+        <x:v>final_access_v_selected</x:v>
+      </x:c>
+      <x:c r="D182" t="str">
+        <x:v>Sistema / Lía</x:v>
+      </x:c>
+      <x:c r="E182" t="str">
+        <x:v>Confirmación breve</x:v>
+      </x:c>
+      <x:c r="F182" t="str">
+        <x:v>Acceso de revisión seleccionado.</x:v>
+      </x:c>
+      <x:c r="G182" t="str">
+        <x:v>Visitante tocó un acceso de mundo.</x:v>
+      </x:c>
+      <x:c r="H182" t="str">
+        <x:v>Confirmar regreso a Mundo V en modo revisión.</x:v>
+      </x:c>
+      <x:c r="I182" t="str">
+        <x:v>Revisión de Mapa</x:v>
+      </x:c>
+      <x:c r="J182" t="str">
+        <x:v>Bloqueo</x:v>
+      </x:c>
+      <x:c r="K182" t="str">
+        <x:v>40-100 caracteres</x:v>
+      </x:c>
+      <x:c r="L182" t="str"/>
+      <x:c r="M182" t="str"/>
+      <x:c r="N182" t="str"/>
+      <x:c r="O182" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" t="str">
+        <x:v>FINAL_HELP_01</x:v>
+      </x:c>
+      <x:c r="B183" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C183" t="str">
+        <x:v>final_review</x:v>
+      </x:c>
+      <x:c r="D183" t="str">
+        <x:v>Lía</x:v>
+      </x:c>
+      <x:c r="E183" t="str">
+        <x:v>Ayuda breve</x:v>
+      </x:c>
+      <x:c r="F183" t="str">
+        <x:v>Mirador final con Lía, accesos y acciones visibles.</x:v>
+      </x:c>
+      <x:c r="G183" t="str">
+        <x:v>Visitante llegó al cierre.</x:v>
+      </x:c>
+      <x:c r="H183" t="str">
+        <x:v>Explicar que puede volver a cualquier mundo completado.</x:v>
+      </x:c>
+      <x:c r="I183" t="str">
+        <x:v>Revisión libre</x:v>
+      </x:c>
+      <x:c r="J183" t="str">
+        <x:v>Bloqueo innecesario</x:v>
+      </x:c>
+      <x:c r="K183" t="str">
+        <x:v>60-130 caracteres</x:v>
+      </x:c>
+      <x:c r="L183" t="str"/>
+      <x:c r="M183" t="str"/>
+      <x:c r="N183" t="str"/>
+      <x:c r="O183" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" t="str">
+        <x:v>FINAL_BACK_HOME_BTN_01</x:v>
+      </x:c>
+      <x:c r="B184" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C184" t="str">
+        <x:v>final_return</x:v>
+      </x:c>
+      <x:c r="D184" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E184" t="str">
+        <x:v>Botón</x:v>
+      </x:c>
+      <x:c r="F184" t="str">
+        <x:v>Acción de volver al inicio visible.</x:v>
+      </x:c>
+      <x:c r="G184" t="str">
+        <x:v>Visitante evalúa salir al inicio.</x:v>
+      </x:c>
+      <x:c r="H184" t="str">
+        <x:v>Volver a portada o inicio según diseño.</x:v>
+      </x:c>
+      <x:c r="I184" t="str">
+        <x:v>Salida clara</x:v>
+      </x:c>
+      <x:c r="J184" t="str">
+        <x:v>Confundir con reinicio</x:v>
+      </x:c>
+      <x:c r="K184" t="str">
+        <x:v>1-4 palabras</x:v>
+      </x:c>
+      <x:c r="L184" t="str"/>
+      <x:c r="M184" t="str"/>
+      <x:c r="N184" t="str"/>
+      <x:c r="O184" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" t="str">
+        <x:v>FINAL_BACK_HOME_HELP_01</x:v>
+      </x:c>
+      <x:c r="B185" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C185" t="str">
+        <x:v>final_return</x:v>
+      </x:c>
+      <x:c r="D185" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E185" t="str">
+        <x:v>Ayuda breve</x:v>
+      </x:c>
+      <x:c r="F185" t="str">
+        <x:v>Acción de volver al inicio visible.</x:v>
+      </x:c>
+      <x:c r="G185" t="str">
+        <x:v>Visitante evalúa salir al inicio.</x:v>
+      </x:c>
+      <x:c r="H185" t="str">
+        <x:v>Aclarar que volver al inicio no es necesariamente borrar progreso.</x:v>
+      </x:c>
+      <x:c r="I185" t="str">
+        <x:v>Volver / conservar</x:v>
+      </x:c>
+      <x:c r="J185" t="str">
+        <x:v>Ambigüedad</x:v>
+      </x:c>
+      <x:c r="K185" t="str">
+        <x:v>50-120 caracteres</x:v>
+      </x:c>
+      <x:c r="L185" t="str"/>
+      <x:c r="M185" t="str"/>
+      <x:c r="N185" t="str"/>
+      <x:c r="O185" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" t="str">
+        <x:v>FINAL_RESTART_BTN_01</x:v>
+      </x:c>
+      <x:c r="B186" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C186" t="str">
+        <x:v>final_restart</x:v>
+      </x:c>
+      <x:c r="D186" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E186" t="str">
+        <x:v>Botón</x:v>
+      </x:c>
+      <x:c r="F186" t="str">
+        <x:v>Acción de reinicio o confirmación visible.</x:v>
+      </x:c>
+      <x:c r="G186" t="str">
+        <x:v>Visitante tocó reiniciar recorrido.</x:v>
+      </x:c>
+      <x:c r="H186" t="str">
+        <x:v>Iniciar flujo de reinicio completo.</x:v>
+      </x:c>
+      <x:c r="I186" t="str">
+        <x:v>Reinicio</x:v>
+      </x:c>
+      <x:c r="J186" t="str">
+        <x:v>Ambigüedad</x:v>
+      </x:c>
+      <x:c r="K186" t="str">
+        <x:v>1-4 palabras</x:v>
+      </x:c>
+      <x:c r="L186" t="str"/>
+      <x:c r="M186" t="str"/>
+      <x:c r="N186" t="str"/>
+      <x:c r="O186" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" t="str">
+        <x:v>FINAL_RESTART_CONFIRM_01</x:v>
+      </x:c>
+      <x:c r="B187" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C187" t="str">
+        <x:v>final_restart_confirm</x:v>
+      </x:c>
+      <x:c r="D187" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E187" t="str">
+        <x:v>Confirmación</x:v>
+      </x:c>
+      <x:c r="F187" t="str">
+        <x:v>Acción de reinicio o confirmación visible.</x:v>
+      </x:c>
+      <x:c r="G187" t="str">
+        <x:v>Visitante tocó reiniciar recorrido.</x:v>
+      </x:c>
+      <x:c r="H187" t="str">
+        <x:v>Evitar reinicio accidental.</x:v>
+      </x:c>
+      <x:c r="I187" t="str">
+        <x:v>Confirmación clara</x:v>
+      </x:c>
+      <x:c r="J187" t="str">
+        <x:v>Poetizar acción crítica</x:v>
+      </x:c>
+      <x:c r="K187" t="str">
+        <x:v>60-130 caracteres</x:v>
+      </x:c>
+      <x:c r="L187" t="str"/>
+      <x:c r="M187" t="str"/>
+      <x:c r="N187" t="str"/>
+      <x:c r="O187" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" t="str">
+        <x:v>FINAL_RESTART_CANCEL_BTN_01</x:v>
+      </x:c>
+      <x:c r="B188" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C188" t="str">
+        <x:v>final_restart_confirm</x:v>
+      </x:c>
+      <x:c r="D188" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E188" t="str">
+        <x:v>Botón secundario</x:v>
+      </x:c>
+      <x:c r="F188" t="str">
+        <x:v>Acción de reinicio o confirmación visible.</x:v>
+      </x:c>
+      <x:c r="G188" t="str">
+        <x:v>Visitante tocó reiniciar recorrido.</x:v>
+      </x:c>
+      <x:c r="H188" t="str">
+        <x:v>Cancelar reinicio completo.</x:v>
+      </x:c>
+      <x:c r="I188" t="str">
+        <x:v>Cancelar</x:v>
+      </x:c>
+      <x:c r="J188" t="str">
+        <x:v>Ambigüedad</x:v>
+      </x:c>
+      <x:c r="K188" t="str">
+        <x:v>1-3 palabras</x:v>
+      </x:c>
+      <x:c r="L188" t="str"/>
+      <x:c r="M188" t="str"/>
+      <x:c r="N188" t="str"/>
+      <x:c r="O188" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" t="str">
+        <x:v>FINAL_RESTART_CONFIRM_BTN_01</x:v>
+      </x:c>
+      <x:c r="B189" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C189" t="str">
+        <x:v>final_restart_confirm</x:v>
+      </x:c>
+      <x:c r="D189" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E189" t="str">
+        <x:v>Botón crítico</x:v>
+      </x:c>
+      <x:c r="F189" t="str">
+        <x:v>Acción de reinicio o confirmación visible.</x:v>
+      </x:c>
+      <x:c r="G189" t="str">
+        <x:v>Visitante tocó reiniciar recorrido.</x:v>
+      </x:c>
+      <x:c r="H189" t="str">
+        <x:v>Confirmar reinicio completo.</x:v>
+      </x:c>
+      <x:c r="I189" t="str">
+        <x:v>Confirmar reinicio</x:v>
+      </x:c>
+      <x:c r="J189" t="str">
+        <x:v>Ambigüedad</x:v>
+      </x:c>
+      <x:c r="K189" t="str">
+        <x:v>1-4 palabras</x:v>
+      </x:c>
+      <x:c r="L189" t="str"/>
+      <x:c r="M189" t="str"/>
+      <x:c r="N189" t="str"/>
+      <x:c r="O189" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" t="str">
+        <x:v>FINAL_CREDITS_01</x:v>
+      </x:c>
+      <x:c r="B190" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C190" t="str">
+        <x:v>final_credits</x:v>
+      </x:c>
+      <x:c r="D190" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E190" t="str">
+        <x:v>Créditos</x:v>
+      </x:c>
+      <x:c r="F190" t="str">
+        <x:v>Créditos esenciales visibles.</x:v>
+      </x:c>
+      <x:c r="G190" t="str">
+        <x:v>Visitante abre o llega a créditos.</x:v>
+      </x:c>
+      <x:c r="H190" t="str">
+        <x:v>Mostrar autoría mínima y clara.</x:v>
+      </x:c>
+      <x:c r="I190" t="str">
+        <x:v>Créditos esenciales</x:v>
+      </x:c>
+      <x:c r="J190" t="str">
+        <x:v>Lista larga saturada</x:v>
+      </x:c>
+      <x:c r="K190" t="str">
+        <x:v>Variable</x:v>
+      </x:c>
+      <x:c r="L190" t="str"/>
+      <x:c r="M190" t="str"/>
+      <x:c r="N190" t="str"/>
+      <x:c r="O190" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" t="str">
+        <x:v>FINAL_ACCESSIBLE_SCENE_01</x:v>
+      </x:c>
+      <x:c r="B191" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C191" t="str">
+        <x:v>final_intro</x:v>
+      </x:c>
+      <x:c r="D191" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E191" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F191" t="str">
+        <x:v>Mirador final con Lía, accesos y acciones visibles.</x:v>
+      </x:c>
+      <x:c r="G191" t="str">
+        <x:v>Visitante llegó al cierre.</x:v>
+      </x:c>
+      <x:c r="H191" t="str">
+        <x:v>Describir mirador, Lía, accesos y botones.</x:v>
+      </x:c>
+      <x:c r="I191" t="str">
+        <x:v>Mirador / revisión</x:v>
+      </x:c>
+      <x:c r="J191" t="str">
+        <x:v>Texto excesivo</x:v>
+      </x:c>
+      <x:c r="K191" t="str">
+        <x:v>90-180 caracteres</x:v>
+      </x:c>
+      <x:c r="L191" t="str"/>
+      <x:c r="M191" t="str"/>
+      <x:c r="N191" t="str"/>
+      <x:c r="O191" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" t="str">
+        <x:v>FINAL_ACCESSIBLE_ACCESS_I_01</x:v>
+      </x:c>
+      <x:c r="B192" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C192" t="str">
+        <x:v>final_review</x:v>
+      </x:c>
+      <x:c r="D192" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E192" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F192" t="str">
+        <x:v>Mirador final con Lía, accesos y acciones visibles.</x:v>
+      </x:c>
+      <x:c r="G192" t="str">
+        <x:v>Visitante llegó al cierre.</x:v>
+      </x:c>
+      <x:c r="H192" t="str">
+        <x:v>Describir acceso a Mundo I.</x:v>
+      </x:c>
+      <x:c r="I192" t="str">
+        <x:v>Acceso Raíz</x:v>
+      </x:c>
+      <x:c r="J192" t="str">
+        <x:v>Texto largo</x:v>
+      </x:c>
+      <x:c r="K192" t="str">
+        <x:v>50-110 caracteres</x:v>
+      </x:c>
+      <x:c r="L192" t="str"/>
+      <x:c r="M192" t="str"/>
+      <x:c r="N192" t="str"/>
+      <x:c r="O192" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" t="str">
+        <x:v>FINAL_ACCESSIBLE_ACCESS_II_01</x:v>
+      </x:c>
+      <x:c r="B193" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C193" t="str">
+        <x:v>final_review</x:v>
+      </x:c>
+      <x:c r="D193" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E193" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F193" t="str">
+        <x:v>Mirador final con Lía, accesos y acciones visibles.</x:v>
+      </x:c>
+      <x:c r="G193" t="str">
+        <x:v>Visitante llegó al cierre.</x:v>
+      </x:c>
+      <x:c r="H193" t="str">
+        <x:v>Describir acceso a Mundo II.</x:v>
+      </x:c>
+      <x:c r="I193" t="str">
+        <x:v>Acceso Pulso</x:v>
+      </x:c>
+      <x:c r="J193" t="str">
+        <x:v>Texto largo</x:v>
+      </x:c>
+      <x:c r="K193" t="str">
+        <x:v>50-110 caracteres</x:v>
+      </x:c>
+      <x:c r="L193" t="str"/>
+      <x:c r="M193" t="str"/>
+      <x:c r="N193" t="str"/>
+      <x:c r="O193" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" t="str">
+        <x:v>FINAL_ACCESSIBLE_ACCESS_III_01</x:v>
+      </x:c>
+      <x:c r="B194" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C194" t="str">
+        <x:v>final_review</x:v>
+      </x:c>
+      <x:c r="D194" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E194" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F194" t="str">
+        <x:v>Mirador final con Lía, accesos y acciones visibles.</x:v>
+      </x:c>
+      <x:c r="G194" t="str">
+        <x:v>Visitante llegó al cierre.</x:v>
+      </x:c>
+      <x:c r="H194" t="str">
+        <x:v>Describir acceso a Mundo III.</x:v>
+      </x:c>
+      <x:c r="I194" t="str">
+        <x:v>Acceso Cuaderno</x:v>
+      </x:c>
+      <x:c r="J194" t="str">
+        <x:v>Texto largo</x:v>
+      </x:c>
+      <x:c r="K194" t="str">
+        <x:v>50-120 caracteres</x:v>
+      </x:c>
+      <x:c r="L194" t="str"/>
+      <x:c r="M194" t="str"/>
+      <x:c r="N194" t="str"/>
+      <x:c r="O194" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" t="str">
+        <x:v>FINAL_ACCESSIBLE_ACCESS_IV_01</x:v>
+      </x:c>
+      <x:c r="B195" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C195" t="str">
+        <x:v>final_review</x:v>
+      </x:c>
+      <x:c r="D195" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E195" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F195" t="str">
+        <x:v>Mirador final con Lía, accesos y acciones visibles.</x:v>
+      </x:c>
+      <x:c r="G195" t="str">
+        <x:v>Visitante llegó al cierre.</x:v>
+      </x:c>
+      <x:c r="H195" t="str">
+        <x:v>Describir acceso a Mundo IV.</x:v>
+      </x:c>
+      <x:c r="I195" t="str">
+        <x:v>Acceso Mesa</x:v>
+      </x:c>
+      <x:c r="J195" t="str">
+        <x:v>Texto largo</x:v>
+      </x:c>
+      <x:c r="K195" t="str">
+        <x:v>50-120 caracteres</x:v>
+      </x:c>
+      <x:c r="L195" t="str"/>
+      <x:c r="M195" t="str"/>
+      <x:c r="N195" t="str"/>
+      <x:c r="O195" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" t="str">
+        <x:v>FINAL_ACCESSIBLE_ACCESS_V_01</x:v>
+      </x:c>
+      <x:c r="B196" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C196" t="str">
+        <x:v>final_review</x:v>
+      </x:c>
+      <x:c r="D196" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E196" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F196" t="str">
+        <x:v>Mirador final con Lía, accesos y acciones visibles.</x:v>
+      </x:c>
+      <x:c r="G196" t="str">
+        <x:v>Visitante llegó al cierre.</x:v>
+      </x:c>
+      <x:c r="H196" t="str">
+        <x:v>Describir acceso a Mundo V.</x:v>
+      </x:c>
+      <x:c r="I196" t="str">
+        <x:v>Acceso Mapa</x:v>
+      </x:c>
+      <x:c r="J196" t="str">
+        <x:v>Texto largo</x:v>
+      </x:c>
+      <x:c r="K196" t="str">
+        <x:v>50-120 caracteres</x:v>
+      </x:c>
+      <x:c r="L196" t="str"/>
+      <x:c r="M196" t="str"/>
+      <x:c r="N196" t="str"/>
+      <x:c r="O196" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" t="str">
+        <x:v>FINAL_ACCESSIBLE_BACK_HOME_01</x:v>
+      </x:c>
+      <x:c r="B197" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C197" t="str">
+        <x:v>final_return</x:v>
+      </x:c>
+      <x:c r="D197" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E197" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F197" t="str">
+        <x:v>Acción de volver al inicio visible.</x:v>
+      </x:c>
+      <x:c r="G197" t="str">
+        <x:v>Visitante evalúa salir al inicio.</x:v>
+      </x:c>
+      <x:c r="H197" t="str">
+        <x:v>Describir acción de volver al inicio.</x:v>
+      </x:c>
+      <x:c r="I197" t="str">
+        <x:v>Volver</x:v>
+      </x:c>
+      <x:c r="J197" t="str">
+        <x:v>Reinicio accidental</x:v>
+      </x:c>
+      <x:c r="K197" t="str">
+        <x:v>50-120 caracteres</x:v>
+      </x:c>
+      <x:c r="L197" t="str"/>
+      <x:c r="M197" t="str"/>
+      <x:c r="N197" t="str"/>
+      <x:c r="O197" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" t="str">
+        <x:v>FINAL_ACCESSIBLE_RESTART_01</x:v>
+      </x:c>
+      <x:c r="B198" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C198" t="str">
+        <x:v>final_restart_confirm</x:v>
+      </x:c>
+      <x:c r="D198" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E198" t="str">
+        <x:v>Descripción accesible</x:v>
+      </x:c>
+      <x:c r="F198" t="str">
+        <x:v>Acción de reinicio o confirmación visible.</x:v>
+      </x:c>
+      <x:c r="G198" t="str">
+        <x:v>Visitante tocó reiniciar recorrido.</x:v>
+      </x:c>
+      <x:c r="H198" t="str">
+        <x:v>Describir acción crítica de reinicio.</x:v>
+      </x:c>
+      <x:c r="I198" t="str">
+        <x:v>Reinicio completo</x:v>
+      </x:c>
+      <x:c r="J198" t="str">
+        <x:v>Ambigüedad</x:v>
+      </x:c>
+      <x:c r="K198" t="str">
+        <x:v>50-130 caracteres</x:v>
+      </x:c>
+      <x:c r="L198" t="str"/>
+      <x:c r="M198" t="str"/>
+      <x:c r="N198" t="str"/>
+      <x:c r="O198" t="str">
+        <x:v>Pendiente escritor</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/docs/narrative/02_MATRIZ_DIALOGOS_Y_TEXTOS_GVO.xlsx
+++ b/docs/narrative/02_MATRIZ_DIALOGOS_Y_TEXTOS_GVO.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz" sheetId="1" r:id="R4601b69ae7054791"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz" sheetId="1" r:id="Rd37d14bc75a847c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -85,9 +85,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -190,6 +190,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="12" max="12" width="50" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="72" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
@@ -1092,11 +1098,15 @@
       <x:c r="K22" t="str">
         <x:v>30-80 caracteres</x:v>
       </x:c>
-      <x:c r="L22" t="str"/>
+      <x:c r="L22" t="str">
+        <x:v>Abriendo Mundo III</x:v>
+      </x:c>
       <x:c r="M22" t="str"/>
-      <x:c r="N22" t="str"/>
+      <x:c r="N22" t="str">
+        <x:v>Copy runtime definitivo; aprobación humana consolidada por GVO-017K-R1.</x:v>
+      </x:c>
       <x:c r="O22" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>FINAL / human_approved</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1133,11 +1143,15 @@
       <x:c r="K23" t="str">
         <x:v>25-70 caracteres</x:v>
       </x:c>
-      <x:c r="L23" t="str"/>
+      <x:c r="L23" t="str">
+        <x:v>Preparando el Cuaderno Pixel de Pruebas…</x:v>
+      </x:c>
       <x:c r="M23" t="str"/>
-      <x:c r="N23" t="str"/>
+      <x:c r="N23" t="str">
+        <x:v>Copy runtime definitivo; aprobación humana consolidada por GVO-017K-R1.</x:v>
+      </x:c>
       <x:c r="O23" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>FINAL / human_approved</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -3556,7 +3570,7 @@
       <x:c r="M82" t="str"/>
       <x:c r="N82" t="str"/>
       <x:c r="O82" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -3597,7 +3611,7 @@
       <x:c r="M83" t="str"/>
       <x:c r="N83" t="str"/>
       <x:c r="O83" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -3638,7 +3652,7 @@
       <x:c r="M84" t="str"/>
       <x:c r="N84" t="str"/>
       <x:c r="O84" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -3679,7 +3693,7 @@
       <x:c r="M85" t="str"/>
       <x:c r="N85" t="str"/>
       <x:c r="O85" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -3720,7 +3734,7 @@
       <x:c r="M86" t="str"/>
       <x:c r="N86" t="str"/>
       <x:c r="O86" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -3761,7 +3775,7 @@
       <x:c r="M87" t="str"/>
       <x:c r="N87" t="str"/>
       <x:c r="O87" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -3802,7 +3816,7 @@
       <x:c r="M88" t="str"/>
       <x:c r="N88" t="str"/>
       <x:c r="O88" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -3843,7 +3857,7 @@
       <x:c r="M89" t="str"/>
       <x:c r="N89" t="str"/>
       <x:c r="O89" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -3884,7 +3898,7 @@
       <x:c r="M90" t="str"/>
       <x:c r="N90" t="str"/>
       <x:c r="O90" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -3925,7 +3939,7 @@
       <x:c r="M91" t="str"/>
       <x:c r="N91" t="str"/>
       <x:c r="O91" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -3966,7 +3980,7 @@
       <x:c r="M92" t="str"/>
       <x:c r="N92" t="str"/>
       <x:c r="O92" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -4007,7 +4021,7 @@
       <x:c r="M93" t="str"/>
       <x:c r="N93" t="str"/>
       <x:c r="O93" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -4048,7 +4062,7 @@
       <x:c r="M94" t="str"/>
       <x:c r="N94" t="str"/>
       <x:c r="O94" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -4089,7 +4103,7 @@
       <x:c r="M95" t="str"/>
       <x:c r="N95" t="str"/>
       <x:c r="O95" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -4130,7 +4144,7 @@
       <x:c r="M96" t="str"/>
       <x:c r="N96" t="str"/>
       <x:c r="O96" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -4171,7 +4185,7 @@
       <x:c r="M97" t="str"/>
       <x:c r="N97" t="str"/>
       <x:c r="O97" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -4212,7 +4226,7 @@
       <x:c r="M98" t="str"/>
       <x:c r="N98" t="str"/>
       <x:c r="O98" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -4253,7 +4267,7 @@
       <x:c r="M99" t="str"/>
       <x:c r="N99" t="str"/>
       <x:c r="O99" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -4294,7 +4308,7 @@
       <x:c r="M100" t="str"/>
       <x:c r="N100" t="str"/>
       <x:c r="O100" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -4335,7 +4349,7 @@
       <x:c r="M101" t="str"/>
       <x:c r="N101" t="str"/>
       <x:c r="O101" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -4376,7 +4390,7 @@
       <x:c r="M102" t="str"/>
       <x:c r="N102" t="str"/>
       <x:c r="O102" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -4417,7 +4431,7 @@
       <x:c r="M103" t="str"/>
       <x:c r="N103" t="str"/>
       <x:c r="O103" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -4458,7 +4472,7 @@
       <x:c r="M104" t="str"/>
       <x:c r="N104" t="str"/>
       <x:c r="O104" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>LEGACY / no consumido por runtime</x:v>
       </x:c>
     </x:row>
     <x:row r="105">

--- a/docs/narrative/02_MATRIZ_DIALOGOS_Y_TEXTOS_GVO.xlsx
+++ b/docs/narrative/02_MATRIZ_DIALOGOS_Y_TEXTOS_GVO.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz" sheetId="1" r:id="Rd37d14bc75a847c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz" sheetId="1" r:id="R5f3b1fd216be472b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7133,11 +7133,17 @@
       <x:c r="K169" t="str">
         <x:v>2-7 palabras</x:v>
       </x:c>
-      <x:c r="L169" t="str"/>
-      <x:c r="M169" t="str"/>
-      <x:c r="N169" t="str"/>
+      <x:c r="L169" t="str">
+        <x:v>Mirador final del jardín</x:v>
+      </x:c>
+      <x:c r="M169" t="str">
+        <x:v>Mirador final</x:v>
+      </x:c>
+      <x:c r="N169" t="str">
+        <x:v>Aprobado por Ing. José David el 2026-08-04.</x:v>
+      </x:c>
       <x:c r="O169" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -7174,11 +7180,17 @@
       <x:c r="K170" t="str">
         <x:v>2-8 palabras</x:v>
       </x:c>
-      <x:c r="L170" t="str"/>
-      <x:c r="M170" t="str"/>
-      <x:c r="N170" t="str"/>
+      <x:c r="L170" t="str">
+        <x:v>Recorrido completo</x:v>
+      </x:c>
+      <x:c r="M170" t="str">
+        <x:v>Recorrido completo</x:v>
+      </x:c>
+      <x:c r="N170" t="str">
+        <x:v>Aprobado por Ing. José David el 2026-08-04.</x:v>
+      </x:c>
       <x:c r="O170" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -7215,11 +7227,17 @@
       <x:c r="K171" t="str">
         <x:v>90-170 caracteres</x:v>
       </x:c>
-      <x:c r="L171" t="str"/>
-      <x:c r="M171" t="str"/>
-      <x:c r="N171" t="str"/>
+      <x:c r="L171" t="str">
+        <x:v>Llegaste al final del recorrido. Puedes volver a cualquier mundo cuando quieras.</x:v>
+      </x:c>
+      <x:c r="M171" t="str">
+        <x:v>Cierre y revisión libre</x:v>
+      </x:c>
+      <x:c r="N171" t="str">
+        <x:v>Aprobado por Ing. José David; excepción de longitud aceptada.</x:v>
+      </x:c>
       <x:c r="O171" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -7256,11 +7274,17 @@
       <x:c r="K172" t="str">
         <x:v>50-130 caracteres</x:v>
       </x:c>
-      <x:c r="L172" t="str"/>
-      <x:c r="M172" t="str"/>
-      <x:c r="N172" t="str"/>
+      <x:c r="L172" t="str">
+        <x:v>El jardín queda abierto para volver a mirarlo.</x:v>
+      </x:c>
+      <x:c r="M172" t="str">
+        <x:v>Jardín abierto</x:v>
+      </x:c>
+      <x:c r="N172" t="str">
+        <x:v>Aprobado por Ing. José David; excepción de longitud aceptada.</x:v>
+      </x:c>
       <x:c r="O172" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -7297,11 +7321,17 @@
       <x:c r="K173" t="str">
         <x:v>2-6 palabras</x:v>
       </x:c>
-      <x:c r="L173" t="str"/>
-      <x:c r="M173" t="str"/>
-      <x:c r="N173" t="str"/>
+      <x:c r="L173" t="str">
+        <x:v>I — Raíz</x:v>
+      </x:c>
+      <x:c r="M173" t="str">
+        <x:v>I — Raíz</x:v>
+      </x:c>
+      <x:c r="N173" t="str">
+        <x:v>Aprobado por Ing. José David el 2026-08-04.</x:v>
+      </x:c>
       <x:c r="O173" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -7338,11 +7368,17 @@
       <x:c r="K174" t="str">
         <x:v>40-100 caracteres</x:v>
       </x:c>
-      <x:c r="L174" t="str"/>
-      <x:c r="M174" t="str"/>
-      <x:c r="N174" t="str"/>
+      <x:c r="L174" t="str">
+        <x:v>Reabriendo Mundo I: Raíz…</x:v>
+      </x:c>
+      <x:c r="M174" t="str">
+        <x:v>Reabrir Mundo I</x:v>
+      </x:c>
+      <x:c r="N174" t="str">
+        <x:v>Aprobado por Ing. José David; excepción de longitud aceptada.</x:v>
+      </x:c>
       <x:c r="O174" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -7379,11 +7415,17 @@
       <x:c r="K175" t="str">
         <x:v>2-6 palabras</x:v>
       </x:c>
-      <x:c r="L175" t="str"/>
-      <x:c r="M175" t="str"/>
-      <x:c r="N175" t="str"/>
+      <x:c r="L175" t="str">
+        <x:v>II — Pulso invisible</x:v>
+      </x:c>
+      <x:c r="M175" t="str">
+        <x:v>II — Pulso invisible</x:v>
+      </x:c>
+      <x:c r="N175" t="str">
+        <x:v>Aprobado por Ing. José David el 2026-08-04.</x:v>
+      </x:c>
       <x:c r="O175" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="176">
@@ -7420,11 +7462,17 @@
       <x:c r="K176" t="str">
         <x:v>40-100 caracteres</x:v>
       </x:c>
-      <x:c r="L176" t="str"/>
-      <x:c r="M176" t="str"/>
-      <x:c r="N176" t="str"/>
+      <x:c r="L176" t="str">
+        <x:v>Reabriendo Mundo II: Pulso invisible…</x:v>
+      </x:c>
+      <x:c r="M176" t="str">
+        <x:v>Reabrir Mundo II</x:v>
+      </x:c>
+      <x:c r="N176" t="str">
+        <x:v>Aprobado por Ing. José David; excepción de longitud aceptada.</x:v>
+      </x:c>
       <x:c r="O176" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -7461,11 +7509,17 @@
       <x:c r="K177" t="str">
         <x:v>2-6 palabras</x:v>
       </x:c>
-      <x:c r="L177" t="str"/>
-      <x:c r="M177" t="str"/>
-      <x:c r="N177" t="str"/>
+      <x:c r="L177" t="str">
+        <x:v>III — Cuaderno de pruebas</x:v>
+      </x:c>
+      <x:c r="M177" t="str">
+        <x:v>III — Cuaderno</x:v>
+      </x:c>
+      <x:c r="N177" t="str">
+        <x:v>Aprobado por Ing. José David el 2026-08-04.</x:v>
+      </x:c>
       <x:c r="O177" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
@@ -7502,11 +7556,17 @@
       <x:c r="K178" t="str">
         <x:v>40-100 caracteres</x:v>
       </x:c>
-      <x:c r="L178" t="str"/>
-      <x:c r="M178" t="str"/>
-      <x:c r="N178" t="str"/>
+      <x:c r="L178" t="str">
+        <x:v>Reabriendo Mundo III: Cuaderno de pruebas…</x:v>
+      </x:c>
+      <x:c r="M178" t="str">
+        <x:v>Reabrir Mundo III</x:v>
+      </x:c>
+      <x:c r="N178" t="str">
+        <x:v>Aprobado por Ing. José David el 2026-08-04.</x:v>
+      </x:c>
       <x:c r="O178" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
@@ -7543,11 +7603,17 @@
       <x:c r="K179" t="str">
         <x:v>2-6 palabras</x:v>
       </x:c>
-      <x:c r="L179" t="str"/>
-      <x:c r="M179" t="str"/>
-      <x:c r="N179" t="str"/>
+      <x:c r="L179" t="str">
+        <x:v>IV — Mesa de sistema</x:v>
+      </x:c>
+      <x:c r="M179" t="str">
+        <x:v>IV — Mesa</x:v>
+      </x:c>
+      <x:c r="N179" t="str">
+        <x:v>Aprobado por Ing. José David el 2026-08-04.</x:v>
+      </x:c>
       <x:c r="O179" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="180">
@@ -7584,11 +7650,17 @@
       <x:c r="K180" t="str">
         <x:v>40-100 caracteres</x:v>
       </x:c>
-      <x:c r="L180" t="str"/>
-      <x:c r="M180" t="str"/>
-      <x:c r="N180" t="str"/>
+      <x:c r="L180" t="str">
+        <x:v>Reabriendo Mundo IV: Mesa de sistema…</x:v>
+      </x:c>
+      <x:c r="M180" t="str">
+        <x:v>Reabrir Mundo IV</x:v>
+      </x:c>
+      <x:c r="N180" t="str">
+        <x:v>Aprobado por Ing. José David; excepción de longitud aceptada.</x:v>
+      </x:c>
       <x:c r="O180" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
@@ -7625,11 +7697,17 @@
       <x:c r="K181" t="str">
         <x:v>2-6 palabras</x:v>
       </x:c>
-      <x:c r="L181" t="str"/>
-      <x:c r="M181" t="str"/>
-      <x:c r="N181" t="str"/>
+      <x:c r="L181" t="str">
+        <x:v>V — Mapa del presente</x:v>
+      </x:c>
+      <x:c r="M181" t="str">
+        <x:v>V — Mapa</x:v>
+      </x:c>
+      <x:c r="N181" t="str">
+        <x:v>Aprobado por Ing. José David el 2026-08-04.</x:v>
+      </x:c>
       <x:c r="O181" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
@@ -7666,11 +7744,17 @@
       <x:c r="K182" t="str">
         <x:v>40-100 caracteres</x:v>
       </x:c>
-      <x:c r="L182" t="str"/>
-      <x:c r="M182" t="str"/>
-      <x:c r="N182" t="str"/>
+      <x:c r="L182" t="str">
+        <x:v>Reabriendo Mundo V: Mapa del presente…</x:v>
+      </x:c>
+      <x:c r="M182" t="str">
+        <x:v>Reabrir Mundo V</x:v>
+      </x:c>
+      <x:c r="N182" t="str">
+        <x:v>Aprobado por Ing. José David; excepción de longitud aceptada.</x:v>
+      </x:c>
       <x:c r="O182" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="183">
@@ -7707,11 +7791,17 @@
       <x:c r="K183" t="str">
         <x:v>60-130 caracteres</x:v>
       </x:c>
-      <x:c r="L183" t="str"/>
-      <x:c r="M183" t="str"/>
-      <x:c r="N183" t="str"/>
+      <x:c r="L183" t="str">
+        <x:v>Elige un mundo para revisarlo libremente.</x:v>
+      </x:c>
+      <x:c r="M183" t="str">
+        <x:v>Revisión libre</x:v>
+      </x:c>
+      <x:c r="N183" t="str">
+        <x:v>Aprobado por Ing. José David; excepción de longitud aceptada.</x:v>
+      </x:c>
       <x:c r="O183" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
@@ -7748,11 +7838,17 @@
       <x:c r="K184" t="str">
         <x:v>1-4 palabras</x:v>
       </x:c>
-      <x:c r="L184" t="str"/>
-      <x:c r="M184" t="str"/>
-      <x:c r="N184" t="str"/>
+      <x:c r="L184" t="str">
+        <x:v>Volver al inicio</x:v>
+      </x:c>
+      <x:c r="M184" t="str">
+        <x:v>Volver al inicio</x:v>
+      </x:c>
+      <x:c r="N184" t="str">
+        <x:v>Aprobado por Ing. José David el 2026-08-04.</x:v>
+      </x:c>
       <x:c r="O184" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
@@ -7789,11 +7885,17 @@
       <x:c r="K185" t="str">
         <x:v>50-120 caracteres</x:v>
       </x:c>
-      <x:c r="L185" t="str"/>
-      <x:c r="M185" t="str"/>
-      <x:c r="N185" t="str"/>
+      <x:c r="L185" t="str">
+        <x:v>Regresa a la portada sin borrar tu recorrido.</x:v>
+      </x:c>
+      <x:c r="M185" t="str">
+        <x:v>Conservar recorrido</x:v>
+      </x:c>
+      <x:c r="N185" t="str">
+        <x:v>Aprobado por Ing. José David; excepción de longitud aceptada.</x:v>
+      </x:c>
       <x:c r="O185" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="186">
@@ -7830,11 +7932,17 @@
       <x:c r="K186" t="str">
         <x:v>1-4 palabras</x:v>
       </x:c>
-      <x:c r="L186" t="str"/>
-      <x:c r="M186" t="str"/>
-      <x:c r="N186" t="str"/>
+      <x:c r="L186" t="str">
+        <x:v>Reiniciar recorrido</x:v>
+      </x:c>
+      <x:c r="M186" t="str">
+        <x:v>Reiniciar recorrido</x:v>
+      </x:c>
+      <x:c r="N186" t="str">
+        <x:v>Aprobado por Ing. José David el 2026-08-04.</x:v>
+      </x:c>
       <x:c r="O186" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
@@ -7871,11 +7979,17 @@
       <x:c r="K187" t="str">
         <x:v>60-130 caracteres</x:v>
       </x:c>
-      <x:c r="L187" t="str"/>
-      <x:c r="M187" t="str"/>
-      <x:c r="N187" t="str"/>
+      <x:c r="L187" t="str">
+        <x:v>¿Quieres reiniciar el recorrido completo? Volverás a comenzar desde el inicio.</x:v>
+      </x:c>
+      <x:c r="M187" t="str">
+        <x:v>Confirmar reinicio</x:v>
+      </x:c>
+      <x:c r="N187" t="str">
+        <x:v>Aprobado por Ing. José David el 2026-08-04.</x:v>
+      </x:c>
       <x:c r="O187" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
@@ -7912,11 +8026,17 @@
       <x:c r="K188" t="str">
         <x:v>1-3 palabras</x:v>
       </x:c>
-      <x:c r="L188" t="str"/>
-      <x:c r="M188" t="str"/>
-      <x:c r="N188" t="str"/>
+      <x:c r="L188" t="str">
+        <x:v>Cancelar</x:v>
+      </x:c>
+      <x:c r="M188" t="str">
+        <x:v>Cancelar</x:v>
+      </x:c>
+      <x:c r="N188" t="str">
+        <x:v>Aprobado por Ing. José David el 2026-08-04.</x:v>
+      </x:c>
       <x:c r="O188" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
@@ -7953,11 +8073,17 @@
       <x:c r="K189" t="str">
         <x:v>1-4 palabras</x:v>
       </x:c>
-      <x:c r="L189" t="str"/>
-      <x:c r="M189" t="str"/>
-      <x:c r="N189" t="str"/>
+      <x:c r="L189" t="str">
+        <x:v>Reiniciar recorrido</x:v>
+      </x:c>
+      <x:c r="M189" t="str">
+        <x:v>Reiniciar recorrido</x:v>
+      </x:c>
+      <x:c r="N189" t="str">
+        <x:v>Aprobado por Ing. José David el 2026-08-04.</x:v>
+      </x:c>
       <x:c r="O189" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
@@ -7994,11 +8120,18 @@
       <x:c r="K190" t="str">
         <x:v>Variable</x:v>
       </x:c>
-      <x:c r="L190" t="str"/>
-      <x:c r="M190" t="str"/>
-      <x:c r="N190" t="str"/>
+      <x:c r="L190" t="str">
+        <x:v>Desarrollado por Momotto S.A.S.
+A cargo del Ing. José David Pérez Zapata.</x:v>
+      </x:c>
+      <x:c r="M190" t="str">
+        <x:v>Créditos</x:v>
+      </x:c>
+      <x:c r="N190" t="str">
+        <x:v>Mostrar las dos líneas con salto DOM.</x:v>
+      </x:c>
       <x:c r="O190" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
@@ -8035,11 +8168,17 @@
       <x:c r="K191" t="str">
         <x:v>90-180 caracteres</x:v>
       </x:c>
-      <x:c r="L191" t="str"/>
-      <x:c r="M191" t="str"/>
-      <x:c r="N191" t="str"/>
+      <x:c r="L191" t="str">
+        <x:v>Mirador final del jardín con cinco accesos de revisión, Lía, regreso a la portada y reinicio del recorrido.</x:v>
+      </x:c>
+      <x:c r="M191" t="str">
+        <x:v>Escena accesible final</x:v>
+      </x:c>
+      <x:c r="N191" t="str">
+        <x:v>Aprobado por Ing. José David el 2026-08-04.</x:v>
+      </x:c>
       <x:c r="O191" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
@@ -8076,11 +8215,17 @@
       <x:c r="K192" t="str">
         <x:v>50-110 caracteres</x:v>
       </x:c>
-      <x:c r="L192" t="str"/>
-      <x:c r="M192" t="str"/>
-      <x:c r="N192" t="str"/>
+      <x:c r="L192" t="str">
+        <x:v>Revisar Mundo I: Raíz</x:v>
+      </x:c>
+      <x:c r="M192" t="str">
+        <x:v>Revisar Mundo I</x:v>
+      </x:c>
+      <x:c r="N192" t="str">
+        <x:v>Aprobado por Ing. José David; excepción de longitud aceptada.</x:v>
+      </x:c>
       <x:c r="O192" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="193">
@@ -8117,11 +8262,17 @@
       <x:c r="K193" t="str">
         <x:v>50-110 caracteres</x:v>
       </x:c>
-      <x:c r="L193" t="str"/>
-      <x:c r="M193" t="str"/>
-      <x:c r="N193" t="str"/>
+      <x:c r="L193" t="str">
+        <x:v>Revisar Mundo II: Pulso invisible</x:v>
+      </x:c>
+      <x:c r="M193" t="str">
+        <x:v>Revisar Mundo II</x:v>
+      </x:c>
+      <x:c r="N193" t="str">
+        <x:v>Aprobado por Ing. José David; excepción de longitud aceptada.</x:v>
+      </x:c>
       <x:c r="O193" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="194">
@@ -8158,11 +8309,17 @@
       <x:c r="K194" t="str">
         <x:v>50-120 caracteres</x:v>
       </x:c>
-      <x:c r="L194" t="str"/>
-      <x:c r="M194" t="str"/>
-      <x:c r="N194" t="str"/>
+      <x:c r="L194" t="str">
+        <x:v>Revisar Mundo III: Cuaderno de pruebas</x:v>
+      </x:c>
+      <x:c r="M194" t="str">
+        <x:v>Revisar Mundo III</x:v>
+      </x:c>
+      <x:c r="N194" t="str">
+        <x:v>Aprobado por Ing. José David; excepción de longitud aceptada.</x:v>
+      </x:c>
       <x:c r="O194" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="195">
@@ -8199,11 +8356,17 @@
       <x:c r="K195" t="str">
         <x:v>50-120 caracteres</x:v>
       </x:c>
-      <x:c r="L195" t="str"/>
-      <x:c r="M195" t="str"/>
-      <x:c r="N195" t="str"/>
+      <x:c r="L195" t="str">
+        <x:v>Revisar Mundo IV: Mesa de sistema</x:v>
+      </x:c>
+      <x:c r="M195" t="str">
+        <x:v>Revisar Mundo IV</x:v>
+      </x:c>
+      <x:c r="N195" t="str">
+        <x:v>Aprobado por Ing. José David; excepción de longitud aceptada.</x:v>
+      </x:c>
       <x:c r="O195" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="196">
@@ -8240,11 +8403,17 @@
       <x:c r="K196" t="str">
         <x:v>50-120 caracteres</x:v>
       </x:c>
-      <x:c r="L196" t="str"/>
-      <x:c r="M196" t="str"/>
-      <x:c r="N196" t="str"/>
+      <x:c r="L196" t="str">
+        <x:v>Revisar Mundo V: Mapa del presente</x:v>
+      </x:c>
+      <x:c r="M196" t="str">
+        <x:v>Revisar Mundo V</x:v>
+      </x:c>
+      <x:c r="N196" t="str">
+        <x:v>Aprobado por Ing. José David; excepción de longitud aceptada.</x:v>
+      </x:c>
       <x:c r="O196" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="197">
@@ -8281,11 +8450,17 @@
       <x:c r="K197" t="str">
         <x:v>50-120 caracteres</x:v>
       </x:c>
-      <x:c r="L197" t="str"/>
-      <x:c r="M197" t="str"/>
-      <x:c r="N197" t="str"/>
+      <x:c r="L197" t="str">
+        <x:v>Volver a la portada sin borrar el recorrido completado</x:v>
+      </x:c>
+      <x:c r="M197" t="str">
+        <x:v>Volver sin borrar</x:v>
+      </x:c>
+      <x:c r="N197" t="str">
+        <x:v>Aprobado por Ing. José David el 2026-08-04.</x:v>
+      </x:c>
       <x:c r="O197" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
     <x:row r="198">
@@ -8322,11 +8497,252 @@
       <x:c r="K198" t="str">
         <x:v>50-130 caracteres</x:v>
       </x:c>
-      <x:c r="L198" t="str"/>
-      <x:c r="M198" t="str"/>
-      <x:c r="N198" t="str"/>
+      <x:c r="L198" t="str">
+        <x:v>Reiniciar el recorrido completo después de confirmar</x:v>
+      </x:c>
+      <x:c r="M198" t="str">
+        <x:v>Reinicio con confirmación</x:v>
+      </x:c>
+      <x:c r="N198" t="str">
+        <x:v>Aprobado por Ing. José David el 2026-08-04.</x:v>
+      </x:c>
       <x:c r="O198" t="str">
-        <x:v>Pendiente escritor</x:v>
+        <x:v>Aprobado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" t="str">
+        <x:v>FINAL_RETURN_TO_MIRADOR_BTN_01</x:v>
+      </x:c>
+      <x:c r="B199" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C199" t="str">
+        <x:v>final_return_to_mirador</x:v>
+      </x:c>
+      <x:c r="D199" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E199" t="str">
+        <x:v>Botón</x:v>
+      </x:c>
+      <x:c r="F199" t="str">
+        <x:v>Revisita de un mundo desde el Mirador.</x:v>
+      </x:c>
+      <x:c r="G199" t="str">
+        <x:v>Visitante revisita un mundo.</x:v>
+      </x:c>
+      <x:c r="H199" t="str">
+        <x:v>Volver al Mirador final.</x:v>
+      </x:c>
+      <x:c r="I199" t="str">
+        <x:v>Retorno al Mirador</x:v>
+      </x:c>
+      <x:c r="J199" t="str">
+        <x:v>Crear navegación sin ticket</x:v>
+      </x:c>
+      <x:c r="K199" t="str">
+        <x:v>1-4 palabras</x:v>
+      </x:c>
+      <x:c r="L199" t="str">
+        <x:v>Volver al Mirador</x:v>
+      </x:c>
+      <x:c r="M199" t="str">
+        <x:v>Volver al Mirador</x:v>
+      </x:c>
+      <x:c r="N199" t="str">
+        <x:v>Registrado sin consumidor funcional.</x:v>
+      </x:c>
+      <x:c r="O199" t="str">
+        <x:v>Aprobado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" t="str">
+        <x:v>FINAL_ACCESSIBLE_RETURN_TO_MIRADOR_01</x:v>
+      </x:c>
+      <x:c r="B200" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C200" t="str">
+        <x:v>final_return_to_mirador</x:v>
+      </x:c>
+      <x:c r="D200" t="str">
+        <x:v>Sistema / accesibilidad</x:v>
+      </x:c>
+      <x:c r="E200" t="str">
+        <x:v>Nombre accesible</x:v>
+      </x:c>
+      <x:c r="F200" t="str">
+        <x:v>Revisita de un mundo desde el Mirador.</x:v>
+      </x:c>
+      <x:c r="G200" t="str">
+        <x:v>Visitante revisita un mundo.</x:v>
+      </x:c>
+      <x:c r="H200" t="str">
+        <x:v>Nombrar el retorno al Mirador.</x:v>
+      </x:c>
+      <x:c r="I200" t="str">
+        <x:v>Retorno accesible</x:v>
+      </x:c>
+      <x:c r="J200" t="str">
+        <x:v>Texto visible duplicado</x:v>
+      </x:c>
+      <x:c r="K200" t="str">
+        <x:v>Variable</x:v>
+      </x:c>
+      <x:c r="L200" t="str">
+        <x:v>Volver al Mirador final desde este mundo</x:v>
+      </x:c>
+      <x:c r="M200" t="str">
+        <x:v>Retorno accesible</x:v>
+      </x:c>
+      <x:c r="N200" t="str">
+        <x:v>Registrado sin consumidor funcional.</x:v>
+      </x:c>
+      <x:c r="O200" t="str">
+        <x:v>Aprobado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" t="str">
+        <x:v>FINAL_RESTART_BUSY_01</x:v>
+      </x:c>
+      <x:c r="B201" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C201" t="str">
+        <x:v>final_restart_busy</x:v>
+      </x:c>
+      <x:c r="D201" t="str">
+        <x:v>Sistema</x:v>
+      </x:c>
+      <x:c r="E201" t="str">
+        <x:v>Estado busy</x:v>
+      </x:c>
+      <x:c r="F201" t="str">
+        <x:v>Reinicio completo en curso.</x:v>
+      </x:c>
+      <x:c r="G201" t="str">
+        <x:v>Visitante confirmó reinicio.</x:v>
+      </x:c>
+      <x:c r="H201" t="str">
+        <x:v>Anunciar reinicio en curso.</x:v>
+      </x:c>
+      <x:c r="I201" t="str">
+        <x:v>Reinicio en curso</x:v>
+      </x:c>
+      <x:c r="J201" t="str">
+        <x:v>Prometer éxito</x:v>
+      </x:c>
+      <x:c r="K201" t="str">
+        <x:v>Variable</x:v>
+      </x:c>
+      <x:c r="L201" t="str">
+        <x:v>Reiniciando recorrido…</x:v>
+      </x:c>
+      <x:c r="M201" t="str">
+        <x:v>Reiniciando</x:v>
+      </x:c>
+      <x:c r="N201" t="str">
+        <x:v>Registrado sin consumidor funcional.</x:v>
+      </x:c>
+      <x:c r="O201" t="str">
+        <x:v>Aprobado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" t="str">
+        <x:v>FINAL_RESTART_ERROR_01</x:v>
+      </x:c>
+      <x:c r="B202" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C202" t="str">
+        <x:v>final_restart_error</x:v>
+      </x:c>
+      <x:c r="D202" t="str">
+        <x:v>Sistema</x:v>
+      </x:c>
+      <x:c r="E202" t="str">
+        <x:v>Error visible</x:v>
+      </x:c>
+      <x:c r="F202" t="str">
+        <x:v>Reinicio completo falló.</x:v>
+      </x:c>
+      <x:c r="G202" t="str">
+        <x:v>Fallo posterior a confirmación.</x:v>
+      </x:c>
+      <x:c r="H202" t="str">
+        <x:v>Informar fallo y conservación verificada.</x:v>
+      </x:c>
+      <x:c r="I202" t="str">
+        <x:v>Progreso conservado</x:v>
+      </x:c>
+      <x:c r="J202" t="str">
+        <x:v>Afirmar rollback no verificado</x:v>
+      </x:c>
+      <x:c r="K202" t="str">
+        <x:v>Variable</x:v>
+      </x:c>
+      <x:c r="L202" t="str">
+        <x:v>No pudimos reiniciar el recorrido. Tu progreso se conservó.</x:v>
+      </x:c>
+      <x:c r="M202" t="str">
+        <x:v>Error de reinicio</x:v>
+      </x:c>
+      <x:c r="N202" t="str">
+        <x:v>Solo consumir tras verificar rollback.</x:v>
+      </x:c>
+      <x:c r="O202" t="str">
+        <x:v>Aprobado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" t="str">
+        <x:v>FINAL_RESTART_RETRY_BTN_01</x:v>
+      </x:c>
+      <x:c r="B203" t="str">
+        <x:v>Pantalla final — Mirador</x:v>
+      </x:c>
+      <x:c r="C203" t="str">
+        <x:v>final_restart_error</x:v>
+      </x:c>
+      <x:c r="D203" t="str">
+        <x:v>Sistema / interfaz</x:v>
+      </x:c>
+      <x:c r="E203" t="str">
+        <x:v>Botón</x:v>
+      </x:c>
+      <x:c r="F203" t="str">
+        <x:v>Error de reinicio visible.</x:v>
+      </x:c>
+      <x:c r="G203" t="str">
+        <x:v>Reinicio completo falló.</x:v>
+      </x:c>
+      <x:c r="H203" t="str">
+        <x:v>Reintentar la operación.</x:v>
+      </x:c>
+      <x:c r="I203" t="str">
+        <x:v>Reintento</x:v>
+      </x:c>
+      <x:c r="J203" t="str">
+        <x:v>Ejecutar sin confirmación</x:v>
+      </x:c>
+      <x:c r="K203" t="str">
+        <x:v>1-2 palabras</x:v>
+      </x:c>
+      <x:c r="L203" t="str">
+        <x:v>Reintentar</x:v>
+      </x:c>
+      <x:c r="M203" t="str">
+        <x:v>Reintentar</x:v>
+      </x:c>
+      <x:c r="N203" t="str">
+        <x:v>Registrado sin consumidor funcional.</x:v>
+      </x:c>
+      <x:c r="O203" t="str">
+        <x:v>Aprobado</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/docs/narrative/02_MATRIZ_DIALOGOS_Y_TEXTOS_GVO.xlsx
+++ b/docs/narrative/02_MATRIZ_DIALOGOS_Y_TEXTOS_GVO.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz" sheetId="1" r:id="R5f3b1fd216be472b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz" sheetId="1" r:id="R37af3cd10dc54457"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8122,13 +8122,13 @@
       </x:c>
       <x:c r="L190" t="str">
         <x:v>Desarrollado por Momotto S.A.S.
-A cargo del Ing. José David Pérez Zapata.</x:v>
+A cargo del Ing. José David P. Z.</x:v>
       </x:c>
       <x:c r="M190" t="str">
         <x:v>Créditos</x:v>
       </x:c>
       <x:c r="N190" t="str">
-        <x:v>Mostrar las dos líneas con salto DOM.</x:v>
+        <x:v>Mostrar las dos líneas con salto DOM. Copy corto aprobado por GVO_FINAL_021K.</x:v>
       </x:c>
       <x:c r="O190" t="str">
         <x:v>Aprobado</x:v>
